--- a/docs/ExplorationMissions_DesignDocument.xlsx
+++ b/docs/ExplorationMissions_DesignDocument.xlsx
@@ -1782,7 +1782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A2:L42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="4.375" customWidth="1" style="43" min="1" max="1"/>
@@ -1793,7 +1793,6 @@
     <col width="9" customWidth="1" style="43" min="17" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -1906,7 +1905,7 @@
       <c r="K6" s="65" t="n"/>
       <c r="L6" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1933,7 @@
       <c r="K7" s="65" t="n"/>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1961,7 @@
       <c r="K8" s="65" t="n"/>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1989,7 @@
       <c r="K9" s="65" t="n"/>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2017,7 @@
       <c r="K10" s="65" t="n"/>
       <c r="L10" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2045,7 @@
       <c r="K11" s="65" t="n"/>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2073,7 @@
       <c r="K12" s="65" t="n"/>
       <c r="L12" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2101,7 @@
       <c r="K13" s="65" t="n"/>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2129,7 @@
       <c r="K14" s="65" t="n"/>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2157,7 @@
       <c r="K15" s="65" t="n"/>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2185,7 @@
       <c r="K16" s="65" t="n"/>
       <c r="L16" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2213,7 @@
       <c r="K17" s="65" t="n"/>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2241,7 @@
       <c r="K18" s="65" t="n"/>
       <c r="L18" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2269,7 @@
       <c r="K19" s="65" t="n"/>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2297,7 @@
       <c r="K20" s="65" t="n"/>
       <c r="L20" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2325,7 @@
       <c r="K21" s="65" t="n"/>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2352,7 @@
       <c r="K22" s="65" t="n"/>
       <c r="L22" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2379,7 @@
       <c r="K23" s="65" t="n"/>
       <c r="L23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2406,7 @@
       <c r="K24" s="65" t="n"/>
       <c r="L24" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2433,7 @@
       <c r="K25" s="68" t="n"/>
       <c r="L25" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Week</t>
+          <t>Juwon Lee</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF142"/>
+  <dimension ref="B2:AF142"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.625" defaultRowHeight="13.5"/>
   <cols>
     <col width="2.625" customWidth="1" style="15" min="1" max="1"/>
@@ -2853,7 +2852,7 @@
       <c r="C7" s="15" t="n"/>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">- Field's Exploration can present Direction and My/The when </t>
+          <t>-</t>
         </is>
       </c>
       <c r="E7" s="15" t="n"/>
@@ -2890,7 +2889,7 @@
       <c r="C8" s="15" t="n"/>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>- PLC And Required/Needed Currency Grant</t>
+          <t>- PLC</t>
         </is>
       </c>
       <c r="E8" s="15" t="n"/>
@@ -3029,7 +3028,7 @@
       <c r="B12" s="15" t="n"/>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>- Exploration Mission World per Exploration Mission and Area per Exploration Mission 2 's Entry to CategorizeDone/Applied</t>
+          <t>- Exploration Mission Exploration Mission zone Exploration Mission 2</t>
         </is>
       </c>
       <c r="D12" s="22" t="n"/>
@@ -5345,19 +5344,19 @@
       <c r="I81" s="76" t="n"/>
       <c r="J81" s="78" t="inlineStr">
         <is>
-          <t>Display Text : World Name
-Function
-• Each Worldper to Compositionapplied Category Button
-• World's sort Above in from MissionCategory.xml's ID Ascending to sort
- ◦ Quest_Adventure.xml's MissionCategoryID input
-• Click when 
- ◦ Arrow Below Direction state in Click when, Corresponding World's World And Area Area Exploration Mission. 
- After Arrow Direction to before
- ◦ Arrow Above Direction state in Click when, World And Area Exploration Mission List.
- After Arrow Below Direction to before
-• Claim Available Reward present Area's World Category red dot Display
- ◦ List when List also Display
-• Drag to Scroll Possible</t>
+          <t>displayed : 
+feature
+• composition 
+• MissionCategory.xml ID 
+◦ Quest_Adventure.xml MissionCategoryID enter
+• click 
+◦ arrow status click , zone zone Exploration Mission . 
+arrow 
+◦ arrow status click , zone Exploration Mission list .
+arrow 
+• possible reward zone displayed
+◦ list list displayed
+• possible</t>
         </is>
       </c>
       <c r="K81" s="71" t="n"/>
@@ -5400,28 +5399,28 @@
       <c r="I82" s="76" t="n"/>
       <c r="J82" s="78" t="inlineStr">
         <is>
-          <t>Display
-• List : World Name
-• List : Area Name
-• Unvisited Area/World : ?????? And Corresponding List Greyscale
-Display Icon
-• PC Location Area List In front Display
-Function
-• Click when 
- ◦ Corresponding World's Map Image time(s) can present Zoom In To the extent UI during Display
- ▪ Image Move when Separate's Moment to Camera Move
- ◦ Corresponding World's Exploration Mission Content UI Display
- ◦ time(s) also Not World And Area Click when None/N/A
- ◦ Selectapplied List Highlight processing
-• World Display
- ◦ Area List and Display
- ◦ Area List Quest_Adventure.xml Standard ID Ascending to sort
- ▪ World's Categorize Quest_Adventure.xml - RegionName to Categorize 
-• Current Achieve Degree X/Y to Display
- ◦ X : Achieve Mission's Count / Y : Corresponding Mission's Count
-• Corresponding World And Area's TRName Display
-• Drag to Scroll Possible
-• Reward Obtain Area And World's case Greyscale processing</t>
+          <t>displayed
+• list : 
+• list : zone 
+• zone/ : ?????? list greyed out
+displayed icon
+• PC zone list displayed
+feature
+• click 
+◦ UI displayed
+▪ move move
+◦ Exploration Mission UI displayed
+◦ zone click 
+◦ select list highlight 
+• displayed
+◦ zone list 
+◦ zone list Quest_Adventure.xml ID 
+▪ Quest_Adventure.xml - RegionName 
+• achieve X/Y displayed
+◦ X : achieve Mission / Y : Mission 
+• zone TRName displayed
+• possible
+• reward obtain zone greyed out</t>
         </is>
       </c>
       <c r="K82" s="71" t="n"/>
@@ -5605,26 +5604,25 @@
       <c r="I86" s="76" t="n"/>
       <c r="J86" s="78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Function
-• Select World or Area's Exploration Mission Info Display
- ◦ Exploration Mission And Map exist Not Area in UI Display when, previous Area's Location Standard to PCIcon Display And UI Even Select Not state
+          <t>feature
+• select zone Exploration Mission displayed
+◦ Exploration Mission zone UI displayed , zone PCicon displayed UI select status
 • Exploration Mission
- ◦ CondScript's Entry Text
- ◦ Achieve Count / Achieve Required/Needed Count number Display
- ▪ List's Each also number Display
- ◦ Completeapplied Text Icon to Display
-• Reward List Icon : Reward Claim can present Icon
- ◦ Click when, Corresponding Reward Immediately Claim And Popup Show
- ◦ Icon Achieve Required/Needed Count Display
- ▪ HalfReward, FullReward Each Entered Quest Complete Required/Needed Count number to Display
- ◦ Reward List Icon 3 state 
- ▪ Reward Claim Possible : Click when, Reward Claim
- → Display : Color Icon And Icon red dot Display
- ▪ Already Reward Claim : Click when, tooltip Show
- → Display : Color Icon And Icon green V Display
- ▪ Reward Claim unavailable : Click when, tooltip Show
- → Display : Icon Greyscale
-</t>
+◦ CondScript 
+◦ achieve / achieve 
+▪ list 
+◦ complete icon 
+• reward list icon : reward icon
+◦ click , reward 
+◦ icon achieve displayed
+▪ HalfReward, FullReward enter complete displayed
+◦ reward list icon 3 status 
+▪ reward possible : click , reward 
+displayed : icon icon displayed
+▪ reward : click , 
+displayed : icon icon V displayed
+▪ reward not possible : click , 
+displayed : icon greyed out</t>
         </is>
       </c>
       <c r="K86" s="71" t="n"/>
@@ -5712,15 +5710,15 @@
       <c r="I88" s="76" t="n"/>
       <c r="J88" s="78" t="inlineStr">
         <is>
-          <t>- Function
-• Specific Area or World's MissionList Complete when, Immediately Popup Show
- ◦ Popup Display after, Day Time and after Automatic to types
- ◦ Corresponding Popup PC Field possible when only DisplayDone/Applied
- ▪ All Type's Indun, Week, Cutscene in DisplayNot done Not
- ▪ PC Field to return after, UI processing according to to Display
-- Display Text
-• : Exploration Mission Complete
-• : Quest_Adventure.xml's MissionList's TRName Display</t>
+          <t>- feature
+• zone MissionList complete , 
+◦ displayed , 
+◦ PC displayed
+▪ Indun, , cutscene displayed 
+▪ PC , UI displayed
+- displayed 
+• : Exploration Mission complete
+• : Quest_Adventure.xml MissionList TRName displayed</t>
         </is>
       </c>
       <c r="K88" s="71" t="n"/>
@@ -6523,7 +6521,6 @@
       <c r="AE109" s="25" t="n"/>
       <c r="AF109" s="25" t="n"/>
     </row>
-    <row r="110"/>
     <row r="111">
       <c r="B111" s="20" t="n"/>
       <c r="C111" s="21" t="inlineStr">
@@ -6561,7 +6558,6 @@
       <c r="AE111" s="20" t="n"/>
       <c r="AF111" s="20" t="n"/>
     </row>
-    <row r="112"/>
     <row r="113">
       <c r="C113" s="28" t="inlineStr">
         <is>
@@ -6569,23 +6565,6 @@
         </is>
       </c>
     </row>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
     <row r="131">
       <c r="B131" s="19" t="inlineStr">
         <is>
@@ -6826,7 +6805,7 @@
       <c r="D137" s="76" t="n"/>
       <c r="E137" s="57" t="inlineStr">
         <is>
-          <t>Achievement Category Categorize input. Corresponding MissionCategory.xml matchingbeing Achievement Category to CategorizeDone/Applied</t>
+          <t>enter. MissionCategory.xml</t>
         </is>
       </c>
       <c r="F137" s="71" t="n"/>
@@ -6865,8 +6844,8 @@
       <c r="D138" s="76" t="n"/>
       <c r="E138" s="57" t="inlineStr">
         <is>
-          <t>MissionList : Reward Grant UI Displaybeing applied column. Above's Mission CondQuest's Target to 
-Mission : Each MissionList's Exploration Mission Content</t>
+          <t>MissionList : reward UI displayed . Mission CondQuest 
+Mission : MissionList Exploration Mission</t>
         </is>
       </c>
       <c r="F138" s="71" t="n"/>
@@ -7110,7 +7089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I872"/>
+  <dimension ref="B2:I872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="36" min="1" max="3"/>
@@ -7118,7 +7097,6 @@
     <col width="9" customWidth="1" style="36" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="59" t="inlineStr">
         <is>
@@ -12033,7 +12011,7 @@
       </c>
       <c r="D272" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> My/The1 While/As </t>
+          <t>1</t>
         </is>
       </c>
       <c r="E272" s="58" t="n">
@@ -12225,7 +12203,7 @@
       </c>
       <c r="D283" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">My/The2 can also </t>
+          <t>2</t>
         </is>
       </c>
       <c r="E283" s="58" t="n">
@@ -12369,7 +12347,7 @@
       </c>
       <c r="D291" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> My/The2 While/As </t>
+          <t>2</t>
         </is>
       </c>
       <c r="E291" s="58" t="n">
@@ -12665,7 +12643,7 @@
       </c>
       <c r="D308" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">My/The3 can also </t>
+          <t>3</t>
         </is>
       </c>
       <c r="E308" s="58" t="n">
@@ -12777,7 +12755,7 @@
       </c>
       <c r="D314" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> My/The3 While/As </t>
+          <t>3</t>
         </is>
       </c>
       <c r="E314" s="58" t="n">
@@ -13233,7 +13211,7 @@
       </c>
       <c r="D339" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">My/The1 can also </t>
+          <t>1</t>
         </is>
       </c>
       <c r="E339" s="58" t="n">
@@ -13409,7 +13387,7 @@
       </c>
       <c r="D349" s="58" t="inlineStr">
         <is>
-          <t>My/The1 While/As during</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E349" s="58" t="n">
@@ -13929,7 +13907,7 @@
       </c>
       <c r="D377" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">My/The4 can also </t>
+          <t>4</t>
         </is>
       </c>
       <c r="E377" s="58" t="n">
@@ -14033,7 +14011,7 @@
       </c>
       <c r="D383" s="58" t="inlineStr">
         <is>
-          <t>My/The2 While/As during</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E383" s="58" t="n">
@@ -15865,7 +15843,7 @@
       </c>
       <c r="D483" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Week 's </t>
+          <t>Master's Quarters</t>
         </is>
       </c>
       <c r="E483" s="58" t="n">
@@ -17913,7 +17891,7 @@
       </c>
       <c r="D595" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">My/The1 Furnace </t>
+          <t>1</t>
         </is>
       </c>
       <c r="E595" s="58" t="n">
@@ -18321,7 +18299,7 @@
       </c>
       <c r="D618" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">My/The2 Furnace </t>
+          <t>2</t>
         </is>
       </c>
       <c r="E618" s="58" t="n">
@@ -18855,7 +18833,7 @@
       <c r="C648" s="58" t="n"/>
       <c r="D648" s="58" t="inlineStr">
         <is>
-          <t>Behind/After Defeat</t>
+          <t>defeat</t>
         </is>
       </c>
       <c r="E648" s="58" t="n">
@@ -19081,7 +19059,7 @@
       </c>
       <c r="D661" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">My/The3 Furnace </t>
+          <t>3</t>
         </is>
       </c>
       <c r="E661" s="58" t="n">
@@ -19185,7 +19163,7 @@
       </c>
       <c r="D667" s="58" t="inlineStr">
         <is>
-          <t>My/The1 My/The</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E667" s="58" t="n">
@@ -19657,7 +19635,7 @@
       </c>
       <c r="D693" s="58" t="inlineStr">
         <is>
-          <t>Furnace Week</t>
+          <t>Furnace Residential District</t>
         </is>
       </c>
       <c r="E693" s="58" t="n">

--- a/docs/ExplorationMissions_DesignDocument.xlsx
+++ b/docs/ExplorationMissions_DesignDocument.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -133,6 +133,15 @@
       <color theme="1"/>
       <sz val="8"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -714,7 +723,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -928,6 +937,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1782,21 +1824,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L42"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="4.375" customWidth="1" style="43" min="1" max="1"/>
-    <col width="9" customWidth="1" style="43" min="2" max="2"/>
-    <col width="11" customWidth="1" style="43" min="3" max="3"/>
-    <col width="9" customWidth="1" style="43" min="4" max="15"/>
+    <col width="8" customWidth="1" style="43" min="2" max="2"/>
+    <col width="12" customWidth="1" style="43" min="3" max="3"/>
+    <col width="75" customWidth="1" style="43" min="4" max="15"/>
+    <col width="18" customWidth="1" style="60" min="12" max="12"/>
     <col width="11.375" bestFit="1" customWidth="1" style="43" min="16" max="16"/>
     <col width="9" customWidth="1" style="43" min="17" max="16384"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Document History : Exploration Mission when </t>
+    <row r="1"/>
+    <row r="2" ht="22" customHeight="1" s="60">
+      <c r="B2" s="81" t="inlineStr">
+        <is>
+          <t>Document History : Exploration Missions</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -1810,10 +1854,22 @@
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
     </row>
-    <row r="3">
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+    <row r="3" ht="18" customHeight="1" s="60">
+      <c r="B3" s="82" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="C3" s="82" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D3" s="82" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
@@ -1821,453 +1877,343 @@
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="22.5" customHeight="1" s="60">
+      <c r="L3" s="82" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="60">
       <c r="A4" s="5" t="n"/>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="C4" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Date</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>Content</t>
-        </is>
-      </c>
-      <c r="E4" s="61" t="n"/>
-      <c r="F4" s="61" t="n"/>
-      <c r="G4" s="61" t="n"/>
-      <c r="H4" s="61" t="n"/>
-      <c r="I4" s="61" t="n"/>
-      <c r="J4" s="61" t="n"/>
-      <c r="K4" s="62" t="n"/>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" s="83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="84" t="inlineStr">
+        <is>
+          <t>24.04.26</t>
+        </is>
+      </c>
+      <c r="D4" s="84" t="inlineStr">
+        <is>
+          <t>Exploration mission list — initial draft</t>
+        </is>
+      </c>
+      <c r="L4" s="85" t="inlineStr">
+        <is>
+          <t>Juwon Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="60">
       <c r="A5" s="5" t="n"/>
-      <c r="B5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>24.04.26</t>
-        </is>
-      </c>
-      <c r="D5" s="63" t="inlineStr">
-        <is>
-          <t>Exploration Mission List Initial Draft</t>
-        </is>
-      </c>
-      <c r="E5" s="64" t="n"/>
-      <c r="F5" s="64" t="n"/>
-      <c r="G5" s="64" t="n"/>
-      <c r="H5" s="64" t="n"/>
-      <c r="I5" s="64" t="n"/>
-      <c r="J5" s="64" t="n"/>
-      <c r="K5" s="65" t="n"/>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" s="60">
+      <c r="B5" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="87" t="inlineStr">
+        <is>
+          <t>24.05.10</t>
+        </is>
+      </c>
+      <c r="D5" s="88" t="inlineStr">
+        <is>
+          <t>Exploration mission system — initial draft</t>
+        </is>
+      </c>
+      <c r="L5" s="89" t="inlineStr">
+        <is>
+          <t>Juwon Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="60">
       <c r="A6" s="5" t="n"/>
-      <c r="B6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>24.05.10</t>
-        </is>
-      </c>
-      <c r="D6" s="63" t="inlineStr">
-        <is>
-          <t>Exploration Mission when Initial Draft</t>
-        </is>
-      </c>
-      <c r="E6" s="64" t="n"/>
-      <c r="F6" s="64" t="n"/>
-      <c r="G6" s="64" t="n"/>
-      <c r="H6" s="64" t="n"/>
-      <c r="I6" s="64" t="n"/>
-      <c r="J6" s="64" t="n"/>
-      <c r="K6" s="65" t="n"/>
-      <c r="L6" s="13" t="inlineStr">
+      <c r="B6" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="87" t="inlineStr">
+        <is>
+          <t>24.05.21</t>
+        </is>
+      </c>
+      <c r="D6" s="88" t="inlineStr">
+        <is>
+          <t>Small Lake in the Garden, Aerial Cart Station, Garden's End — mission list updated</t>
+        </is>
+      </c>
+      <c r="L6" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="60">
+    <row r="7" ht="18" customHeight="1" s="60">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>24.05.21</t>
-        </is>
-      </c>
-      <c r="D7" s="63" t="inlineStr">
-        <is>
-          <t>Small Lake in the Garden, Aerial Cart Station, Garden's End Albin Soul Exploration Mission Remove</t>
-        </is>
-      </c>
-      <c r="E7" s="64" t="n"/>
-      <c r="F7" s="64" t="n"/>
-      <c r="G7" s="64" t="n"/>
-      <c r="H7" s="64" t="n"/>
-      <c r="I7" s="64" t="n"/>
-      <c r="J7" s="64" t="n"/>
-      <c r="K7" s="65" t="n"/>
-      <c r="L7" s="13" t="inlineStr">
+      <c r="B7" s="90" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="87" t="inlineStr">
+        <is>
+          <t>24.05.23</t>
+        </is>
+      </c>
+      <c r="D7" s="88" t="inlineStr">
+        <is>
+          <t>Where the Curtain Flutters — exploration mission list modified</t>
+        </is>
+      </c>
+      <c r="L7" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="60">
+    <row r="8" ht="18" customHeight="1" s="60">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>24.05.23</t>
-        </is>
-      </c>
-      <c r="D8" s="63" t="inlineStr">
-        <is>
-          <t>Where the Curtain Flutters's Exploration Mission List Modify (Dark Temple Unlock -&gt; Treasure Chest Obtain)</t>
-        </is>
-      </c>
-      <c r="E8" s="64" t="n"/>
-      <c r="F8" s="64" t="n"/>
-      <c r="G8" s="64" t="n"/>
-      <c r="H8" s="64" t="n"/>
-      <c r="I8" s="64" t="n"/>
-      <c r="J8" s="64" t="n"/>
-      <c r="K8" s="65" t="n"/>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="B8" s="90" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="87" t="inlineStr">
+        <is>
+          <t>24.07.24</t>
+        </is>
+      </c>
+      <c r="D8" s="88" t="inlineStr">
+        <is>
+          <t>Burning Furnace 001 (Burning Bridge) — Carlotta's Soul removed</t>
+        </is>
+      </c>
+      <c r="L8" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="60">
+    <row r="9" ht="18" customHeight="1" s="60">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>24.07.24</t>
-        </is>
-      </c>
-      <c r="D9" s="63" t="inlineStr">
-        <is>
-          <t>Burning Furnace 001(Burning Bridge)'s Carlotta Soul Remove</t>
-        </is>
-      </c>
-      <c r="E9" s="64" t="n"/>
-      <c r="F9" s="64" t="n"/>
-      <c r="G9" s="64" t="n"/>
-      <c r="H9" s="64" t="n"/>
-      <c r="I9" s="64" t="n"/>
-      <c r="J9" s="64" t="n"/>
-      <c r="K9" s="65" t="n"/>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="B9" s="90" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="87" t="inlineStr">
+        <is>
+          <t>24.08.21</t>
+        </is>
+      </c>
+      <c r="D9" s="88" t="inlineStr">
+        <is>
+          <t>Exploration mission list updated; format changed</t>
+        </is>
+      </c>
+      <c r="L9" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="60">
+    <row r="10" ht="18" customHeight="1" s="60">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>24.08.21</t>
-        </is>
-      </c>
-      <c r="D10" s="63" t="inlineStr">
-        <is>
-          <t>Exploration Mission List Updated And Format Change</t>
-        </is>
-      </c>
-      <c r="E10" s="64" t="n"/>
-      <c r="F10" s="64" t="n"/>
-      <c r="G10" s="64" t="n"/>
-      <c r="H10" s="64" t="n"/>
-      <c r="I10" s="64" t="n"/>
-      <c r="J10" s="64" t="n"/>
-      <c r="K10" s="65" t="n"/>
-      <c r="L10" s="13" t="inlineStr">
+      <c r="B10" s="90" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="87" t="inlineStr">
+        <is>
+          <t>24.08.28</t>
+        </is>
+      </c>
+      <c r="D10" s="88" t="inlineStr">
+        <is>
+          <t>Exploration mission list updated — Resurrection Stone ×1 added</t>
+        </is>
+      </c>
+      <c r="L10" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="60">
+    <row r="11" ht="18" customHeight="1" s="60">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="90" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>24.08.28</t>
-        </is>
-      </c>
-      <c r="D11" s="63" t="inlineStr">
-        <is>
-          <t>Exploration Mission List Updated - Resurrection Stone 1pieces to Unify, List's Reward And Mission Content Typo Modify</t>
-        </is>
-      </c>
-      <c r="E11" s="64" t="n"/>
-      <c r="F11" s="64" t="n"/>
-      <c r="G11" s="64" t="n"/>
-      <c r="H11" s="64" t="n"/>
-      <c r="I11" s="64" t="n"/>
-      <c r="J11" s="64" t="n"/>
-      <c r="K11" s="65" t="n"/>
-      <c r="L11" s="13" t="inlineStr">
+      <c r="C11" s="87" t="inlineStr">
+        <is>
+          <t>24.08.29</t>
+        </is>
+      </c>
+      <c r="D11" s="88" t="inlineStr">
+        <is>
+          <t>Exploration mission list — reward typo fixed</t>
+        </is>
+      </c>
+      <c r="L11" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="60">
+    <row r="12" ht="18" customHeight="1" s="60">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>24.08.29</t>
-        </is>
-      </c>
-      <c r="D12" s="63" t="inlineStr">
-        <is>
-          <t>Exploration Mission List Reward Typo Modify</t>
-        </is>
-      </c>
-      <c r="E12" s="64" t="n"/>
-      <c r="F12" s="64" t="n"/>
-      <c r="G12" s="64" t="n"/>
-      <c r="H12" s="64" t="n"/>
-      <c r="I12" s="64" t="n"/>
-      <c r="J12" s="64" t="n"/>
-      <c r="K12" s="65" t="n"/>
-      <c r="L12" s="13" t="inlineStr">
+      <c r="B12" s="90" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="87" t="inlineStr">
+        <is>
+          <t>24.09.05</t>
+        </is>
+      </c>
+      <c r="D12" s="88" t="inlineStr">
+        <is>
+          <t>Stamina Potion reward removed</t>
+        </is>
+      </c>
+      <c r="L12" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="60">
+    <row r="13" ht="18" customHeight="1" s="60">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>24.09.05</t>
-        </is>
-      </c>
-      <c r="D13" s="63" t="inlineStr">
-        <is>
-          <t>Stamina Potion Reward Remove</t>
-        </is>
-      </c>
-      <c r="E13" s="64" t="n"/>
-      <c r="F13" s="64" t="n"/>
-      <c r="G13" s="64" t="n"/>
-      <c r="H13" s="64" t="n"/>
-      <c r="I13" s="64" t="n"/>
-      <c r="J13" s="64" t="n"/>
-      <c r="K13" s="65" t="n"/>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="B13" s="90" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="87" t="inlineStr">
+        <is>
+          <t>24.11.25</t>
+        </is>
+      </c>
+      <c r="D13" s="88" t="inlineStr">
+        <is>
+          <t>Sage's Library exploration missions added</t>
+        </is>
+      </c>
+      <c r="L13" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="60">
+    <row r="14" ht="18" customHeight="1" s="60">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>24.11.25</t>
-        </is>
-      </c>
-      <c r="D14" s="63" t="inlineStr">
-        <is>
-          <t>Sage's Library Exploration Mission Add</t>
-        </is>
-      </c>
-      <c r="E14" s="64" t="n"/>
-      <c r="F14" s="64" t="n"/>
-      <c r="G14" s="64" t="n"/>
-      <c r="H14" s="64" t="n"/>
-      <c r="I14" s="64" t="n"/>
-      <c r="J14" s="64" t="n"/>
-      <c r="K14" s="65" t="n"/>
-      <c r="L14" s="13" t="inlineStr">
+      <c r="B14" s="90" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="87" t="inlineStr">
+        <is>
+          <t>24.12.09</t>
+        </is>
+      </c>
+      <c r="D14" s="88" t="inlineStr">
+        <is>
+          <t>Sage's Library exploration mission rewards specified</t>
+        </is>
+      </c>
+      <c r="L14" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="60">
+    <row r="15" ht="18" customHeight="1" s="60">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>24.12.09</t>
-        </is>
-      </c>
-      <c r="D15" s="63" t="inlineStr">
-        <is>
-          <t>Sage's Library Exploration Mission Reward Content Add</t>
-        </is>
-      </c>
-      <c r="E15" s="64" t="n"/>
-      <c r="F15" s="64" t="n"/>
-      <c r="G15" s="64" t="n"/>
-      <c r="H15" s="64" t="n"/>
-      <c r="I15" s="64" t="n"/>
-      <c r="J15" s="64" t="n"/>
-      <c r="K15" s="65" t="n"/>
-      <c r="L15" s="13" t="inlineStr">
+      <c r="B15" s="90" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="87" t="inlineStr">
+        <is>
+          <t>24.12.12</t>
+        </is>
+      </c>
+      <c r="D15" s="88" t="inlineStr">
+        <is>
+          <t>Will-o'-Wisp defeat mission removed</t>
+        </is>
+      </c>
+      <c r="L15" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="60">
+    <row r="16" ht="18" customHeight="1" s="60">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>24.12.12</t>
-        </is>
-      </c>
-      <c r="D16" s="63" t="inlineStr">
-        <is>
-          <t>Will-o'-Wisp Defeat Mission Remove</t>
-        </is>
-      </c>
-      <c r="E16" s="64" t="n"/>
-      <c r="F16" s="64" t="n"/>
-      <c r="G16" s="64" t="n"/>
-      <c r="H16" s="64" t="n"/>
-      <c r="I16" s="64" t="n"/>
-      <c r="J16" s="64" t="n"/>
-      <c r="K16" s="65" t="n"/>
-      <c r="L16" s="13" t="inlineStr">
+      <c r="B16" s="90" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" s="87" t="inlineStr">
+        <is>
+          <t>24.12.17</t>
+        </is>
+      </c>
+      <c r="D16" s="88" t="inlineStr">
+        <is>
+          <t>Difficult monster defeat exploration missions removed</t>
+        </is>
+      </c>
+      <c r="L16" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="60">
+    <row r="17" ht="18" customHeight="1" s="60">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>24.12.17</t>
-        </is>
-      </c>
-      <c r="D17" s="63" t="inlineStr">
-        <is>
-          <t>Achieve Difficult Monster Defeat Exploration Mission Remove</t>
-        </is>
-      </c>
-      <c r="E17" s="64" t="n"/>
-      <c r="F17" s="64" t="n"/>
-      <c r="G17" s="64" t="n"/>
-      <c r="H17" s="64" t="n"/>
-      <c r="I17" s="64" t="n"/>
-      <c r="J17" s="64" t="n"/>
-      <c r="K17" s="65" t="n"/>
-      <c r="L17" s="13" t="inlineStr">
+      <c r="B17" s="90" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="87" t="inlineStr">
+        <is>
+          <t>24.12.24</t>
+        </is>
+      </c>
+      <c r="D17" s="88" t="inlineStr">
+        <is>
+          <t>Completed reward areas greyed out in list</t>
+        </is>
+      </c>
+      <c r="L17" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1" s="60">
+    <row r="18" ht="18" customHeight="1" s="60">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>24.12.24</t>
-        </is>
-      </c>
-      <c r="D18" s="63" t="inlineStr">
-        <is>
-          <t>Reward Obtain Area List Greyscale processing</t>
-        </is>
-      </c>
-      <c r="E18" s="64" t="n"/>
-      <c r="F18" s="64" t="n"/>
-      <c r="G18" s="64" t="n"/>
-      <c r="H18" s="64" t="n"/>
-      <c r="I18" s="64" t="n"/>
-      <c r="J18" s="64" t="n"/>
-      <c r="K18" s="65" t="n"/>
-      <c r="L18" s="13" t="inlineStr">
+      <c r="B18" s="90" t="n">
+        <v>14</v>
+      </c>
+      <c r="C18" s="87" t="inlineStr">
+        <is>
+          <t>24.12.27</t>
+        </is>
+      </c>
+      <c r="D18" s="88" t="inlineStr">
+        <is>
+          <t>Reward list updated</t>
+        </is>
+      </c>
+      <c r="L18" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="60">
+    <row r="19" ht="18" customHeight="1" s="60">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>24.12.27</t>
-        </is>
-      </c>
-      <c r="D19" s="63" t="inlineStr">
-        <is>
-          <t>Reward List Updated</t>
-        </is>
-      </c>
-      <c r="E19" s="64" t="n"/>
-      <c r="F19" s="64" t="n"/>
-      <c r="G19" s="64" t="n"/>
-      <c r="H19" s="64" t="n"/>
-      <c r="I19" s="64" t="n"/>
-      <c r="J19" s="64" t="n"/>
-      <c r="K19" s="65" t="n"/>
-      <c r="L19" s="13" t="inlineStr">
+      <c r="B19" s="90" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" s="87" t="inlineStr">
+        <is>
+          <t>25.01.14</t>
+        </is>
+      </c>
+      <c r="D19" s="88" t="inlineStr">
+        <is>
+          <t>Spring Waterway rewards modified</t>
+        </is>
+      </c>
+      <c r="L19" s="91" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
@@ -2275,380 +2221,94 @@
     </row>
     <row r="20" ht="15.75" customHeight="1" s="60">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>25.01.14</t>
-        </is>
-      </c>
-      <c r="D20" s="63" t="inlineStr">
-        <is>
-          <t>Spring Waterway Reward Modify</t>
-        </is>
-      </c>
-      <c r="E20" s="64" t="n"/>
-      <c r="F20" s="64" t="n"/>
-      <c r="G20" s="64" t="n"/>
-      <c r="H20" s="64" t="n"/>
-      <c r="I20" s="64" t="n"/>
-      <c r="J20" s="64" t="n"/>
-      <c r="K20" s="65" t="n"/>
-      <c r="L20" s="13" t="inlineStr">
-        <is>
-          <t>Juwon Lee</t>
-        </is>
-      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="63" t="n"/>
+      <c r="L20" s="13" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="60">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>25.01.14</t>
-        </is>
-      </c>
-      <c r="D21" s="63" t="inlineStr">
-        <is>
-          <t>Haven of Knowledge Exploration Mission Typo Modify</t>
-        </is>
-      </c>
-      <c r="E21" s="64" t="n"/>
-      <c r="F21" s="64" t="n"/>
-      <c r="G21" s="64" t="n"/>
-      <c r="H21" s="64" t="n"/>
-      <c r="I21" s="64" t="n"/>
-      <c r="J21" s="64" t="n"/>
-      <c r="K21" s="65" t="n"/>
-      <c r="L21" s="13" t="inlineStr">
-        <is>
-          <t>Juwon Lee</t>
-        </is>
-      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="63" t="n"/>
+      <c r="L21" s="13" t="n"/>
     </row>
     <row r="22" ht="13.5" customHeight="1" s="60">
-      <c r="B22" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>25.03.05</t>
-        </is>
-      </c>
-      <c r="D22" s="63" t="inlineStr">
-        <is>
-          <t>Crystal -&gt; Shining Modify Text Change</t>
-        </is>
-      </c>
-      <c r="E22" s="64" t="n"/>
-      <c r="F22" s="64" t="n"/>
-      <c r="G22" s="64" t="n"/>
-      <c r="H22" s="64" t="n"/>
-      <c r="I22" s="64" t="n"/>
-      <c r="J22" s="64" t="n"/>
-      <c r="K22" s="65" t="n"/>
-      <c r="L22" s="13" t="inlineStr">
-        <is>
-          <t>Juwon Lee</t>
-        </is>
-      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="63" t="n"/>
+      <c r="L22" s="13" t="n"/>
     </row>
     <row r="23" ht="13.5" customHeight="1" s="60">
-      <c r="B23" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>25.03.31</t>
-        </is>
-      </c>
-      <c r="D23" s="63" t="inlineStr">
-        <is>
-          <t>21007's Debris Dwarf Defeat -&gt; Shrine Dwarf Defeat to Condition Change</t>
-        </is>
-      </c>
-      <c r="E23" s="64" t="n"/>
-      <c r="F23" s="64" t="n"/>
-      <c r="G23" s="64" t="n"/>
-      <c r="H23" s="64" t="n"/>
-      <c r="I23" s="64" t="n"/>
-      <c r="J23" s="64" t="n"/>
-      <c r="K23" s="65" t="n"/>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>Juwon Lee</t>
-        </is>
-      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="63" t="n"/>
+      <c r="L23" s="13" t="n"/>
     </row>
     <row r="24" ht="13.5" customHeight="1" s="60">
-      <c r="B24" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>25.05.14</t>
-        </is>
-      </c>
-      <c r="D24" s="63" t="inlineStr">
-        <is>
-          <t>Salt Mine, Silak's Mansion Hunting Ground's Exploration Mission Change</t>
-        </is>
-      </c>
-      <c r="E24" s="64" t="n"/>
-      <c r="F24" s="64" t="n"/>
-      <c r="G24" s="64" t="n"/>
-      <c r="H24" s="64" t="n"/>
-      <c r="I24" s="64" t="n"/>
-      <c r="J24" s="64" t="n"/>
-      <c r="K24" s="65" t="n"/>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>Juwon Lee</t>
-        </is>
-      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="63" t="n"/>
+      <c r="L24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>25.06.09</t>
-        </is>
-      </c>
-      <c r="D25" s="66" t="inlineStr">
-        <is>
-          <t>Knight's Garden, Salt Mine, Silak's Mansion Exploration Mission List Updated</t>
-        </is>
-      </c>
-      <c r="E25" s="67" t="n"/>
-      <c r="F25" s="67" t="n"/>
-      <c r="G25" s="67" t="n"/>
-      <c r="H25" s="67" t="n"/>
-      <c r="I25" s="67" t="n"/>
-      <c r="J25" s="67" t="n"/>
-      <c r="K25" s="68" t="n"/>
-      <c r="L25" s="34" t="inlineStr">
-        <is>
-          <t>Juwon Lee</t>
-        </is>
-      </c>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="33" t="n"/>
+      <c r="D25" s="66" t="n"/>
+      <c r="L25" s="34" t="n"/>
     </row>
     <row r="26">
       <c r="D26" s="43" t="n"/>
-      <c r="E26" s="69" t="n"/>
-      <c r="F26" s="69" t="n"/>
-      <c r="G26" s="69" t="n"/>
-      <c r="H26" s="69" t="n"/>
-      <c r="I26" s="69" t="n"/>
-      <c r="J26" s="69" t="n"/>
-      <c r="K26" s="70" t="n"/>
     </row>
     <row r="27">
       <c r="D27" s="43" t="n"/>
-      <c r="E27" s="69" t="n"/>
-      <c r="F27" s="69" t="n"/>
-      <c r="G27" s="69" t="n"/>
-      <c r="H27" s="69" t="n"/>
-      <c r="I27" s="69" t="n"/>
-      <c r="J27" s="69" t="n"/>
-      <c r="K27" s="70" t="n"/>
     </row>
     <row r="28">
       <c r="D28" s="43" t="n"/>
-      <c r="E28" s="69" t="n"/>
-      <c r="F28" s="69" t="n"/>
-      <c r="G28" s="69" t="n"/>
-      <c r="H28" s="69" t="n"/>
-      <c r="I28" s="69" t="n"/>
-      <c r="J28" s="69" t="n"/>
-      <c r="K28" s="70" t="n"/>
     </row>
     <row r="29">
       <c r="D29" s="43" t="n"/>
-      <c r="E29" s="69" t="n"/>
-      <c r="F29" s="69" t="n"/>
-      <c r="G29" s="69" t="n"/>
-      <c r="H29" s="69" t="n"/>
-      <c r="I29" s="69" t="n"/>
-      <c r="J29" s="69" t="n"/>
-      <c r="K29" s="70" t="n"/>
     </row>
     <row r="30">
       <c r="D30" s="43" t="n"/>
-      <c r="E30" s="69" t="n"/>
-      <c r="F30" s="69" t="n"/>
-      <c r="G30" s="69" t="n"/>
-      <c r="H30" s="69" t="n"/>
-      <c r="I30" s="69" t="n"/>
-      <c r="J30" s="69" t="n"/>
-      <c r="K30" s="70" t="n"/>
     </row>
     <row r="31">
       <c r="D31" s="43" t="n"/>
-      <c r="E31" s="69" t="n"/>
-      <c r="F31" s="69" t="n"/>
-      <c r="G31" s="69" t="n"/>
-      <c r="H31" s="69" t="n"/>
-      <c r="I31" s="69" t="n"/>
-      <c r="J31" s="69" t="n"/>
-      <c r="K31" s="70" t="n"/>
     </row>
     <row r="32">
       <c r="D32" s="43" t="n"/>
-      <c r="E32" s="69" t="n"/>
-      <c r="F32" s="69" t="n"/>
-      <c r="G32" s="69" t="n"/>
-      <c r="H32" s="69" t="n"/>
-      <c r="I32" s="69" t="n"/>
-      <c r="J32" s="69" t="n"/>
-      <c r="K32" s="70" t="n"/>
     </row>
     <row r="33">
       <c r="D33" s="43" t="n"/>
-      <c r="E33" s="69" t="n"/>
-      <c r="F33" s="69" t="n"/>
-      <c r="G33" s="69" t="n"/>
-      <c r="H33" s="69" t="n"/>
-      <c r="I33" s="69" t="n"/>
-      <c r="J33" s="69" t="n"/>
-      <c r="K33" s="70" t="n"/>
     </row>
     <row r="34">
       <c r="D34" s="43" t="n"/>
-      <c r="E34" s="69" t="n"/>
-      <c r="F34" s="69" t="n"/>
-      <c r="G34" s="69" t="n"/>
-      <c r="H34" s="69" t="n"/>
-      <c r="I34" s="69" t="n"/>
-      <c r="J34" s="69" t="n"/>
-      <c r="K34" s="70" t="n"/>
     </row>
     <row r="35">
       <c r="D35" s="43" t="n"/>
-      <c r="E35" s="69" t="n"/>
-      <c r="F35" s="69" t="n"/>
-      <c r="G35" s="69" t="n"/>
-      <c r="H35" s="69" t="n"/>
-      <c r="I35" s="69" t="n"/>
-      <c r="J35" s="69" t="n"/>
-      <c r="K35" s="70" t="n"/>
     </row>
     <row r="36">
       <c r="D36" s="43" t="n"/>
-      <c r="E36" s="69" t="n"/>
-      <c r="F36" s="69" t="n"/>
-      <c r="G36" s="69" t="n"/>
-      <c r="H36" s="69" t="n"/>
-      <c r="I36" s="69" t="n"/>
-      <c r="J36" s="69" t="n"/>
-      <c r="K36" s="70" t="n"/>
     </row>
     <row r="37">
       <c r="D37" s="43" t="n"/>
-      <c r="E37" s="69" t="n"/>
-      <c r="F37" s="69" t="n"/>
-      <c r="G37" s="69" t="n"/>
-      <c r="H37" s="69" t="n"/>
-      <c r="I37" s="69" t="n"/>
-      <c r="J37" s="69" t="n"/>
-      <c r="K37" s="70" t="n"/>
     </row>
     <row r="38">
       <c r="D38" s="43" t="n"/>
-      <c r="E38" s="69" t="n"/>
-      <c r="F38" s="69" t="n"/>
-      <c r="G38" s="69" t="n"/>
-      <c r="H38" s="69" t="n"/>
-      <c r="I38" s="69" t="n"/>
-      <c r="J38" s="69" t="n"/>
-      <c r="K38" s="70" t="n"/>
     </row>
     <row r="39">
       <c r="D39" s="43" t="n"/>
-      <c r="E39" s="69" t="n"/>
-      <c r="F39" s="69" t="n"/>
-      <c r="G39" s="69" t="n"/>
-      <c r="H39" s="69" t="n"/>
-      <c r="I39" s="69" t="n"/>
-      <c r="J39" s="69" t="n"/>
-      <c r="K39" s="70" t="n"/>
     </row>
     <row r="40">
       <c r="D40" s="43" t="n"/>
-      <c r="E40" s="69" t="n"/>
-      <c r="F40" s="69" t="n"/>
-      <c r="G40" s="69" t="n"/>
-      <c r="H40" s="69" t="n"/>
-      <c r="I40" s="69" t="n"/>
-      <c r="J40" s="69" t="n"/>
-      <c r="K40" s="70" t="n"/>
     </row>
     <row r="41">
       <c r="D41" s="43" t="n"/>
-      <c r="E41" s="69" t="n"/>
-      <c r="F41" s="69" t="n"/>
-      <c r="G41" s="69" t="n"/>
-      <c r="H41" s="69" t="n"/>
-      <c r="I41" s="69" t="n"/>
-      <c r="J41" s="69" t="n"/>
-      <c r="K41" s="70" t="n"/>
     </row>
     <row r="42">
       <c r="D42" s="43" t="n"/>
-      <c r="E42" s="69" t="n"/>
-      <c r="F42" s="69" t="n"/>
-      <c r="G42" s="69" t="n"/>
-      <c r="H42" s="69" t="n"/>
-      <c r="I42" s="69" t="n"/>
-      <c r="J42" s="69" t="n"/>
-      <c r="K42" s="70" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="D26:K26"/>
-    <mergeCell ref="D20:K20"/>
-    <mergeCell ref="D19:K19"/>
-    <mergeCell ref="D34:K34"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="D22:K22"/>
-    <mergeCell ref="D31:K31"/>
-    <mergeCell ref="D40:K40"/>
-    <mergeCell ref="D36:K36"/>
-    <mergeCell ref="D21:K21"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="D13:K13"/>
-    <mergeCell ref="D27:K27"/>
-    <mergeCell ref="D41:K41"/>
-    <mergeCell ref="D32:K32"/>
-    <mergeCell ref="D17:K17"/>
-    <mergeCell ref="D7:K7"/>
-    <mergeCell ref="D16:K16"/>
-    <mergeCell ref="D28:K28"/>
-    <mergeCell ref="D37:K37"/>
-    <mergeCell ref="D4:K4"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="D18:K18"/>
-    <mergeCell ref="D9:K9"/>
-    <mergeCell ref="D39:K39"/>
-    <mergeCell ref="D25:K25"/>
-    <mergeCell ref="D30:K30"/>
-    <mergeCell ref="D15:K15"/>
-    <mergeCell ref="D33:K33"/>
-    <mergeCell ref="D8:K8"/>
-    <mergeCell ref="D24:K24"/>
-    <mergeCell ref="D42:K42"/>
-    <mergeCell ref="D38:K38"/>
-    <mergeCell ref="D14:K14"/>
-    <mergeCell ref="D29:K29"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D23:K23"/>
-    <mergeCell ref="D35:K35"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
@@ -2660,7 +2320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AF142"/>
+  <dimension ref="A1:AF142"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.625" defaultRowHeight="13.5"/>
   <cols>
     <col width="2.625" customWidth="1" style="15" min="1" max="1"/>
@@ -5344,19 +5004,7 @@
       <c r="I81" s="76" t="n"/>
       <c r="J81" s="78" t="inlineStr">
         <is>
-          <t>displayed : 
-feature
-• composition 
-• MissionCategory.xml ID 
-◦ Quest_Adventure.xml MissionCategoryID enter
-• click 
-◦ arrow status click , zone zone Exploration Mission . 
-arrow 
-◦ arrow status click , zone Exploration Mission list .
-arrow 
-• possible reward zone displayed
-◦ list list displayed
-• possible</t>
+          <t>displayed : feature • composition • MissionCategory.xml ID ◦ Quest_Adventure.xml MissionCategoryID enter • click ◦ arrow status click , zone Exploration Mission . arrow ◦ arrow status click , zone Exploration Mission list . arrow • possible reward zone displayed ◦ list displayed • possible</t>
         </is>
       </c>
       <c r="K81" s="71" t="n"/>
@@ -5399,28 +5047,7 @@
       <c r="I82" s="76" t="n"/>
       <c r="J82" s="78" t="inlineStr">
         <is>
-          <t>displayed
-• list : 
-• list : zone 
-• zone/ : ?????? list greyed out
-displayed icon
-• PC zone list displayed
-feature
-• click 
-◦ UI displayed
-▪ move move
-◦ Exploration Mission UI displayed
-◦ zone click 
-◦ select list highlight 
-• displayed
-◦ zone list 
-◦ zone list Quest_Adventure.xml ID 
-▪ Quest_Adventure.xml - RegionName 
-• achieve X/Y displayed
-◦ X : achieve Mission / Y : Mission 
-• zone TRName displayed
-• possible
-• reward obtain zone greyed out</t>
+          <t>displayed • list : • list : zone • zone/ : [data pending] list greyed out displayed icon • PC zone list displayed feature • click ◦ UI displayed ▪ move ◦ Exploration Mission UI displayed ◦ zone click ◦ select list highlight • displayed ◦ zone list ◦ zone list Quest_Adventure.xml ID ▪ Quest_Adventure.xml - RegionName • achieve X/Y displayed ◦ X : achieve Mission / Y : Mission • zone TRName displayed • possible • reward obtain zone greyed out</t>
         </is>
       </c>
       <c r="K82" s="71" t="n"/>
@@ -5463,15 +5090,7 @@
       <c r="I83" s="76" t="n"/>
       <c r="J83" s="78" t="inlineStr">
         <is>
-          <t>Display Image : Exploration Mission List in in Selectapplied Area(World) Image
-Function
-Map&amp; designed Apply Standard and Same Standard to Each Info Display
-• Map Image Display Area in Each Area's Zoom In, Zoom Outbeing 
-• Pinch to Zoom In Zoom Out Possible
- ◦ Zoom In Zoom Out according to Zoom In Zoom Out as follows 
-• World connectNot done Not Area's Image Display
-• Him Corresponding User's Achieve also and Display
- ◦ Achieve also Each in Location Display</t>
+          <t>Display Image : Exploration Mission List in Selectapplied Area(World) Image Function Map&amp; designed Apply Standard and Same Standard to Each Info Display • Map Image Display Area in Each Area's Zoom In, Zoom Outbeing • Pinch to Zoom In Zoom Out Possible ◦ Zoom In Zoom Out according to Zoom In Zoom Out as follows • World connectNot done Not Area's Image Display • Him Corresponding User's Achieve also and Display ◦ Achieve also Each in Location Display</t>
         </is>
       </c>
       <c r="K83" s="71" t="n"/>
@@ -5604,25 +5223,7 @@
       <c r="I86" s="76" t="n"/>
       <c r="J86" s="78" t="inlineStr">
         <is>
-          <t>feature
-• select zone Exploration Mission displayed
-◦ Exploration Mission zone UI displayed , zone PCicon displayed UI select status
-• Exploration Mission
-◦ CondScript 
-◦ achieve / achieve 
-▪ list 
-◦ complete icon 
-• reward list icon : reward icon
-◦ click , reward 
-◦ icon achieve displayed
-▪ HalfReward, FullReward enter complete displayed
-◦ reward list icon 3 status 
-▪ reward possible : click , reward 
-displayed : icon icon displayed
-▪ reward : click , 
-displayed : icon icon V displayed
-▪ reward not possible : click , 
-displayed : icon greyed out</t>
+          <t>feature • select zone Exploration Mission displayed ◦ Exploration Mission zone UI displayed , zone PCicon displayed UI select status • Exploration Mission ◦ CondScript ◦ achieve / achieve ▪ list ◦ complete icon • reward list icon : reward icon ◦ click , reward ◦ icon achieve displayed ▪ HalfReward, FullReward enter complete displayed ◦ reward list icon 3 status ▪ reward possible : click , reward displayed : icon displayed ▪ reward : click , displayed : icon V displayed ▪ reward not possible : click , displayed : icon greyed out</t>
         </is>
       </c>
       <c r="K86" s="71" t="n"/>
@@ -6521,7 +6122,8 @@
       <c r="AE109" s="25" t="n"/>
       <c r="AF109" s="25" t="n"/>
     </row>
-    <row r="111">
+    <row r="110" s="60"/>
+    <row r="111" s="60">
       <c r="B111" s="20" t="n"/>
       <c r="C111" s="21" t="inlineStr">
         <is>
@@ -6558,14 +6160,32 @@
       <c r="AE111" s="20" t="n"/>
       <c r="AF111" s="20" t="n"/>
     </row>
-    <row r="113">
+    <row r="112" s="60"/>
+    <row r="113" s="60">
       <c r="C113" s="28" t="inlineStr">
         <is>
           <t>○ Quest_Adventure.xml</t>
         </is>
       </c>
     </row>
-    <row r="131">
+    <row r="114" s="60"/>
+    <row r="115" s="60"/>
+    <row r="116" s="60"/>
+    <row r="117" s="60"/>
+    <row r="118" s="60"/>
+    <row r="119" s="60"/>
+    <row r="120" s="60"/>
+    <row r="121" s="60"/>
+    <row r="122" s="60"/>
+    <row r="123" s="60"/>
+    <row r="124" s="60"/>
+    <row r="125" s="60"/>
+    <row r="126" s="60"/>
+    <row r="127" s="60"/>
+    <row r="128" s="60"/>
+    <row r="129" s="60"/>
+    <row r="130" s="60"/>
+    <row r="131" s="60">
       <c r="B131" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">○ Quest's Data Structure </t>
@@ -6600,7 +6220,7 @@
       <c r="AC131" s="24" t="n"/>
       <c r="AD131" s="24" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" s="60">
       <c r="B132" s="47" t="inlineStr">
         <is>
           <t>Name</t>
@@ -6639,7 +6259,7 @@
       <c r="AC132" s="73" t="n"/>
       <c r="AD132" s="74" t="n"/>
     </row>
-    <row r="133">
+    <row r="133" s="60">
       <c r="B133" s="75" t="inlineStr">
         <is>
           <t>ID</t>
@@ -6678,7 +6298,7 @@
       <c r="AC133" s="71" t="n"/>
       <c r="AD133" s="76" t="n"/>
     </row>
-    <row r="134">
+    <row r="134" s="60">
       <c r="B134" s="75" t="inlineStr">
         <is>
           <t>TRName</t>
@@ -6717,7 +6337,7 @@
       <c r="AC134" s="71" t="n"/>
       <c r="AD134" s="76" t="n"/>
     </row>
-    <row r="135">
+    <row r="135" s="60">
       <c r="B135" s="75" t="inlineStr">
         <is>
           <t>QuestObjective</t>
@@ -6795,7 +6415,7 @@
       <c r="AC136" s="71" t="n"/>
       <c r="AD136" s="76" t="n"/>
     </row>
-    <row r="137">
+    <row r="137" s="60">
       <c r="B137" s="75" t="inlineStr">
         <is>
           <t>MissionCategory</t>
@@ -6914,7 +6534,7 @@
       <c r="AC139" s="71" t="n"/>
       <c r="AD139" s="76" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" s="60">
       <c r="B140" s="75" t="inlineStr">
         <is>
           <t>CondScript</t>
@@ -7089,7 +6709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I872"/>
+  <dimension ref="A1:I872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="36" min="1" max="3"/>
@@ -7097,14 +6717,15 @@
     <col width="9" customWidth="1" style="36" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="1" s="60"/>
+    <row r="2" s="60">
       <c r="B2" s="59" t="inlineStr">
         <is>
           <t>Exploration Mission List</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" s="60">
       <c r="B3" s="59" t="n"/>
       <c r="C3" s="59" t="n"/>
       <c r="D3" s="59" t="n"/>
@@ -7114,7 +6735,7 @@
       <c r="H3" s="59" t="n"/>
       <c r="I3" s="59" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" s="60">
       <c r="B4" s="35" t="inlineStr">
         <is>
           <t>World</t>
@@ -7148,7 +6769,7 @@
       </c>
       <c r="I4" s="35" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" s="60">
       <c r="B5" s="58" t="inlineStr">
         <is>
           <t>Knight's Garden</t>
@@ -7180,7 +6801,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" s="60">
       <c r="B6" s="79" t="n"/>
       <c r="C6" s="58" t="n"/>
       <c r="D6" s="58" t="inlineStr">
@@ -7196,7 +6817,7 @@
       <c r="H6" s="58" t="n"/>
       <c r="I6" s="58" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" s="60">
       <c r="B7" s="79" t="n"/>
       <c r="C7" s="58" t="n"/>
       <c r="D7" s="58" t="inlineStr">
@@ -7212,7 +6833,7 @@
       <c r="H7" s="58" t="n"/>
       <c r="I7" s="58" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" s="60">
       <c r="B8" s="79" t="n"/>
       <c r="C8" s="58" t="n"/>
       <c r="D8" s="58" t="inlineStr">
@@ -7228,7 +6849,7 @@
       <c r="H8" s="58" t="n"/>
       <c r="I8" s="58" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" s="60">
       <c r="B9" s="79" t="n"/>
       <c r="C9" s="58" t="n"/>
       <c r="D9" s="58" t="inlineStr">
@@ -7244,7 +6865,7 @@
       <c r="H9" s="58" t="n"/>
       <c r="I9" s="58" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" s="60">
       <c r="B10" s="79" t="n"/>
       <c r="C10" s="58" t="n"/>
       <c r="D10" s="58" t="inlineStr">
@@ -7260,7 +6881,7 @@
       <c r="H10" s="58" t="n"/>
       <c r="I10" s="58" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" s="60">
       <c r="B11" s="79" t="n"/>
       <c r="C11" s="58" t="n"/>
       <c r="D11" s="58" t="inlineStr">
@@ -7276,7 +6897,7 @@
       <c r="H11" s="58" t="n"/>
       <c r="I11" s="58" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" s="60">
       <c r="B12" s="79" t="n"/>
       <c r="C12" s="58" t="n">
         <v>21000</v>
@@ -7300,7 +6921,7 @@
       <c r="H12" s="58" t="n"/>
       <c r="I12" s="58" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" s="60">
       <c r="B13" s="79" t="n"/>
       <c r="C13" s="58" t="n"/>
       <c r="D13" s="58" t="inlineStr">
@@ -7316,7 +6937,7 @@
       <c r="H13" s="58" t="n"/>
       <c r="I13" s="58" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" s="60">
       <c r="B14" s="79" t="n"/>
       <c r="C14" s="58" t="n">
         <v>21002</v>
@@ -7340,7 +6961,7 @@
       <c r="H14" s="58" t="n"/>
       <c r="I14" s="58" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" s="60">
       <c r="B15" s="79" t="n"/>
       <c r="C15" s="58" t="n"/>
       <c r="D15" s="58" t="inlineStr">
@@ -7356,7 +6977,7 @@
       <c r="H15" s="58" t="n"/>
       <c r="I15" s="58" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" s="60">
       <c r="B16" s="79" t="n"/>
       <c r="C16" s="58" t="n"/>
       <c r="D16" s="58" t="inlineStr">
@@ -7372,7 +6993,7 @@
       <c r="H16" s="58" t="n"/>
       <c r="I16" s="58" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" s="60">
       <c r="B17" s="79" t="n"/>
       <c r="C17" s="58" t="n">
         <v>21003</v>
@@ -7396,7 +7017,7 @@
       <c r="H17" s="58" t="n"/>
       <c r="I17" s="58" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" s="60">
       <c r="B18" s="79" t="n"/>
       <c r="C18" s="58" t="n"/>
       <c r="D18" s="58" t="inlineStr">
@@ -7412,7 +7033,7 @@
       <c r="H18" s="58" t="n"/>
       <c r="I18" s="58" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" s="60">
       <c r="B19" s="79" t="n"/>
       <c r="C19" s="58" t="n"/>
       <c r="D19" s="58" t="inlineStr">
@@ -7428,7 +7049,7 @@
       <c r="H19" s="58" t="n"/>
       <c r="I19" s="58" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" s="60">
       <c r="B20" s="79" t="n"/>
       <c r="C20" s="58" t="n"/>
       <c r="D20" s="58" t="inlineStr">
@@ -7444,7 +7065,7 @@
       <c r="H20" s="58" t="n"/>
       <c r="I20" s="58" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" s="60">
       <c r="B21" s="79" t="n"/>
       <c r="C21" s="58" t="n">
         <v>21004</v>
@@ -7468,7 +7089,7 @@
       <c r="H21" s="58" t="n"/>
       <c r="I21" s="58" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" s="60">
       <c r="B22" s="79" t="n"/>
       <c r="C22" s="58" t="n"/>
       <c r="D22" s="58" t="inlineStr">
@@ -7484,7 +7105,7 @@
       <c r="H22" s="58" t="n"/>
       <c r="I22" s="58" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" s="60">
       <c r="B23" s="79" t="n"/>
       <c r="C23" s="58" t="n"/>
       <c r="D23" s="58" t="inlineStr">
@@ -7500,7 +7121,7 @@
       <c r="H23" s="58" t="n"/>
       <c r="I23" s="58" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" s="60">
       <c r="B24" s="79" t="n"/>
       <c r="C24" s="58" t="n"/>
       <c r="D24" s="58" t="inlineStr">
@@ -7516,7 +7137,7 @@
       <c r="H24" s="58" t="n"/>
       <c r="I24" s="58" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" s="60">
       <c r="B25" s="79" t="n"/>
       <c r="C25" s="58" t="n"/>
       <c r="D25" s="58" t="inlineStr">
@@ -7532,7 +7153,7 @@
       <c r="H25" s="58" t="n"/>
       <c r="I25" s="58" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" s="60">
       <c r="B26" s="79" t="n"/>
       <c r="C26" s="58" t="n"/>
       <c r="D26" s="58" t="inlineStr">
@@ -7548,7 +7169,7 @@
       <c r="H26" s="58" t="n"/>
       <c r="I26" s="58" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" s="60">
       <c r="B27" s="79" t="n"/>
       <c r="C27" s="58" t="n">
         <v>21012</v>
@@ -7572,7 +7193,7 @@
       <c r="H27" s="58" t="n"/>
       <c r="I27" s="58" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" s="60">
       <c r="B28" s="79" t="n"/>
       <c r="C28" s="58" t="n"/>
       <c r="D28" s="58" t="inlineStr">
@@ -7588,7 +7209,7 @@
       <c r="H28" s="58" t="n"/>
       <c r="I28" s="58" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" s="60">
       <c r="B29" s="79" t="n"/>
       <c r="C29" s="58" t="n"/>
       <c r="D29" s="58" t="inlineStr">
@@ -7604,7 +7225,7 @@
       <c r="H29" s="58" t="n"/>
       <c r="I29" s="58" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" s="60">
       <c r="B30" s="79" t="n"/>
       <c r="C30" s="58" t="n">
         <v>21013</v>
@@ -7628,7 +7249,7 @@
       <c r="H30" s="58" t="n"/>
       <c r="I30" s="58" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" s="60">
       <c r="B31" s="79" t="n"/>
       <c r="C31" s="58" t="n"/>
       <c r="D31" s="58" t="inlineStr">
@@ -7644,7 +7265,7 @@
       <c r="H31" s="58" t="n"/>
       <c r="I31" s="58" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" s="60">
       <c r="B32" s="79" t="n"/>
       <c r="C32" s="58" t="n">
         <v>21008</v>
@@ -7668,7 +7289,7 @@
       <c r="H32" s="58" t="n"/>
       <c r="I32" s="58" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" s="60">
       <c r="B33" s="79" t="n"/>
       <c r="C33" s="58" t="n"/>
       <c r="D33" s="58" t="inlineStr">
@@ -7684,7 +7305,7 @@
       <c r="H33" s="58" t="n"/>
       <c r="I33" s="58" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" s="60">
       <c r="B34" s="79" t="n"/>
       <c r="C34" s="58" t="n"/>
       <c r="D34" s="58" t="inlineStr">
@@ -7700,7 +7321,7 @@
       <c r="H34" s="58" t="n"/>
       <c r="I34" s="58" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" s="60">
       <c r="B35" s="79" t="n"/>
       <c r="C35" s="58" t="n">
         <v>21005</v>
@@ -7724,7 +7345,7 @@
       <c r="H35" s="58" t="n"/>
       <c r="I35" s="58" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" s="60">
       <c r="B36" s="79" t="n"/>
       <c r="C36" s="58" t="n"/>
       <c r="D36" s="58" t="inlineStr">
@@ -7740,7 +7361,7 @@
       <c r="H36" s="58" t="n"/>
       <c r="I36" s="58" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" s="60">
       <c r="B37" s="79" t="n"/>
       <c r="C37" s="58" t="n"/>
       <c r="D37" s="58" t="inlineStr">
@@ -7756,7 +7377,7 @@
       <c r="H37" s="58" t="n"/>
       <c r="I37" s="58" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" s="60">
       <c r="B38" s="79" t="n"/>
       <c r="C38" s="58" t="n">
         <v>21006</v>
@@ -7780,7 +7401,7 @@
       <c r="H38" s="58" t="n"/>
       <c r="I38" s="58" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" s="60">
       <c r="B39" s="79" t="n"/>
       <c r="C39" s="58" t="n"/>
       <c r="D39" s="58" t="inlineStr">
@@ -7796,7 +7417,7 @@
       <c r="H39" s="58" t="n"/>
       <c r="I39" s="58" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" s="60">
       <c r="B40" s="79" t="n"/>
       <c r="C40" s="58" t="n"/>
       <c r="D40" s="58" t="inlineStr">
@@ -7812,7 +7433,7 @@
       <c r="H40" s="58" t="n"/>
       <c r="I40" s="58" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" s="60">
       <c r="B41" s="79" t="n"/>
       <c r="C41" s="58" t="n"/>
       <c r="D41" s="58" t="inlineStr">
@@ -7828,7 +7449,7 @@
       <c r="H41" s="58" t="n"/>
       <c r="I41" s="58" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" s="60">
       <c r="B42" s="79" t="n"/>
       <c r="C42" s="58" t="n"/>
       <c r="D42" s="58" t="inlineStr">
@@ -7844,7 +7465,7 @@
       <c r="H42" s="58" t="n"/>
       <c r="I42" s="58" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" s="60">
       <c r="B43" s="79" t="n"/>
       <c r="C43" s="58" t="n">
         <v>21007</v>
@@ -7868,7 +7489,7 @@
       <c r="H43" s="58" t="n"/>
       <c r="I43" s="58" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" s="60">
       <c r="B44" s="79" t="n"/>
       <c r="C44" s="58" t="n"/>
       <c r="D44" s="58" t="inlineStr">
@@ -7884,7 +7505,7 @@
       <c r="H44" s="58" t="n"/>
       <c r="I44" s="58" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" s="60">
       <c r="B45" s="79" t="n"/>
       <c r="C45" s="58" t="n"/>
       <c r="D45" s="58" t="inlineStr">
@@ -7900,7 +7521,7 @@
       <c r="H45" s="58" t="n"/>
       <c r="I45" s="58" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" s="60">
       <c r="B46" s="79" t="n"/>
       <c r="C46" s="58" t="n"/>
       <c r="D46" s="58" t="inlineStr">
@@ -7916,7 +7537,7 @@
       <c r="H46" s="58" t="n"/>
       <c r="I46" s="58" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" s="60">
       <c r="B47" s="79" t="n"/>
       <c r="C47" s="58" t="n"/>
       <c r="D47" s="58" t="inlineStr">
@@ -7932,7 +7553,7 @@
       <c r="H47" s="58" t="n"/>
       <c r="I47" s="58" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" s="60">
       <c r="B48" s="79" t="n"/>
       <c r="C48" s="58" t="n">
         <v>21020</v>
@@ -7956,7 +7577,7 @@
       <c r="H48" s="58" t="n"/>
       <c r="I48" s="58" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" s="60">
       <c r="B49" s="79" t="n"/>
       <c r="C49" s="58" t="n"/>
       <c r="D49" s="58" t="inlineStr">
@@ -7972,7 +7593,7 @@
       <c r="H49" s="58" t="n"/>
       <c r="I49" s="58" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" s="60">
       <c r="B50" s="79" t="n"/>
       <c r="C50" s="58" t="n"/>
       <c r="D50" s="58" t="inlineStr">
@@ -7988,7 +7609,7 @@
       <c r="H50" s="58" t="n"/>
       <c r="I50" s="58" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" s="60">
       <c r="B51" s="79" t="n"/>
       <c r="C51" s="58" t="n">
         <v>21009</v>
@@ -8012,7 +7633,7 @@
       <c r="H51" s="58" t="n"/>
       <c r="I51" s="58" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" s="60">
       <c r="B52" s="79" t="n"/>
       <c r="C52" s="58" t="n"/>
       <c r="D52" s="58" t="inlineStr">
@@ -8028,7 +7649,7 @@
       <c r="H52" s="58" t="n"/>
       <c r="I52" s="58" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" s="60">
       <c r="B53" s="79" t="n"/>
       <c r="C53" s="58" t="n"/>
       <c r="D53" s="58" t="inlineStr">
@@ -8044,7 +7665,7 @@
       <c r="H53" s="58" t="n"/>
       <c r="I53" s="58" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" s="60">
       <c r="B54" s="79" t="n"/>
       <c r="C54" s="58" t="n">
         <v>21010</v>
@@ -8068,7 +7689,7 @@
       <c r="H54" s="58" t="n"/>
       <c r="I54" s="58" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" s="60">
       <c r="B55" s="79" t="n"/>
       <c r="C55" s="58" t="n"/>
       <c r="D55" s="58" t="inlineStr">
@@ -8084,7 +7705,7 @@
       <c r="H55" s="58" t="n"/>
       <c r="I55" s="58" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" s="60">
       <c r="B56" s="79" t="n"/>
       <c r="C56" s="58" t="n"/>
       <c r="D56" s="58" t="inlineStr">
@@ -8100,7 +7721,7 @@
       <c r="H56" s="58" t="n"/>
       <c r="I56" s="58" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" s="60">
       <c r="B57" s="79" t="n"/>
       <c r="C57" s="58" t="n">
         <v>21014</v>
@@ -8124,7 +7745,7 @@
       <c r="H57" s="58" t="n"/>
       <c r="I57" s="58" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" s="60">
       <c r="B58" s="79" t="n"/>
       <c r="C58" s="58" t="n"/>
       <c r="D58" s="58" t="inlineStr">
@@ -8140,7 +7761,7 @@
       <c r="H58" s="58" t="n"/>
       <c r="I58" s="58" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" s="60">
       <c r="B59" s="79" t="n"/>
       <c r="C59" s="58" t="n"/>
       <c r="D59" s="58" t="inlineStr">
@@ -8156,7 +7777,7 @@
       <c r="H59" s="58" t="n"/>
       <c r="I59" s="58" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" s="60">
       <c r="B60" s="79" t="n"/>
       <c r="C60" s="58" t="n"/>
       <c r="D60" s="58" t="inlineStr">
@@ -8172,7 +7793,7 @@
       <c r="H60" s="58" t="n"/>
       <c r="I60" s="58" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" s="60">
       <c r="B61" s="79" t="n"/>
       <c r="C61" s="58" t="n"/>
       <c r="D61" s="58" t="inlineStr">
@@ -8188,7 +7809,7 @@
       <c r="H61" s="58" t="n"/>
       <c r="I61" s="58" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" s="60">
       <c r="B62" s="79" t="n"/>
       <c r="C62" s="58" t="n">
         <v>21015</v>
@@ -8212,7 +7833,7 @@
       <c r="H62" s="58" t="n"/>
       <c r="I62" s="58" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" s="60">
       <c r="B63" s="79" t="n"/>
       <c r="C63" s="58" t="n"/>
       <c r="D63" s="58" t="inlineStr">
@@ -8228,7 +7849,7 @@
       <c r="H63" s="58" t="n"/>
       <c r="I63" s="58" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" s="60">
       <c r="B64" s="79" t="n"/>
       <c r="C64" s="58" t="n"/>
       <c r="D64" s="58" t="inlineStr">
@@ -8244,7 +7865,7 @@
       <c r="H64" s="58" t="n"/>
       <c r="I64" s="58" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" s="60">
       <c r="B65" s="79" t="n"/>
       <c r="C65" s="58" t="n">
         <v>21016</v>
@@ -8268,7 +7889,7 @@
       <c r="H65" s="58" t="n"/>
       <c r="I65" s="58" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" s="60">
       <c r="B66" s="79" t="n"/>
       <c r="C66" s="58" t="n"/>
       <c r="D66" s="58" t="inlineStr">
@@ -8284,7 +7905,7 @@
       <c r="H66" s="58" t="n"/>
       <c r="I66" s="58" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" s="60">
       <c r="B67" s="79" t="n"/>
       <c r="C67" s="58" t="n">
         <v>21017</v>
@@ -8308,7 +7929,7 @@
       <c r="H67" s="58" t="n"/>
       <c r="I67" s="58" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" s="60">
       <c r="B68" s="79" t="n"/>
       <c r="C68" s="58" t="n"/>
       <c r="D68" s="58" t="inlineStr">
@@ -8324,7 +7945,7 @@
       <c r="H68" s="58" t="n"/>
       <c r="I68" s="58" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" s="60">
       <c r="B69" s="79" t="n"/>
       <c r="C69" s="58" t="n">
         <v>21018</v>
@@ -8348,7 +7969,7 @@
       <c r="H69" s="58" t="n"/>
       <c r="I69" s="58" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" s="60">
       <c r="B70" s="79" t="n"/>
       <c r="C70" s="58" t="n"/>
       <c r="D70" s="58" t="inlineStr">
@@ -8364,7 +7985,7 @@
       <c r="H70" s="58" t="n"/>
       <c r="I70" s="58" t="n"/>
     </row>
-    <row r="71">
+    <row r="71" s="60">
       <c r="B71" s="79" t="n"/>
       <c r="C71" s="58" t="n"/>
       <c r="D71" s="58" t="inlineStr">
@@ -8380,7 +8001,7 @@
       <c r="H71" s="58" t="n"/>
       <c r="I71" s="58" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" s="60">
       <c r="B72" s="79" t="n"/>
       <c r="C72" s="58" t="n"/>
       <c r="D72" s="58" t="inlineStr">
@@ -8396,7 +8017,7 @@
       <c r="H72" s="58" t="n"/>
       <c r="I72" s="58" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" s="60">
       <c r="B73" s="80" t="n"/>
       <c r="C73" s="58" t="n"/>
       <c r="D73" s="58" t="inlineStr">
@@ -8412,7 +8033,7 @@
       <c r="H73" s="58" t="n"/>
       <c r="I73" s="58" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" s="60">
       <c r="B74" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -8444,7 +8065,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" s="60">
       <c r="B75" s="79" t="n"/>
       <c r="C75" s="58" t="n"/>
       <c r="D75" s="58" t="inlineStr">
@@ -8460,7 +8081,7 @@
       <c r="H75" s="58" t="n"/>
       <c r="I75" s="58" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" s="60">
       <c r="B76" s="79" t="n"/>
       <c r="C76" s="58" t="n"/>
       <c r="D76" s="58" t="inlineStr">
@@ -8476,7 +8097,7 @@
       <c r="H76" s="58" t="n"/>
       <c r="I76" s="58" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" s="60">
       <c r="B77" s="79" t="n"/>
       <c r="C77" s="58" t="n">
         <v>19000</v>
@@ -8500,7 +8121,7 @@
       <c r="H77" s="58" t="n"/>
       <c r="I77" s="58" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" s="60">
       <c r="B78" s="79" t="n"/>
       <c r="C78" s="58" t="n"/>
       <c r="D78" s="58" t="inlineStr">
@@ -8516,7 +8137,7 @@
       <c r="H78" s="58" t="n"/>
       <c r="I78" s="58" t="n"/>
     </row>
-    <row r="79">
+    <row r="79" s="60">
       <c r="B79" s="79" t="n"/>
       <c r="C79" s="58" t="n"/>
       <c r="D79" s="58" t="inlineStr">
@@ -8532,7 +8153,7 @@
       <c r="H79" s="58" t="n"/>
       <c r="I79" s="58" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" s="60">
       <c r="B80" s="79" t="n"/>
       <c r="C80" s="58" t="n">
         <v>19002</v>
@@ -8556,7 +8177,7 @@
       <c r="H80" s="58" t="n"/>
       <c r="I80" s="58" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" s="60">
       <c r="B81" s="80" t="n"/>
       <c r="C81" s="58" t="n"/>
       <c r="D81" s="58" t="inlineStr">
@@ -8572,7 +8193,7 @@
       <c r="H81" s="58" t="n"/>
       <c r="I81" s="58" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" s="60">
       <c r="B82" s="58" t="inlineStr">
         <is>
           <t>Spring Waterway</t>
@@ -8604,7 +8225,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" s="60">
       <c r="B83" s="79" t="n"/>
       <c r="C83" s="58" t="n"/>
       <c r="D83" s="58" t="inlineStr">
@@ -8620,7 +8241,7 @@
       <c r="H83" s="58" t="n"/>
       <c r="I83" s="58" t="n"/>
     </row>
-    <row r="84">
+    <row r="84" s="60">
       <c r="B84" s="79" t="n"/>
       <c r="C84" s="58" t="n"/>
       <c r="D84" s="58" t="inlineStr">
@@ -8636,7 +8257,7 @@
       <c r="H84" s="58" t="n"/>
       <c r="I84" s="58" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" s="60">
       <c r="B85" s="79" t="n"/>
       <c r="C85" s="58" t="n"/>
       <c r="D85" s="58" t="inlineStr">
@@ -8652,7 +8273,7 @@
       <c r="H85" s="58" t="n"/>
       <c r="I85" s="58" t="n"/>
     </row>
-    <row r="86">
+    <row r="86" s="60">
       <c r="B86" s="79" t="n"/>
       <c r="C86" s="58" t="n"/>
       <c r="D86" s="58" t="inlineStr">
@@ -8668,7 +8289,7 @@
       <c r="H86" s="58" t="n"/>
       <c r="I86" s="58" t="n"/>
     </row>
-    <row r="87">
+    <row r="87" s="60">
       <c r="B87" s="79" t="n"/>
       <c r="C87" s="58" t="n"/>
       <c r="D87" s="58" t="inlineStr">
@@ -8684,7 +8305,7 @@
       <c r="H87" s="58" t="n"/>
       <c r="I87" s="58" t="n"/>
     </row>
-    <row r="88">
+    <row r="88" s="60">
       <c r="B88" s="79" t="n"/>
       <c r="C88" s="58" t="n"/>
       <c r="D88" s="58" t="inlineStr">
@@ -8700,7 +8321,7 @@
       <c r="H88" s="58" t="n"/>
       <c r="I88" s="58" t="n"/>
     </row>
-    <row r="89">
+    <row r="89" s="60">
       <c r="B89" s="79" t="n"/>
       <c r="C89" s="58" t="n">
         <v>22901</v>
@@ -8724,7 +8345,7 @@
       <c r="H89" s="58" t="n"/>
       <c r="I89" s="58" t="n"/>
     </row>
-    <row r="90">
+    <row r="90" s="60">
       <c r="B90" s="79" t="n"/>
       <c r="C90" s="58" t="n"/>
       <c r="D90" s="58" t="inlineStr">
@@ -8740,7 +8361,7 @@
       <c r="H90" s="58" t="n"/>
       <c r="I90" s="58" t="n"/>
     </row>
-    <row r="91">
+    <row r="91" s="60">
       <c r="B91" s="79" t="n"/>
       <c r="C91" s="58" t="n">
         <v>22000</v>
@@ -8764,7 +8385,7 @@
       <c r="H91" s="58" t="n"/>
       <c r="I91" s="58" t="n"/>
     </row>
-    <row r="92">
+    <row r="92" s="60">
       <c r="B92" s="79" t="n"/>
       <c r="C92" s="58" t="n"/>
       <c r="D92" s="58" t="inlineStr">
@@ -8780,7 +8401,7 @@
       <c r="H92" s="58" t="n"/>
       <c r="I92" s="58" t="n"/>
     </row>
-    <row r="93">
+    <row r="93" s="60">
       <c r="B93" s="79" t="n"/>
       <c r="C93" s="58" t="n">
         <v>22001</v>
@@ -8804,7 +8425,7 @@
       <c r="H93" s="58" t="n"/>
       <c r="I93" s="58" t="n"/>
     </row>
-    <row r="94">
+    <row r="94" s="60">
       <c r="B94" s="79" t="n"/>
       <c r="C94" s="58" t="n"/>
       <c r="D94" s="58" t="inlineStr">
@@ -8820,7 +8441,7 @@
       <c r="H94" s="58" t="n"/>
       <c r="I94" s="58" t="n"/>
     </row>
-    <row r="95">
+    <row r="95" s="60">
       <c r="B95" s="79" t="n"/>
       <c r="C95" s="58" t="n"/>
       <c r="D95" s="58" t="inlineStr">
@@ -8836,7 +8457,7 @@
       <c r="H95" s="58" t="n"/>
       <c r="I95" s="58" t="n"/>
     </row>
-    <row r="96">
+    <row r="96" s="60">
       <c r="B96" s="79" t="n"/>
       <c r="C96" s="58" t="n"/>
       <c r="D96" s="58" t="inlineStr">
@@ -8852,7 +8473,7 @@
       <c r="H96" s="58" t="n"/>
       <c r="I96" s="58" t="n"/>
     </row>
-    <row r="97">
+    <row r="97" s="60">
       <c r="B97" s="79" t="n"/>
       <c r="C97" s="58" t="n"/>
       <c r="D97" s="58" t="inlineStr">
@@ -8868,7 +8489,7 @@
       <c r="H97" s="58" t="n"/>
       <c r="I97" s="58" t="n"/>
     </row>
-    <row r="98">
+    <row r="98" s="60">
       <c r="B98" s="79" t="n"/>
       <c r="C98" s="58" t="n">
         <v>22004</v>
@@ -8892,7 +8513,7 @@
       <c r="H98" s="58" t="n"/>
       <c r="I98" s="58" t="n"/>
     </row>
-    <row r="99">
+    <row r="99" s="60">
       <c r="B99" s="79" t="n"/>
       <c r="C99" s="58" t="n"/>
       <c r="D99" s="58" t="inlineStr">
@@ -8908,7 +8529,7 @@
       <c r="H99" s="58" t="n"/>
       <c r="I99" s="58" t="n"/>
     </row>
-    <row r="100">
+    <row r="100" s="60">
       <c r="B100" s="79" t="n"/>
       <c r="C100" s="58" t="n"/>
       <c r="D100" s="58" t="inlineStr">
@@ -8924,7 +8545,7 @@
       <c r="H100" s="58" t="n"/>
       <c r="I100" s="58" t="n"/>
     </row>
-    <row r="101">
+    <row r="101" s="60">
       <c r="B101" s="79" t="n"/>
       <c r="C101" s="58" t="n"/>
       <c r="D101" s="58" t="inlineStr">
@@ -8940,7 +8561,7 @@
       <c r="H101" s="58" t="n"/>
       <c r="I101" s="58" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" s="60">
       <c r="B102" s="79" t="n"/>
       <c r="C102" s="58" t="n">
         <v>22002</v>
@@ -8964,7 +8585,7 @@
       <c r="H102" s="58" t="n"/>
       <c r="I102" s="58" t="n"/>
     </row>
-    <row r="103">
+    <row r="103" s="60">
       <c r="B103" s="79" t="n"/>
       <c r="C103" s="58" t="n"/>
       <c r="D103" s="58" t="inlineStr">
@@ -8980,7 +8601,7 @@
       <c r="H103" s="58" t="n"/>
       <c r="I103" s="58" t="n"/>
     </row>
-    <row r="104">
+    <row r="104" s="60">
       <c r="B104" s="79" t="n"/>
       <c r="C104" s="58" t="n"/>
       <c r="D104" s="58" t="inlineStr">
@@ -8996,7 +8617,7 @@
       <c r="H104" s="58" t="n"/>
       <c r="I104" s="58" t="n"/>
     </row>
-    <row r="105">
+    <row r="105" s="60">
       <c r="B105" s="79" t="n"/>
       <c r="C105" s="58" t="n"/>
       <c r="D105" s="58" t="inlineStr">
@@ -9012,7 +8633,7 @@
       <c r="H105" s="58" t="n"/>
       <c r="I105" s="58" t="n"/>
     </row>
-    <row r="106">
+    <row r="106" s="60">
       <c r="B106" s="79" t="n"/>
       <c r="C106" s="58" t="n"/>
       <c r="D106" s="58" t="inlineStr">
@@ -9028,7 +8649,7 @@
       <c r="H106" s="58" t="n"/>
       <c r="I106" s="58" t="n"/>
     </row>
-    <row r="107">
+    <row r="107" s="60">
       <c r="B107" s="79" t="n"/>
       <c r="C107" s="58" t="n">
         <v>22003</v>
@@ -9052,7 +8673,7 @@
       <c r="H107" s="58" t="n"/>
       <c r="I107" s="58" t="n"/>
     </row>
-    <row r="108">
+    <row r="108" s="60">
       <c r="B108" s="79" t="n"/>
       <c r="C108" s="58" t="n"/>
       <c r="D108" s="58" t="inlineStr">
@@ -9068,7 +8689,7 @@
       <c r="H108" s="58" t="n"/>
       <c r="I108" s="58" t="n"/>
     </row>
-    <row r="109">
+    <row r="109" s="60">
       <c r="B109" s="79" t="n"/>
       <c r="C109" s="58" t="n"/>
       <c r="D109" s="58" t="inlineStr">
@@ -9084,7 +8705,7 @@
       <c r="H109" s="58" t="n"/>
       <c r="I109" s="58" t="n"/>
     </row>
-    <row r="110">
+    <row r="110" s="60">
       <c r="B110" s="79" t="n"/>
       <c r="C110" s="58" t="n">
         <v>22005</v>
@@ -9108,7 +8729,7 @@
       <c r="H110" s="58" t="n"/>
       <c r="I110" s="58" t="n"/>
     </row>
-    <row r="111">
+    <row r="111" s="60">
       <c r="B111" s="79" t="n"/>
       <c r="C111" s="58" t="n"/>
       <c r="D111" s="58" t="inlineStr">
@@ -9124,7 +8745,7 @@
       <c r="H111" s="58" t="n"/>
       <c r="I111" s="58" t="n"/>
     </row>
-    <row r="112">
+    <row r="112" s="60">
       <c r="B112" s="79" t="n"/>
       <c r="C112" s="58" t="n"/>
       <c r="D112" s="58" t="inlineStr">
@@ -9140,7 +8761,7 @@
       <c r="H112" s="58" t="n"/>
       <c r="I112" s="58" t="n"/>
     </row>
-    <row r="113">
+    <row r="113" s="60">
       <c r="B113" s="79" t="n"/>
       <c r="C113" s="58" t="n"/>
       <c r="D113" s="58" t="inlineStr">
@@ -9156,7 +8777,7 @@
       <c r="H113" s="58" t="n"/>
       <c r="I113" s="58" t="n"/>
     </row>
-    <row r="114">
+    <row r="114" s="60">
       <c r="B114" s="79" t="n"/>
       <c r="C114" s="58" t="n">
         <v>22006</v>
@@ -9180,7 +8801,7 @@
       <c r="H114" s="58" t="n"/>
       <c r="I114" s="58" t="n"/>
     </row>
-    <row r="115">
+    <row r="115" s="60">
       <c r="B115" s="79" t="n"/>
       <c r="C115" s="58" t="n"/>
       <c r="D115" s="58" t="inlineStr">
@@ -9196,7 +8817,7 @@
       <c r="H115" s="58" t="n"/>
       <c r="I115" s="58" t="n"/>
     </row>
-    <row r="116">
+    <row r="116" s="60">
       <c r="B116" s="79" t="n"/>
       <c r="C116" s="58" t="n"/>
       <c r="D116" s="58" t="inlineStr">
@@ -9212,7 +8833,7 @@
       <c r="H116" s="58" t="n"/>
       <c r="I116" s="58" t="n"/>
     </row>
-    <row r="117">
+    <row r="117" s="60">
       <c r="B117" s="79" t="n"/>
       <c r="C117" s="58" t="n">
         <v>22007</v>
@@ -9236,7 +8857,7 @@
       <c r="H117" s="58" t="n"/>
       <c r="I117" s="58" t="n"/>
     </row>
-    <row r="118">
+    <row r="118" s="60">
       <c r="B118" s="79" t="n"/>
       <c r="C118" s="58" t="n"/>
       <c r="D118" s="58" t="inlineStr">
@@ -9252,7 +8873,7 @@
       <c r="H118" s="58" t="n"/>
       <c r="I118" s="58" t="n"/>
     </row>
-    <row r="119">
+    <row r="119" s="60">
       <c r="B119" s="79" t="n"/>
       <c r="C119" s="58" t="n"/>
       <c r="D119" s="58" t="inlineStr">
@@ -9268,7 +8889,7 @@
       <c r="H119" s="58" t="n"/>
       <c r="I119" s="58" t="n"/>
     </row>
-    <row r="120">
+    <row r="120" s="60">
       <c r="B120" s="79" t="n"/>
       <c r="C120" s="58" t="n"/>
       <c r="D120" s="58" t="inlineStr">
@@ -9284,7 +8905,7 @@
       <c r="H120" s="58" t="n"/>
       <c r="I120" s="58" t="n"/>
     </row>
-    <row r="121">
+    <row r="121" s="60">
       <c r="B121" s="79" t="n"/>
       <c r="C121" s="58" t="n"/>
       <c r="D121" s="58" t="inlineStr">
@@ -9300,7 +8921,7 @@
       <c r="H121" s="58" t="n"/>
       <c r="I121" s="58" t="n"/>
     </row>
-    <row r="122">
+    <row r="122" s="60">
       <c r="B122" s="79" t="n"/>
       <c r="C122" s="58" t="n"/>
       <c r="D122" s="58" t="inlineStr">
@@ -9316,7 +8937,7 @@
       <c r="H122" s="58" t="n"/>
       <c r="I122" s="58" t="n"/>
     </row>
-    <row r="123">
+    <row r="123" s="60">
       <c r="B123" s="79" t="n"/>
       <c r="C123" s="58" t="n">
         <v>22902</v>
@@ -9340,7 +8961,7 @@
       <c r="H123" s="58" t="n"/>
       <c r="I123" s="58" t="n"/>
     </row>
-    <row r="124">
+    <row r="124" s="60">
       <c r="B124" s="79" t="n"/>
       <c r="C124" s="58" t="n"/>
       <c r="D124" s="58" t="inlineStr">
@@ -9356,7 +8977,7 @@
       <c r="H124" s="58" t="n"/>
       <c r="I124" s="58" t="n"/>
     </row>
-    <row r="125">
+    <row r="125" s="60">
       <c r="B125" s="79" t="n"/>
       <c r="C125" s="58" t="n"/>
       <c r="D125" s="58" t="inlineStr">
@@ -9372,7 +8993,7 @@
       <c r="H125" s="58" t="n"/>
       <c r="I125" s="58" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" s="60">
       <c r="B126" s="79" t="n"/>
       <c r="C126" s="58" t="n">
         <v>22903</v>
@@ -9396,7 +9017,7 @@
       <c r="H126" s="58" t="n"/>
       <c r="I126" s="58" t="n"/>
     </row>
-    <row r="127">
+    <row r="127" s="60">
       <c r="B127" s="79" t="n"/>
       <c r="C127" s="58" t="n"/>
       <c r="D127" s="58" t="inlineStr">
@@ -9412,7 +9033,7 @@
       <c r="H127" s="58" t="n"/>
       <c r="I127" s="58" t="n"/>
     </row>
-    <row r="128">
+    <row r="128" s="60">
       <c r="B128" s="79" t="n"/>
       <c r="C128" s="58" t="n">
         <v>22009</v>
@@ -9436,7 +9057,7 @@
       <c r="H128" s="58" t="n"/>
       <c r="I128" s="58" t="n"/>
     </row>
-    <row r="129">
+    <row r="129" s="60">
       <c r="B129" s="79" t="n"/>
       <c r="C129" s="58" t="n"/>
       <c r="D129" s="58" t="inlineStr">
@@ -9452,7 +9073,7 @@
       <c r="H129" s="58" t="n"/>
       <c r="I129" s="58" t="n"/>
     </row>
-    <row r="130">
+    <row r="130" s="60">
       <c r="B130" s="79" t="n"/>
       <c r="C130" s="58" t="n"/>
       <c r="D130" s="58" t="inlineStr">
@@ -9468,7 +9089,7 @@
       <c r="H130" s="58" t="n"/>
       <c r="I130" s="58" t="n"/>
     </row>
-    <row r="131">
+    <row r="131" s="60">
       <c r="B131" s="79" t="n"/>
       <c r="C131" s="58" t="n">
         <v>22010</v>
@@ -9492,7 +9113,7 @@
       <c r="H131" s="58" t="n"/>
       <c r="I131" s="58" t="n"/>
     </row>
-    <row r="132">
+    <row r="132" s="60">
       <c r="B132" s="79" t="n"/>
       <c r="C132" s="58" t="n"/>
       <c r="D132" s="58" t="inlineStr">
@@ -9508,7 +9129,7 @@
       <c r="H132" s="58" t="n"/>
       <c r="I132" s="58" t="n"/>
     </row>
-    <row r="133">
+    <row r="133" s="60">
       <c r="B133" s="79" t="n"/>
       <c r="C133" s="58" t="n"/>
       <c r="D133" s="58" t="inlineStr">
@@ -9524,7 +9145,7 @@
       <c r="H133" s="58" t="n"/>
       <c r="I133" s="58" t="n"/>
     </row>
-    <row r="134">
+    <row r="134" s="60">
       <c r="B134" s="79" t="n"/>
       <c r="C134" s="58" t="n">
         <v>22012</v>
@@ -9548,7 +9169,7 @@
       <c r="H134" s="58" t="n"/>
       <c r="I134" s="58" t="n"/>
     </row>
-    <row r="135">
+    <row r="135" s="60">
       <c r="B135" s="79" t="n"/>
       <c r="C135" s="58" t="n"/>
       <c r="D135" s="58" t="inlineStr">
@@ -9564,7 +9185,7 @@
       <c r="H135" s="58" t="n"/>
       <c r="I135" s="58" t="n"/>
     </row>
-    <row r="136">
+    <row r="136" s="60">
       <c r="B136" s="79" t="n"/>
       <c r="C136" s="58" t="n"/>
       <c r="D136" s="58" t="inlineStr">
@@ -9580,7 +9201,7 @@
       <c r="H136" s="58" t="n"/>
       <c r="I136" s="58" t="n"/>
     </row>
-    <row r="137">
+    <row r="137" s="60">
       <c r="B137" s="79" t="n"/>
       <c r="C137" s="58" t="n"/>
       <c r="D137" s="58" t="inlineStr">
@@ -9596,7 +9217,7 @@
       <c r="H137" s="58" t="n"/>
       <c r="I137" s="58" t="n"/>
     </row>
-    <row r="138">
+    <row r="138" s="60">
       <c r="B138" s="79" t="n"/>
       <c r="C138" s="58" t="n"/>
       <c r="D138" s="58" t="inlineStr">
@@ -9612,7 +9233,7 @@
       <c r="H138" s="58" t="n"/>
       <c r="I138" s="58" t="n"/>
     </row>
-    <row r="139">
+    <row r="139" s="60">
       <c r="B139" s="79" t="n"/>
       <c r="C139" s="58" t="n">
         <v>22013</v>
@@ -9636,7 +9257,7 @@
       <c r="H139" s="58" t="n"/>
       <c r="I139" s="58" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" s="60">
       <c r="B140" s="79" t="n"/>
       <c r="C140" s="58" t="n"/>
       <c r="D140" s="58" t="inlineStr">
@@ -9652,7 +9273,7 @@
       <c r="H140" s="58" t="n"/>
       <c r="I140" s="58" t="n"/>
     </row>
-    <row r="141">
+    <row r="141" s="60">
       <c r="B141" s="79" t="n"/>
       <c r="C141" s="58" t="n">
         <v>22014</v>
@@ -9676,7 +9297,7 @@
       <c r="H141" s="58" t="n"/>
       <c r="I141" s="58" t="n"/>
     </row>
-    <row r="142">
+    <row r="142" s="60">
       <c r="B142" s="79" t="n"/>
       <c r="C142" s="58" t="n"/>
       <c r="D142" s="58" t="inlineStr">
@@ -9692,7 +9313,7 @@
       <c r="H142" s="58" t="n"/>
       <c r="I142" s="58" t="n"/>
     </row>
-    <row r="143">
+    <row r="143" s="60">
       <c r="B143" s="79" t="n"/>
       <c r="C143" s="58" t="n"/>
       <c r="D143" s="58" t="inlineStr">
@@ -9708,7 +9329,7 @@
       <c r="H143" s="58" t="n"/>
       <c r="I143" s="58" t="n"/>
     </row>
-    <row r="144">
+    <row r="144" s="60">
       <c r="B144" s="79" t="n"/>
       <c r="C144" s="58" t="n"/>
       <c r="D144" s="58" t="inlineStr">
@@ -9724,7 +9345,7 @@
       <c r="H144" s="58" t="n"/>
       <c r="I144" s="58" t="n"/>
     </row>
-    <row r="145">
+    <row r="145" s="60">
       <c r="B145" s="79" t="n"/>
       <c r="C145" s="58" t="n">
         <v>22015</v>
@@ -9748,7 +9369,7 @@
       <c r="H145" s="58" t="n"/>
       <c r="I145" s="58" t="n"/>
     </row>
-    <row r="146">
+    <row r="146" s="60">
       <c r="B146" s="79" t="n"/>
       <c r="C146" s="58" t="n"/>
       <c r="D146" s="58" t="inlineStr">
@@ -9764,7 +9385,7 @@
       <c r="H146" s="58" t="n"/>
       <c r="I146" s="58" t="n"/>
     </row>
-    <row r="147">
+    <row r="147" s="60">
       <c r="B147" s="79" t="n"/>
       <c r="C147" s="58" t="n"/>
       <c r="D147" s="58" t="inlineStr">
@@ -9780,7 +9401,7 @@
       <c r="H147" s="58" t="n"/>
       <c r="I147" s="58" t="n"/>
     </row>
-    <row r="148">
+    <row r="148" s="60">
       <c r="B148" s="79" t="n"/>
       <c r="C148" s="58" t="n"/>
       <c r="D148" s="58" t="inlineStr">
@@ -9796,7 +9417,7 @@
       <c r="H148" s="58" t="n"/>
       <c r="I148" s="58" t="n"/>
     </row>
-    <row r="149">
+    <row r="149" s="60">
       <c r="B149" s="79" t="n"/>
       <c r="C149" s="58" t="n"/>
       <c r="D149" s="58" t="inlineStr">
@@ -9812,7 +9433,7 @@
       <c r="H149" s="58" t="n"/>
       <c r="I149" s="58" t="n"/>
     </row>
-    <row r="150">
+    <row r="150" s="60">
       <c r="B150" s="79" t="n"/>
       <c r="C150" s="58" t="n">
         <v>22300</v>
@@ -9836,7 +9457,7 @@
       <c r="H150" s="58" t="n"/>
       <c r="I150" s="58" t="n"/>
     </row>
-    <row r="151">
+    <row r="151" s="60">
       <c r="B151" s="79" t="n"/>
       <c r="C151" s="58" t="n"/>
       <c r="D151" s="58" t="inlineStr">
@@ -9852,7 +9473,7 @@
       <c r="H151" s="58" t="n"/>
       <c r="I151" s="58" t="n"/>
     </row>
-    <row r="152">
+    <row r="152" s="60">
       <c r="B152" s="79" t="n"/>
       <c r="C152" s="58" t="n"/>
       <c r="D152" s="58" t="inlineStr">
@@ -9868,7 +9489,7 @@
       <c r="H152" s="58" t="n"/>
       <c r="I152" s="58" t="n"/>
     </row>
-    <row r="153">
+    <row r="153" s="60">
       <c r="B153" s="79" t="n"/>
       <c r="C153" s="58" t="n">
         <v>22016</v>
@@ -9892,7 +9513,7 @@
       <c r="H153" s="58" t="n"/>
       <c r="I153" s="58" t="n"/>
     </row>
-    <row r="154">
+    <row r="154" s="60">
       <c r="B154" s="79" t="n"/>
       <c r="C154" s="58" t="n"/>
       <c r="D154" s="58" t="inlineStr">
@@ -9908,7 +9529,7 @@
       <c r="H154" s="58" t="n"/>
       <c r="I154" s="58" t="n"/>
     </row>
-    <row r="155">
+    <row r="155" s="60">
       <c r="B155" s="79" t="n"/>
       <c r="C155" s="58" t="n"/>
       <c r="D155" s="58" t="inlineStr">
@@ -9924,7 +9545,7 @@
       <c r="H155" s="58" t="n"/>
       <c r="I155" s="58" t="n"/>
     </row>
-    <row r="156">
+    <row r="156" s="60">
       <c r="B156" s="79" t="n"/>
       <c r="C156" s="58" t="n"/>
       <c r="D156" s="58" t="inlineStr">
@@ -9940,7 +9561,7 @@
       <c r="H156" s="58" t="n"/>
       <c r="I156" s="58" t="n"/>
     </row>
-    <row r="157">
+    <row r="157" s="60">
       <c r="B157" s="79" t="n"/>
       <c r="C157" s="58" t="n"/>
       <c r="D157" s="58" t="inlineStr">
@@ -9956,7 +9577,7 @@
       <c r="H157" s="58" t="n"/>
       <c r="I157" s="58" t="n"/>
     </row>
-    <row r="158">
+    <row r="158" s="60">
       <c r="B158" s="79" t="n"/>
       <c r="C158" s="58" t="n"/>
       <c r="D158" s="58" t="inlineStr">
@@ -9972,7 +9593,7 @@
       <c r="H158" s="58" t="n"/>
       <c r="I158" s="58" t="n"/>
     </row>
-    <row r="159">
+    <row r="159" s="60">
       <c r="B159" s="79" t="n"/>
       <c r="C159" s="58" t="n"/>
       <c r="D159" s="58" t="inlineStr">
@@ -9988,7 +9609,7 @@
       <c r="H159" s="58" t="n"/>
       <c r="I159" s="58" t="n"/>
     </row>
-    <row r="160">
+    <row r="160" s="60">
       <c r="B160" s="79" t="n"/>
       <c r="C160" s="58" t="n">
         <v>22017</v>
@@ -10012,7 +9633,7 @@
       <c r="H160" s="58" t="n"/>
       <c r="I160" s="58" t="n"/>
     </row>
-    <row r="161">
+    <row r="161" s="60">
       <c r="B161" s="79" t="n"/>
       <c r="C161" s="58" t="n"/>
       <c r="D161" s="58" t="inlineStr">
@@ -10028,7 +9649,7 @@
       <c r="H161" s="58" t="n"/>
       <c r="I161" s="58" t="n"/>
     </row>
-    <row r="162">
+    <row r="162" s="60">
       <c r="B162" s="79" t="n"/>
       <c r="C162" s="58" t="n"/>
       <c r="D162" s="58" t="inlineStr">
@@ -10044,7 +9665,7 @@
       <c r="H162" s="58" t="n"/>
       <c r="I162" s="58" t="n"/>
     </row>
-    <row r="163">
+    <row r="163" s="60">
       <c r="B163" s="79" t="n"/>
       <c r="C163" s="58" t="n"/>
       <c r="D163" s="58" t="inlineStr">
@@ -10060,7 +9681,7 @@
       <c r="H163" s="58" t="n"/>
       <c r="I163" s="58" t="n"/>
     </row>
-    <row r="164">
+    <row r="164" s="60">
       <c r="B164" s="79" t="n"/>
       <c r="C164" s="58" t="n">
         <v>22011</v>
@@ -10084,7 +9705,7 @@
       <c r="H164" s="58" t="n"/>
       <c r="I164" s="58" t="n"/>
     </row>
-    <row r="165">
+    <row r="165" s="60">
       <c r="B165" s="79" t="n"/>
       <c r="C165" s="58" t="n"/>
       <c r="D165" s="58" t="inlineStr">
@@ -10100,7 +9721,7 @@
       <c r="H165" s="58" t="n"/>
       <c r="I165" s="58" t="n"/>
     </row>
-    <row r="166">
+    <row r="166" s="60">
       <c r="B166" s="79" t="n"/>
       <c r="C166" s="58" t="n">
         <v>22018</v>
@@ -10124,7 +9745,7 @@
       <c r="H166" s="58" t="n"/>
       <c r="I166" s="58" t="n"/>
     </row>
-    <row r="167">
+    <row r="167" s="60">
       <c r="B167" s="79" t="n"/>
       <c r="C167" s="58" t="n"/>
       <c r="D167" s="58" t="inlineStr">
@@ -10140,7 +9761,7 @@
       <c r="H167" s="58" t="n"/>
       <c r="I167" s="58" t="n"/>
     </row>
-    <row r="168">
+    <row r="168" s="60">
       <c r="B168" s="79" t="n"/>
       <c r="C168" s="58" t="n"/>
       <c r="D168" s="58" t="inlineStr">
@@ -10156,7 +9777,7 @@
       <c r="H168" s="58" t="n"/>
       <c r="I168" s="58" t="n"/>
     </row>
-    <row r="169">
+    <row r="169" s="60">
       <c r="B169" s="79" t="n"/>
       <c r="C169" s="58" t="n"/>
       <c r="D169" s="58" t="inlineStr">
@@ -10172,7 +9793,7 @@
       <c r="H169" s="58" t="n"/>
       <c r="I169" s="58" t="n"/>
     </row>
-    <row r="170">
+    <row r="170" s="60">
       <c r="B170" s="79" t="n"/>
       <c r="C170" s="58" t="n"/>
       <c r="D170" s="58" t="inlineStr">
@@ -10188,7 +9809,7 @@
       <c r="H170" s="58" t="n"/>
       <c r="I170" s="58" t="n"/>
     </row>
-    <row r="171">
+    <row r="171" s="60">
       <c r="B171" s="79" t="n"/>
       <c r="C171" s="58" t="n"/>
       <c r="D171" s="58" t="inlineStr">
@@ -10204,7 +9825,7 @@
       <c r="H171" s="58" t="n"/>
       <c r="I171" s="58" t="n"/>
     </row>
-    <row r="172">
+    <row r="172" s="60">
       <c r="B172" s="79" t="n"/>
       <c r="C172" s="58" t="n">
         <v>22019</v>
@@ -10228,7 +9849,7 @@
       <c r="H172" s="58" t="n"/>
       <c r="I172" s="58" t="n"/>
     </row>
-    <row r="173">
+    <row r="173" s="60">
       <c r="B173" s="79" t="n"/>
       <c r="C173" s="58" t="n"/>
       <c r="D173" s="58" t="inlineStr">
@@ -10244,7 +9865,7 @@
       <c r="H173" s="58" t="n"/>
       <c r="I173" s="58" t="n"/>
     </row>
-    <row r="174">
+    <row r="174" s="60">
       <c r="B174" s="79" t="n"/>
       <c r="C174" s="58" t="n"/>
       <c r="D174" s="58" t="inlineStr">
@@ -10260,7 +9881,7 @@
       <c r="H174" s="58" t="n"/>
       <c r="I174" s="58" t="n"/>
     </row>
-    <row r="175">
+    <row r="175" s="60">
       <c r="B175" s="79" t="n"/>
       <c r="C175" s="58" t="n">
         <v>22008</v>
@@ -10284,7 +9905,7 @@
       <c r="H175" s="58" t="n"/>
       <c r="I175" s="58" t="n"/>
     </row>
-    <row r="176">
+    <row r="176" s="60">
       <c r="B176" s="79" t="n"/>
       <c r="C176" s="58" t="n"/>
       <c r="D176" s="58" t="inlineStr">
@@ -10300,7 +9921,7 @@
       <c r="H176" s="58" t="n"/>
       <c r="I176" s="58" t="n"/>
     </row>
-    <row r="177">
+    <row r="177" s="60">
       <c r="B177" s="79" t="n"/>
       <c r="C177" s="58" t="n"/>
       <c r="D177" s="58" t="inlineStr">
@@ -10316,7 +9937,7 @@
       <c r="H177" s="58" t="n"/>
       <c r="I177" s="58" t="n"/>
     </row>
-    <row r="178">
+    <row r="178" s="60">
       <c r="B178" s="79" t="n"/>
       <c r="C178" s="58" t="n">
         <v>22020</v>
@@ -10340,7 +9961,7 @@
       <c r="H178" s="58" t="n"/>
       <c r="I178" s="58" t="n"/>
     </row>
-    <row r="179">
+    <row r="179" s="60">
       <c r="B179" s="79" t="n"/>
       <c r="C179" s="58" t="n"/>
       <c r="D179" s="58" t="inlineStr">
@@ -10356,7 +9977,7 @@
       <c r="H179" s="58" t="n"/>
       <c r="I179" s="58" t="n"/>
     </row>
-    <row r="180">
+    <row r="180" s="60">
       <c r="B180" s="79" t="n"/>
       <c r="C180" s="58" t="n"/>
       <c r="D180" s="58" t="inlineStr">
@@ -10372,7 +9993,7 @@
       <c r="H180" s="58" t="n"/>
       <c r="I180" s="58" t="n"/>
     </row>
-    <row r="181">
+    <row r="181" s="60">
       <c r="B181" s="79" t="n"/>
       <c r="C181" s="58" t="n"/>
       <c r="D181" s="58" t="inlineStr">
@@ -10388,7 +10009,7 @@
       <c r="H181" s="58" t="n"/>
       <c r="I181" s="58" t="n"/>
     </row>
-    <row r="182">
+    <row r="182" s="60">
       <c r="B182" s="79" t="n"/>
       <c r="C182" s="58" t="n"/>
       <c r="D182" s="58" t="inlineStr">
@@ -10404,7 +10025,7 @@
       <c r="H182" s="58" t="n"/>
       <c r="I182" s="58" t="n"/>
     </row>
-    <row r="183">
+    <row r="183" s="60">
       <c r="B183" s="79" t="n"/>
       <c r="C183" s="58" t="n">
         <v>22021</v>
@@ -10428,7 +10049,7 @@
       <c r="H183" s="58" t="n"/>
       <c r="I183" s="58" t="n"/>
     </row>
-    <row r="184">
+    <row r="184" s="60">
       <c r="B184" s="79" t="n"/>
       <c r="C184" s="58" t="n"/>
       <c r="D184" s="58" t="inlineStr">
@@ -10444,7 +10065,7 @@
       <c r="H184" s="58" t="n"/>
       <c r="I184" s="58" t="n"/>
     </row>
-    <row r="185">
+    <row r="185" s="60">
       <c r="B185" s="79" t="n"/>
       <c r="C185" s="58" t="n"/>
       <c r="D185" s="58" t="inlineStr">
@@ -10460,7 +10081,7 @@
       <c r="H185" s="58" t="n"/>
       <c r="I185" s="58" t="n"/>
     </row>
-    <row r="186">
+    <row r="186" s="60">
       <c r="B186" s="79" t="n"/>
       <c r="C186" s="58" t="n"/>
       <c r="D186" s="58" t="inlineStr">
@@ -10476,7 +10097,7 @@
       <c r="H186" s="58" t="n"/>
       <c r="I186" s="58" t="n"/>
     </row>
-    <row r="187">
+    <row r="187" s="60">
       <c r="B187" s="79" t="n"/>
       <c r="C187" s="58" t="n">
         <v>22022</v>
@@ -10500,7 +10121,7 @@
       <c r="H187" s="58" t="n"/>
       <c r="I187" s="58" t="n"/>
     </row>
-    <row r="188">
+    <row r="188" s="60">
       <c r="B188" s="79" t="n"/>
       <c r="C188" s="58" t="n"/>
       <c r="D188" s="58" t="inlineStr">
@@ -10516,7 +10137,7 @@
       <c r="H188" s="58" t="n"/>
       <c r="I188" s="58" t="n"/>
     </row>
-    <row r="189">
+    <row r="189" s="60">
       <c r="B189" s="79" t="n"/>
       <c r="C189" s="58" t="n"/>
       <c r="D189" s="58" t="inlineStr">
@@ -10532,7 +10153,7 @@
       <c r="H189" s="58" t="n"/>
       <c r="I189" s="58" t="n"/>
     </row>
-    <row r="190">
+    <row r="190" s="60">
       <c r="B190" s="79" t="n"/>
       <c r="C190" s="58" t="n"/>
       <c r="D190" s="58" t="inlineStr">
@@ -10548,7 +10169,7 @@
       <c r="H190" s="58" t="n"/>
       <c r="I190" s="58" t="n"/>
     </row>
-    <row r="191">
+    <row r="191" s="60">
       <c r="B191" s="79" t="n"/>
       <c r="C191" s="58" t="n"/>
       <c r="D191" s="58" t="inlineStr">
@@ -10564,7 +10185,7 @@
       <c r="H191" s="58" t="n"/>
       <c r="I191" s="58" t="n"/>
     </row>
-    <row r="192">
+    <row r="192" s="60">
       <c r="B192" s="79" t="n"/>
       <c r="C192" s="58" t="n"/>
       <c r="D192" s="58" t="inlineStr">
@@ -10580,7 +10201,7 @@
       <c r="H192" s="58" t="n"/>
       <c r="I192" s="58" t="n"/>
     </row>
-    <row r="193">
+    <row r="193" s="60">
       <c r="B193" s="79" t="n"/>
       <c r="C193" s="58" t="n">
         <v>22023</v>
@@ -10604,7 +10225,7 @@
       <c r="H193" s="58" t="n"/>
       <c r="I193" s="58" t="n"/>
     </row>
-    <row r="194">
+    <row r="194" s="60">
       <c r="B194" s="79" t="n"/>
       <c r="C194" s="58" t="n"/>
       <c r="D194" s="58" t="inlineStr">
@@ -10620,7 +10241,7 @@
       <c r="H194" s="58" t="n"/>
       <c r="I194" s="58" t="n"/>
     </row>
-    <row r="195">
+    <row r="195" s="60">
       <c r="B195" s="79" t="n"/>
       <c r="C195" s="58" t="n"/>
       <c r="D195" s="58" t="inlineStr">
@@ -10636,7 +10257,7 @@
       <c r="H195" s="58" t="n"/>
       <c r="I195" s="58" t="n"/>
     </row>
-    <row r="196">
+    <row r="196" s="60">
       <c r="B196" s="79" t="n"/>
       <c r="C196" s="58" t="n"/>
       <c r="D196" s="58" t="inlineStr">
@@ -10652,7 +10273,7 @@
       <c r="H196" s="58" t="n"/>
       <c r="I196" s="58" t="n"/>
     </row>
-    <row r="197">
+    <row r="197" s="60">
       <c r="B197" s="79" t="n"/>
       <c r="C197" s="58" t="n"/>
       <c r="D197" s="58" t="inlineStr">
@@ -10668,7 +10289,7 @@
       <c r="H197" s="58" t="n"/>
       <c r="I197" s="58" t="n"/>
     </row>
-    <row r="198">
+    <row r="198" s="60">
       <c r="B198" s="79" t="n"/>
       <c r="C198" s="58" t="n"/>
       <c r="D198" s="58" t="inlineStr">
@@ -10684,7 +10305,7 @@
       <c r="H198" s="58" t="n"/>
       <c r="I198" s="58" t="n"/>
     </row>
-    <row r="199">
+    <row r="199" s="60">
       <c r="B199" s="79" t="n"/>
       <c r="C199" s="58" t="n">
         <v>22024</v>
@@ -10708,7 +10329,7 @@
       <c r="H199" s="58" t="n"/>
       <c r="I199" s="58" t="n"/>
     </row>
-    <row r="200">
+    <row r="200" s="60">
       <c r="B200" s="79" t="n"/>
       <c r="C200" s="58" t="n"/>
       <c r="D200" s="58" t="inlineStr">
@@ -10724,7 +10345,7 @@
       <c r="H200" s="58" t="n"/>
       <c r="I200" s="58" t="n"/>
     </row>
-    <row r="201">
+    <row r="201" s="60">
       <c r="B201" s="79" t="n"/>
       <c r="C201" s="58" t="n"/>
       <c r="D201" s="58" t="inlineStr">
@@ -10740,7 +10361,7 @@
       <c r="H201" s="58" t="n"/>
       <c r="I201" s="58" t="n"/>
     </row>
-    <row r="202">
+    <row r="202" s="60">
       <c r="B202" s="79" t="n"/>
       <c r="C202" s="58" t="n"/>
       <c r="D202" s="58" t="inlineStr">
@@ -10756,7 +10377,7 @@
       <c r="H202" s="58" t="n"/>
       <c r="I202" s="58" t="n"/>
     </row>
-    <row r="203">
+    <row r="203" s="60">
       <c r="B203" s="79" t="n"/>
       <c r="C203" s="58" t="n"/>
       <c r="D203" s="58" t="inlineStr">
@@ -10772,7 +10393,7 @@
       <c r="H203" s="58" t="n"/>
       <c r="I203" s="58" t="n"/>
     </row>
-    <row r="204">
+    <row r="204" s="60">
       <c r="B204" s="79" t="n"/>
       <c r="C204" s="58" t="n"/>
       <c r="D204" s="58" t="inlineStr">
@@ -10788,7 +10409,7 @@
       <c r="H204" s="58" t="n"/>
       <c r="I204" s="58" t="n"/>
     </row>
-    <row r="205">
+    <row r="205" s="60">
       <c r="B205" s="79" t="n"/>
       <c r="C205" s="58" t="n">
         <v>22025</v>
@@ -10812,7 +10433,7 @@
       <c r="H205" s="58" t="n"/>
       <c r="I205" s="58" t="n"/>
     </row>
-    <row r="206">
+    <row r="206" s="60">
       <c r="B206" s="79" t="n"/>
       <c r="C206" s="58" t="n"/>
       <c r="D206" s="58" t="inlineStr">
@@ -10828,7 +10449,7 @@
       <c r="H206" s="58" t="n"/>
       <c r="I206" s="58" t="n"/>
     </row>
-    <row r="207">
+    <row r="207" s="60">
       <c r="B207" s="79" t="n"/>
       <c r="C207" s="58" t="n"/>
       <c r="D207" s="58" t="inlineStr">
@@ -10844,7 +10465,7 @@
       <c r="H207" s="58" t="n"/>
       <c r="I207" s="58" t="n"/>
     </row>
-    <row r="208">
+    <row r="208" s="60">
       <c r="B208" s="79" t="n"/>
       <c r="C208" s="58" t="n"/>
       <c r="D208" s="58" t="inlineStr">
@@ -10860,7 +10481,7 @@
       <c r="H208" s="58" t="n"/>
       <c r="I208" s="58" t="n"/>
     </row>
-    <row r="209">
+    <row r="209" s="60">
       <c r="B209" s="79" t="n"/>
       <c r="C209" s="58" t="n"/>
       <c r="D209" s="58" t="inlineStr">
@@ -10876,7 +10497,7 @@
       <c r="H209" s="58" t="n"/>
       <c r="I209" s="58" t="n"/>
     </row>
-    <row r="210">
+    <row r="210" s="60">
       <c r="B210" s="79" t="n"/>
       <c r="C210" s="58" t="n">
         <v>22026</v>
@@ -10900,7 +10521,7 @@
       <c r="H210" s="58" t="n"/>
       <c r="I210" s="58" t="n"/>
     </row>
-    <row r="211">
+    <row r="211" s="60">
       <c r="B211" s="79" t="n"/>
       <c r="C211" s="58" t="n"/>
       <c r="D211" s="58" t="inlineStr">
@@ -10916,7 +10537,7 @@
       <c r="H211" s="58" t="n"/>
       <c r="I211" s="58" t="n"/>
     </row>
-    <row r="212">
+    <row r="212" s="60">
       <c r="B212" s="79" t="n"/>
       <c r="C212" s="58" t="n"/>
       <c r="D212" s="58" t="inlineStr">
@@ -10932,7 +10553,7 @@
       <c r="H212" s="58" t="n"/>
       <c r="I212" s="58" t="n"/>
     </row>
-    <row r="213">
+    <row r="213" s="60">
       <c r="B213" s="79" t="n"/>
       <c r="C213" s="58" t="n"/>
       <c r="D213" s="58" t="inlineStr">
@@ -10948,7 +10569,7 @@
       <c r="H213" s="58" t="n"/>
       <c r="I213" s="58" t="n"/>
     </row>
-    <row r="214">
+    <row r="214" s="60">
       <c r="B214" s="79" t="n"/>
       <c r="C214" s="58" t="n"/>
       <c r="D214" s="58" t="inlineStr">
@@ -10964,7 +10585,7 @@
       <c r="H214" s="58" t="n"/>
       <c r="I214" s="58" t="n"/>
     </row>
-    <row r="215">
+    <row r="215" s="60">
       <c r="B215" s="79" t="n"/>
       <c r="C215" s="58" t="n"/>
       <c r="D215" s="58" t="inlineStr">
@@ -10980,7 +10601,7 @@
       <c r="H215" s="58" t="n"/>
       <c r="I215" s="58" t="n"/>
     </row>
-    <row r="216">
+    <row r="216" s="60">
       <c r="B216" s="79" t="n"/>
       <c r="C216" s="58" t="n"/>
       <c r="D216" s="58" t="inlineStr">
@@ -10996,7 +10617,7 @@
       <c r="H216" s="58" t="n"/>
       <c r="I216" s="58" t="n"/>
     </row>
-    <row r="217">
+    <row r="217" s="60">
       <c r="B217" s="79" t="n"/>
       <c r="C217" s="58" t="n">
         <v>22029</v>
@@ -11020,7 +10641,7 @@
       <c r="H217" s="58" t="n"/>
       <c r="I217" s="58" t="n"/>
     </row>
-    <row r="218">
+    <row r="218" s="60">
       <c r="B218" s="79" t="n"/>
       <c r="C218" s="58" t="n"/>
       <c r="D218" s="58" t="inlineStr">
@@ -11036,7 +10657,7 @@
       <c r="H218" s="58" t="n"/>
       <c r="I218" s="58" t="n"/>
     </row>
-    <row r="219">
+    <row r="219" s="60">
       <c r="B219" s="79" t="n"/>
       <c r="C219" s="58" t="n">
         <v>22600</v>
@@ -11060,7 +10681,7 @@
       <c r="H219" s="58" t="n"/>
       <c r="I219" s="58" t="n"/>
     </row>
-    <row r="220">
+    <row r="220" s="60">
       <c r="B220" s="79" t="n"/>
       <c r="C220" s="58" t="n"/>
       <c r="D220" s="58" t="inlineStr">
@@ -11076,7 +10697,7 @@
       <c r="H220" s="58" t="n"/>
       <c r="I220" s="58" t="n"/>
     </row>
-    <row r="221">
+    <row r="221" s="60">
       <c r="B221" s="79" t="n"/>
       <c r="C221" s="58" t="n"/>
       <c r="D221" s="58" t="inlineStr">
@@ -11092,7 +10713,7 @@
       <c r="H221" s="58" t="n"/>
       <c r="I221" s="58" t="n"/>
     </row>
-    <row r="222">
+    <row r="222" s="60">
       <c r="B222" s="79" t="n"/>
       <c r="C222" s="58" t="n"/>
       <c r="D222" s="58" t="inlineStr">
@@ -11108,7 +10729,7 @@
       <c r="H222" s="58" t="n"/>
       <c r="I222" s="58" t="n"/>
     </row>
-    <row r="223">
+    <row r="223" s="60">
       <c r="B223" s="79" t="n"/>
       <c r="C223" s="58" t="n">
         <v>22028</v>
@@ -11132,7 +10753,7 @@
       <c r="H223" s="58" t="n"/>
       <c r="I223" s="58" t="n"/>
     </row>
-    <row r="224">
+    <row r="224" s="60">
       <c r="B224" s="79" t="n"/>
       <c r="C224" s="58" t="n"/>
       <c r="D224" s="58" t="inlineStr">
@@ -11148,7 +10769,7 @@
       <c r="H224" s="58" t="n"/>
       <c r="I224" s="58" t="n"/>
     </row>
-    <row r="225">
+    <row r="225" s="60">
       <c r="B225" s="79" t="n"/>
       <c r="C225" s="58" t="n"/>
       <c r="D225" s="58" t="inlineStr">
@@ -11164,7 +10785,7 @@
       <c r="H225" s="58" t="n"/>
       <c r="I225" s="58" t="n"/>
     </row>
-    <row r="226">
+    <row r="226" s="60">
       <c r="B226" s="79" t="n"/>
       <c r="C226" s="58" t="n">
         <v>22904</v>
@@ -11188,7 +10809,7 @@
       <c r="H226" s="58" t="n"/>
       <c r="I226" s="58" t="n"/>
     </row>
-    <row r="227">
+    <row r="227" s="60">
       <c r="B227" s="80" t="n"/>
       <c r="C227" s="58" t="n"/>
       <c r="D227" s="58" t="inlineStr">
@@ -11204,7 +10825,7 @@
       <c r="H227" s="58" t="n"/>
       <c r="I227" s="58" t="n"/>
     </row>
-    <row r="228">
+    <row r="228" s="60">
       <c r="B228" s="58" t="inlineStr">
         <is>
           <t>Submerged Passage</t>
@@ -11236,7 +10857,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" s="60">
       <c r="B229" s="79" t="n"/>
       <c r="C229" s="58" t="n"/>
       <c r="D229" s="58" t="inlineStr">
@@ -11252,7 +10873,7 @@
       <c r="H229" s="58" t="n"/>
       <c r="I229" s="58" t="n"/>
     </row>
-    <row r="230">
+    <row r="230" s="60">
       <c r="B230" s="79" t="n"/>
       <c r="C230" s="58" t="n"/>
       <c r="D230" s="58" t="inlineStr">
@@ -11268,7 +10889,7 @@
       <c r="H230" s="58" t="n"/>
       <c r="I230" s="58" t="n"/>
     </row>
-    <row r="231">
+    <row r="231" s="60">
       <c r="B231" s="79" t="n"/>
       <c r="C231" s="58" t="n"/>
       <c r="D231" s="58" t="inlineStr">
@@ -11284,7 +10905,7 @@
       <c r="H231" s="58" t="n"/>
       <c r="I231" s="58" t="n"/>
     </row>
-    <row r="232">
+    <row r="232" s="60">
       <c r="B232" s="79" t="n"/>
       <c r="C232" s="58" t="n">
         <v>23900</v>
@@ -11308,7 +10929,7 @@
       <c r="H232" s="58" t="n"/>
       <c r="I232" s="58" t="n"/>
     </row>
-    <row r="233">
+    <row r="233" s="60">
       <c r="B233" s="79" t="n"/>
       <c r="C233" s="58" t="n"/>
       <c r="D233" s="58" t="inlineStr">
@@ -11324,7 +10945,7 @@
       <c r="H233" s="58" t="n"/>
       <c r="I233" s="58" t="n"/>
     </row>
-    <row r="234">
+    <row r="234" s="60">
       <c r="B234" s="79" t="n"/>
       <c r="C234" s="58" t="n">
         <v>23001</v>
@@ -11348,7 +10969,7 @@
       <c r="H234" s="58" t="n"/>
       <c r="I234" s="58" t="n"/>
     </row>
-    <row r="235">
+    <row r="235" s="60">
       <c r="B235" s="79" t="n"/>
       <c r="C235" s="58" t="n"/>
       <c r="D235" s="58" t="inlineStr">
@@ -11364,7 +10985,7 @@
       <c r="H235" s="58" t="n"/>
       <c r="I235" s="58" t="n"/>
     </row>
-    <row r="236">
+    <row r="236" s="60">
       <c r="B236" s="79" t="n"/>
       <c r="C236" s="58" t="n"/>
       <c r="D236" s="58" t="inlineStr">
@@ -11380,7 +11001,7 @@
       <c r="H236" s="58" t="n"/>
       <c r="I236" s="58" t="n"/>
     </row>
-    <row r="237">
+    <row r="237" s="60">
       <c r="B237" s="79" t="n"/>
       <c r="C237" s="58" t="n"/>
       <c r="D237" s="58" t="inlineStr">
@@ -11396,7 +11017,7 @@
       <c r="H237" s="58" t="n"/>
       <c r="I237" s="58" t="n"/>
     </row>
-    <row r="238">
+    <row r="238" s="60">
       <c r="B238" s="79" t="n"/>
       <c r="C238" s="58" t="n"/>
       <c r="D238" s="58" t="inlineStr">
@@ -11412,7 +11033,7 @@
       <c r="H238" s="58" t="n"/>
       <c r="I238" s="58" t="n"/>
     </row>
-    <row r="239">
+    <row r="239" s="60">
       <c r="B239" s="79" t="n"/>
       <c r="C239" s="58" t="n">
         <v>23002</v>
@@ -11436,7 +11057,7 @@
       <c r="H239" s="58" t="n"/>
       <c r="I239" s="58" t="n"/>
     </row>
-    <row r="240">
+    <row r="240" s="60">
       <c r="B240" s="79" t="n"/>
       <c r="C240" s="58" t="n"/>
       <c r="D240" s="58" t="inlineStr">
@@ -11452,7 +11073,7 @@
       <c r="H240" s="58" t="n"/>
       <c r="I240" s="58" t="n"/>
     </row>
-    <row r="241">
+    <row r="241" s="60">
       <c r="B241" s="79" t="n"/>
       <c r="C241" s="58" t="n"/>
       <c r="D241" s="58" t="inlineStr">
@@ -11468,7 +11089,7 @@
       <c r="H241" s="58" t="n"/>
       <c r="I241" s="58" t="n"/>
     </row>
-    <row r="242">
+    <row r="242" s="60">
       <c r="B242" s="79" t="n"/>
       <c r="C242" s="58" t="n"/>
       <c r="D242" s="58" t="inlineStr">
@@ -11484,7 +11105,7 @@
       <c r="H242" s="58" t="n"/>
       <c r="I242" s="58" t="n"/>
     </row>
-    <row r="243">
+    <row r="243" s="60">
       <c r="B243" s="79" t="n"/>
       <c r="C243" s="58" t="n"/>
       <c r="D243" s="58" t="inlineStr">
@@ -11500,7 +11121,7 @@
       <c r="H243" s="58" t="n"/>
       <c r="I243" s="58" t="n"/>
     </row>
-    <row r="244">
+    <row r="244" s="60">
       <c r="B244" s="79" t="n"/>
       <c r="C244" s="58" t="n">
         <v>23003</v>
@@ -11524,7 +11145,7 @@
       <c r="H244" s="58" t="n"/>
       <c r="I244" s="58" t="n"/>
     </row>
-    <row r="245">
+    <row r="245" s="60">
       <c r="B245" s="79" t="n"/>
       <c r="C245" s="58" t="n"/>
       <c r="D245" s="58" t="inlineStr">
@@ -11540,7 +11161,7 @@
       <c r="H245" s="58" t="n"/>
       <c r="I245" s="58" t="n"/>
     </row>
-    <row r="246">
+    <row r="246" s="60">
       <c r="B246" s="79" t="n"/>
       <c r="C246" s="58" t="n"/>
       <c r="D246" s="58" t="inlineStr">
@@ -11556,7 +11177,7 @@
       <c r="H246" s="58" t="n"/>
       <c r="I246" s="58" t="n"/>
     </row>
-    <row r="247">
+    <row r="247" s="60">
       <c r="B247" s="79" t="n"/>
       <c r="C247" s="58" t="n"/>
       <c r="D247" s="58" t="inlineStr">
@@ -11572,7 +11193,7 @@
       <c r="H247" s="58" t="n"/>
       <c r="I247" s="58" t="n"/>
     </row>
-    <row r="248">
+    <row r="248" s="60">
       <c r="B248" s="79" t="n"/>
       <c r="C248" s="58" t="n"/>
       <c r="D248" s="58" t="inlineStr">
@@ -11588,7 +11209,7 @@
       <c r="H248" s="58" t="n"/>
       <c r="I248" s="58" t="n"/>
     </row>
-    <row r="249">
+    <row r="249" s="60">
       <c r="B249" s="79" t="n"/>
       <c r="C249" s="58" t="n">
         <v>23004</v>
@@ -11612,7 +11233,7 @@
       <c r="H249" s="58" t="n"/>
       <c r="I249" s="58" t="n"/>
     </row>
-    <row r="250">
+    <row r="250" s="60">
       <c r="B250" s="79" t="n"/>
       <c r="C250" s="58" t="n"/>
       <c r="D250" s="58" t="inlineStr">
@@ -11628,7 +11249,7 @@
       <c r="H250" s="58" t="n"/>
       <c r="I250" s="58" t="n"/>
     </row>
-    <row r="251">
+    <row r="251" s="60">
       <c r="B251" s="80" t="n"/>
       <c r="C251" s="58" t="n"/>
       <c r="D251" s="58" t="inlineStr">
@@ -11644,7 +11265,7 @@
       <c r="H251" s="58" t="n"/>
       <c r="I251" s="58" t="n"/>
     </row>
-    <row r="252">
+    <row r="252" s="60">
       <c r="B252" s="58" t="inlineStr">
         <is>
           <t>Salt Mine</t>
@@ -11676,7 +11297,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" s="60">
       <c r="B253" s="79" t="n"/>
       <c r="C253" s="58" t="n"/>
       <c r="D253" s="58" t="inlineStr">
@@ -11692,7 +11313,7 @@
       <c r="H253" s="58" t="n"/>
       <c r="I253" s="58" t="n"/>
     </row>
-    <row r="254">
+    <row r="254" s="60">
       <c r="B254" s="79" t="n"/>
       <c r="C254" s="58" t="n"/>
       <c r="D254" s="58" t="inlineStr">
@@ -11708,7 +11329,7 @@
       <c r="H254" s="58" t="n"/>
       <c r="I254" s="58" t="n"/>
     </row>
-    <row r="255">
+    <row r="255" s="60">
       <c r="B255" s="79" t="n"/>
       <c r="C255" s="58" t="n"/>
       <c r="D255" s="58" t="inlineStr">
@@ -11724,7 +11345,7 @@
       <c r="H255" s="58" t="n"/>
       <c r="I255" s="58" t="n"/>
     </row>
-    <row r="256">
+    <row r="256" s="60">
       <c r="B256" s="79" t="n"/>
       <c r="C256" s="58" t="n"/>
       <c r="D256" s="58" t="inlineStr">
@@ -11740,7 +11361,7 @@
       <c r="H256" s="58" t="n"/>
       <c r="I256" s="58" t="n"/>
     </row>
-    <row r="257">
+    <row r="257" s="60">
       <c r="B257" s="79" t="n"/>
       <c r="C257" s="58" t="n"/>
       <c r="D257" s="58" t="inlineStr">
@@ -11756,7 +11377,7 @@
       <c r="H257" s="58" t="n"/>
       <c r="I257" s="58" t="n"/>
     </row>
-    <row r="258">
+    <row r="258" s="60">
       <c r="B258" s="79" t="n"/>
       <c r="C258" s="58" t="n"/>
       <c r="D258" s="58" t="inlineStr">
@@ -11772,7 +11393,7 @@
       <c r="H258" s="58" t="n"/>
       <c r="I258" s="58" t="n"/>
     </row>
-    <row r="259">
+    <row r="259" s="60">
       <c r="B259" s="79" t="n"/>
       <c r="C259" s="58" t="n">
         <v>24001</v>
@@ -11796,7 +11417,7 @@
       <c r="H259" s="58" t="n"/>
       <c r="I259" s="58" t="n"/>
     </row>
-    <row r="260">
+    <row r="260" s="60">
       <c r="B260" s="79" t="n"/>
       <c r="C260" s="58" t="n"/>
       <c r="D260" s="58" t="inlineStr">
@@ -11812,7 +11433,7 @@
       <c r="H260" s="58" t="n"/>
       <c r="I260" s="58" t="n"/>
     </row>
-    <row r="261">
+    <row r="261" s="60">
       <c r="B261" s="79" t="n"/>
       <c r="C261" s="58" t="n"/>
       <c r="D261" s="58" t="inlineStr">
@@ -11828,7 +11449,7 @@
       <c r="H261" s="58" t="n"/>
       <c r="I261" s="58" t="n"/>
     </row>
-    <row r="262">
+    <row r="262" s="60">
       <c r="B262" s="79" t="n"/>
       <c r="C262" s="58" t="n">
         <v>24002</v>
@@ -11852,7 +11473,7 @@
       <c r="H262" s="58" t="n"/>
       <c r="I262" s="58" t="n"/>
     </row>
-    <row r="263">
+    <row r="263" s="60">
       <c r="B263" s="79" t="n"/>
       <c r="C263" s="58" t="n"/>
       <c r="D263" s="58" t="inlineStr">
@@ -11868,7 +11489,7 @@
       <c r="H263" s="58" t="n"/>
       <c r="I263" s="58" t="n"/>
     </row>
-    <row r="264">
+    <row r="264" s="60">
       <c r="B264" s="79" t="n"/>
       <c r="C264" s="58" t="n"/>
       <c r="D264" s="58" t="inlineStr">
@@ -11884,7 +11505,7 @@
       <c r="H264" s="58" t="n"/>
       <c r="I264" s="58" t="n"/>
     </row>
-    <row r="265">
+    <row r="265" s="60">
       <c r="B265" s="79" t="n"/>
       <c r="C265" s="58" t="n"/>
       <c r="D265" s="58" t="inlineStr">
@@ -11900,7 +11521,7 @@
       <c r="H265" s="58" t="n"/>
       <c r="I265" s="58" t="n"/>
     </row>
-    <row r="266">
+    <row r="266" s="60">
       <c r="B266" s="79" t="n"/>
       <c r="C266" s="58" t="n"/>
       <c r="D266" s="58" t="inlineStr">
@@ -11916,7 +11537,7 @@
       <c r="H266" s="58" t="n"/>
       <c r="I266" s="58" t="n"/>
     </row>
-    <row r="267">
+    <row r="267" s="60">
       <c r="B267" s="79" t="n"/>
       <c r="C267" s="58" t="n"/>
       <c r="D267" s="58" t="inlineStr">
@@ -11932,7 +11553,7 @@
       <c r="H267" s="58" t="n"/>
       <c r="I267" s="58" t="n"/>
     </row>
-    <row r="268">
+    <row r="268" s="60">
       <c r="B268" s="79" t="n"/>
       <c r="C268" s="58" t="n">
         <v>24006</v>
@@ -11956,7 +11577,7 @@
       <c r="H268" s="58" t="n"/>
       <c r="I268" s="58" t="n"/>
     </row>
-    <row r="269">
+    <row r="269" s="60">
       <c r="B269" s="79" t="n"/>
       <c r="C269" s="58" t="n"/>
       <c r="D269" s="58" t="inlineStr">
@@ -11972,7 +11593,7 @@
       <c r="H269" s="58" t="n"/>
       <c r="I269" s="58" t="n"/>
     </row>
-    <row r="270">
+    <row r="270" s="60">
       <c r="B270" s="79" t="n"/>
       <c r="C270" s="58" t="n"/>
       <c r="D270" s="58" t="inlineStr">
@@ -11988,7 +11609,7 @@
       <c r="H270" s="58" t="n"/>
       <c r="I270" s="58" t="n"/>
     </row>
-    <row r="271">
+    <row r="271" s="60">
       <c r="B271" s="79" t="n"/>
       <c r="C271" s="58" t="n"/>
       <c r="D271" s="58" t="inlineStr">
@@ -12004,7 +11625,7 @@
       <c r="H271" s="58" t="n"/>
       <c r="I271" s="58" t="n"/>
     </row>
-    <row r="272">
+    <row r="272" s="60">
       <c r="B272" s="79" t="n"/>
       <c r="C272" s="58" t="n">
         <v>24007</v>
@@ -12028,7 +11649,7 @@
       <c r="H272" s="58" t="n"/>
       <c r="I272" s="58" t="n"/>
     </row>
-    <row r="273">
+    <row r="273" s="60">
       <c r="B273" s="79" t="n"/>
       <c r="C273" s="58" t="n"/>
       <c r="D273" s="58" t="inlineStr">
@@ -12044,7 +11665,7 @@
       <c r="H273" s="58" t="n"/>
       <c r="I273" s="58" t="n"/>
     </row>
-    <row r="274">
+    <row r="274" s="60">
       <c r="B274" s="79" t="n"/>
       <c r="C274" s="58" t="n"/>
       <c r="D274" s="58" t="inlineStr">
@@ -12060,7 +11681,7 @@
       <c r="H274" s="58" t="n"/>
       <c r="I274" s="58" t="n"/>
     </row>
-    <row r="275">
+    <row r="275" s="60">
       <c r="B275" s="79" t="n"/>
       <c r="C275" s="58" t="n"/>
       <c r="D275" s="58" t="inlineStr">
@@ -12076,7 +11697,7 @@
       <c r="H275" s="58" t="n"/>
       <c r="I275" s="58" t="n"/>
     </row>
-    <row r="276">
+    <row r="276" s="60">
       <c r="B276" s="79" t="n"/>
       <c r="C276" s="58" t="n"/>
       <c r="D276" s="58" t="inlineStr">
@@ -12092,7 +11713,7 @@
       <c r="H276" s="58" t="n"/>
       <c r="I276" s="58" t="n"/>
     </row>
-    <row r="277">
+    <row r="277" s="60">
       <c r="B277" s="79" t="n"/>
       <c r="C277" s="58" t="n"/>
       <c r="D277" s="58" t="inlineStr">
@@ -12108,7 +11729,7 @@
       <c r="H277" s="58" t="n"/>
       <c r="I277" s="58" t="n"/>
     </row>
-    <row r="278">
+    <row r="278" s="60">
       <c r="B278" s="79" t="n"/>
       <c r="C278" s="58" t="n">
         <v>24009</v>
@@ -12132,7 +11753,7 @@
       <c r="H278" s="58" t="n"/>
       <c r="I278" s="58" t="n"/>
     </row>
-    <row r="279">
+    <row r="279" s="60">
       <c r="B279" s="79" t="n"/>
       <c r="C279" s="58" t="n"/>
       <c r="D279" s="58" t="inlineStr">
@@ -12148,7 +11769,7 @@
       <c r="H279" s="58" t="n"/>
       <c r="I279" s="58" t="n"/>
     </row>
-    <row r="280">
+    <row r="280" s="60">
       <c r="B280" s="79" t="n"/>
       <c r="C280" s="58" t="n"/>
       <c r="D280" s="58" t="inlineStr">
@@ -12164,7 +11785,7 @@
       <c r="H280" s="58" t="n"/>
       <c r="I280" s="58" t="n"/>
     </row>
-    <row r="281">
+    <row r="281" s="60">
       <c r="B281" s="79" t="n"/>
       <c r="C281" s="58" t="n"/>
       <c r="D281" s="58" t="inlineStr">
@@ -12180,7 +11801,7 @@
       <c r="H281" s="58" t="n"/>
       <c r="I281" s="58" t="n"/>
     </row>
-    <row r="282">
+    <row r="282" s="60">
       <c r="B282" s="79" t="n"/>
       <c r="C282" s="58" t="n"/>
       <c r="D282" s="58" t="inlineStr">
@@ -12196,7 +11817,7 @@
       <c r="H282" s="58" t="n"/>
       <c r="I282" s="58" t="n"/>
     </row>
-    <row r="283">
+    <row r="283" s="60">
       <c r="B283" s="79" t="n"/>
       <c r="C283" s="58" t="n">
         <v>24010</v>
@@ -12220,7 +11841,7 @@
       <c r="H283" s="58" t="n"/>
       <c r="I283" s="58" t="n"/>
     </row>
-    <row r="284">
+    <row r="284" s="60">
       <c r="B284" s="79" t="n"/>
       <c r="C284" s="58" t="n"/>
       <c r="D284" s="58" t="inlineStr">
@@ -12236,7 +11857,7 @@
       <c r="H284" s="58" t="n"/>
       <c r="I284" s="58" t="n"/>
     </row>
-    <row r="285">
+    <row r="285" s="60">
       <c r="B285" s="79" t="n"/>
       <c r="C285" s="58" t="n"/>
       <c r="D285" s="58" t="inlineStr">
@@ -12252,7 +11873,7 @@
       <c r="H285" s="58" t="n"/>
       <c r="I285" s="58" t="n"/>
     </row>
-    <row r="286">
+    <row r="286" s="60">
       <c r="B286" s="79" t="n"/>
       <c r="C286" s="58" t="n"/>
       <c r="D286" s="58" t="inlineStr">
@@ -12268,7 +11889,7 @@
       <c r="H286" s="58" t="n"/>
       <c r="I286" s="58" t="n"/>
     </row>
-    <row r="287">
+    <row r="287" s="60">
       <c r="B287" s="79" t="n"/>
       <c r="C287" s="58" t="n"/>
       <c r="D287" s="58" t="inlineStr">
@@ -12284,7 +11905,7 @@
       <c r="H287" s="58" t="n"/>
       <c r="I287" s="58" t="n"/>
     </row>
-    <row r="288">
+    <row r="288" s="60">
       <c r="B288" s="79" t="n"/>
       <c r="C288" s="58" t="n">
         <v>24011</v>
@@ -12308,7 +11929,7 @@
       <c r="H288" s="58" t="n"/>
       <c r="I288" s="58" t="n"/>
     </row>
-    <row r="289">
+    <row r="289" s="60">
       <c r="B289" s="79" t="n"/>
       <c r="C289" s="58" t="n"/>
       <c r="D289" s="58" t="inlineStr">
@@ -12324,7 +11945,7 @@
       <c r="H289" s="58" t="n"/>
       <c r="I289" s="58" t="n"/>
     </row>
-    <row r="290">
+    <row r="290" s="60">
       <c r="B290" s="79" t="n"/>
       <c r="C290" s="58" t="n"/>
       <c r="D290" s="58" t="inlineStr">
@@ -12340,7 +11961,7 @@
       <c r="H290" s="58" t="n"/>
       <c r="I290" s="58" t="n"/>
     </row>
-    <row r="291">
+    <row r="291" s="60">
       <c r="B291" s="79" t="n"/>
       <c r="C291" s="58" t="n">
         <v>24012</v>
@@ -12364,7 +11985,7 @@
       <c r="H291" s="58" t="n"/>
       <c r="I291" s="58" t="n"/>
     </row>
-    <row r="292">
+    <row r="292" s="60">
       <c r="B292" s="79" t="n"/>
       <c r="C292" s="58" t="n"/>
       <c r="D292" s="58" t="inlineStr">
@@ -12380,7 +12001,7 @@
       <c r="H292" s="58" t="n"/>
       <c r="I292" s="58" t="n"/>
     </row>
-    <row r="293">
+    <row r="293" s="60">
       <c r="B293" s="79" t="n"/>
       <c r="C293" s="58" t="n"/>
       <c r="D293" s="58" t="inlineStr">
@@ -12396,7 +12017,7 @@
       <c r="H293" s="58" t="n"/>
       <c r="I293" s="58" t="n"/>
     </row>
-    <row r="294">
+    <row r="294" s="60">
       <c r="B294" s="79" t="n"/>
       <c r="C294" s="58" t="n"/>
       <c r="D294" s="58" t="inlineStr">
@@ -12412,7 +12033,7 @@
       <c r="H294" s="58" t="n"/>
       <c r="I294" s="58" t="n"/>
     </row>
-    <row r="295">
+    <row r="295" s="60">
       <c r="B295" s="79" t="n"/>
       <c r="C295" s="58" t="n"/>
       <c r="D295" s="58" t="inlineStr">
@@ -12428,7 +12049,7 @@
       <c r="H295" s="58" t="n"/>
       <c r="I295" s="58" t="n"/>
     </row>
-    <row r="296">
+    <row r="296" s="60">
       <c r="B296" s="79" t="n"/>
       <c r="C296" s="58" t="n"/>
       <c r="D296" s="58" t="inlineStr">
@@ -12444,7 +12065,7 @@
       <c r="H296" s="58" t="n"/>
       <c r="I296" s="58" t="n"/>
     </row>
-    <row r="297">
+    <row r="297" s="60">
       <c r="B297" s="79" t="n"/>
       <c r="C297" s="58" t="n">
         <v>24013</v>
@@ -12468,7 +12089,7 @@
       <c r="H297" s="58" t="n"/>
       <c r="I297" s="58" t="n"/>
     </row>
-    <row r="298">
+    <row r="298" s="60">
       <c r="B298" s="79" t="n"/>
       <c r="C298" s="58" t="n"/>
       <c r="D298" s="58" t="inlineStr">
@@ -12484,7 +12105,7 @@
       <c r="H298" s="58" t="n"/>
       <c r="I298" s="58" t="n"/>
     </row>
-    <row r="299">
+    <row r="299" s="60">
       <c r="B299" s="79" t="n"/>
       <c r="C299" s="58" t="n"/>
       <c r="D299" s="58" t="inlineStr">
@@ -12500,7 +12121,7 @@
       <c r="H299" s="58" t="n"/>
       <c r="I299" s="58" t="n"/>
     </row>
-    <row r="300">
+    <row r="300" s="60">
       <c r="B300" s="79" t="n"/>
       <c r="C300" s="58" t="n"/>
       <c r="D300" s="58" t="inlineStr">
@@ -12516,7 +12137,7 @@
       <c r="H300" s="58" t="n"/>
       <c r="I300" s="58" t="n"/>
     </row>
-    <row r="301">
+    <row r="301" s="60">
       <c r="B301" s="79" t="n"/>
       <c r="C301" s="58" t="n"/>
       <c r="D301" s="58" t="inlineStr">
@@ -12532,7 +12153,7 @@
       <c r="H301" s="58" t="n"/>
       <c r="I301" s="58" t="n"/>
     </row>
-    <row r="302">
+    <row r="302" s="60">
       <c r="B302" s="79" t="n"/>
       <c r="C302" s="58" t="n"/>
       <c r="D302" s="58" t="inlineStr">
@@ -12548,7 +12169,7 @@
       <c r="H302" s="58" t="n"/>
       <c r="I302" s="58" t="n"/>
     </row>
-    <row r="303">
+    <row r="303" s="60">
       <c r="B303" s="79" t="n"/>
       <c r="C303" s="58" t="n">
         <v>24014</v>
@@ -12572,7 +12193,7 @@
       <c r="H303" s="58" t="n"/>
       <c r="I303" s="58" t="n"/>
     </row>
-    <row r="304">
+    <row r="304" s="60">
       <c r="B304" s="79" t="n"/>
       <c r="C304" s="58" t="n"/>
       <c r="D304" s="58" t="inlineStr">
@@ -12588,7 +12209,7 @@
       <c r="H304" s="58" t="n"/>
       <c r="I304" s="58" t="n"/>
     </row>
-    <row r="305">
+    <row r="305" s="60">
       <c r="B305" s="79" t="n"/>
       <c r="C305" s="58" t="n"/>
       <c r="D305" s="58" t="inlineStr">
@@ -12604,7 +12225,7 @@
       <c r="H305" s="58" t="n"/>
       <c r="I305" s="58" t="n"/>
     </row>
-    <row r="306">
+    <row r="306" s="60">
       <c r="B306" s="79" t="n"/>
       <c r="C306" s="58" t="n"/>
       <c r="D306" s="58" t="inlineStr">
@@ -12620,7 +12241,7 @@
       <c r="H306" s="58" t="n"/>
       <c r="I306" s="58" t="n"/>
     </row>
-    <row r="307">
+    <row r="307" s="60">
       <c r="B307" s="79" t="n"/>
       <c r="C307" s="58" t="n"/>
       <c r="D307" s="58" t="inlineStr">
@@ -12636,7 +12257,7 @@
       <c r="H307" s="58" t="n"/>
       <c r="I307" s="58" t="n"/>
     </row>
-    <row r="308">
+    <row r="308" s="60">
       <c r="B308" s="79" t="n"/>
       <c r="C308" s="58" t="n">
         <v>24015</v>
@@ -12660,7 +12281,7 @@
       <c r="H308" s="58" t="n"/>
       <c r="I308" s="58" t="n"/>
     </row>
-    <row r="309">
+    <row r="309" s="60">
       <c r="B309" s="79" t="n"/>
       <c r="C309" s="58" t="n"/>
       <c r="D309" s="58" t="inlineStr">
@@ -12676,7 +12297,7 @@
       <c r="H309" s="58" t="n"/>
       <c r="I309" s="58" t="n"/>
     </row>
-    <row r="310">
+    <row r="310" s="60">
       <c r="B310" s="79" t="n"/>
       <c r="C310" s="58" t="n"/>
       <c r="D310" s="58" t="inlineStr">
@@ -12692,7 +12313,7 @@
       <c r="H310" s="58" t="n"/>
       <c r="I310" s="58" t="n"/>
     </row>
-    <row r="311">
+    <row r="311" s="60">
       <c r="B311" s="79" t="n"/>
       <c r="C311" s="58" t="n">
         <v>24016</v>
@@ -12716,7 +12337,7 @@
       <c r="H311" s="58" t="n"/>
       <c r="I311" s="58" t="n"/>
     </row>
-    <row r="312">
+    <row r="312" s="60">
       <c r="B312" s="79" t="n"/>
       <c r="C312" s="58" t="n"/>
       <c r="D312" s="58" t="inlineStr">
@@ -12732,7 +12353,7 @@
       <c r="H312" s="58" t="n"/>
       <c r="I312" s="58" t="n"/>
     </row>
-    <row r="313">
+    <row r="313" s="60">
       <c r="B313" s="79" t="n"/>
       <c r="C313" s="58" t="n"/>
       <c r="D313" s="58" t="inlineStr">
@@ -12748,7 +12369,7 @@
       <c r="H313" s="58" t="n"/>
       <c r="I313" s="58" t="n"/>
     </row>
-    <row r="314">
+    <row r="314" s="60">
       <c r="B314" s="79" t="n"/>
       <c r="C314" s="58" t="n">
         <v>24017</v>
@@ -12772,7 +12393,7 @@
       <c r="H314" s="58" t="n"/>
       <c r="I314" s="58" t="n"/>
     </row>
-    <row r="315">
+    <row r="315" s="60">
       <c r="B315" s="79" t="n"/>
       <c r="C315" s="58" t="n"/>
       <c r="D315" s="58" t="inlineStr">
@@ -12788,7 +12409,7 @@
       <c r="H315" s="58" t="n"/>
       <c r="I315" s="58" t="n"/>
     </row>
-    <row r="316">
+    <row r="316" s="60">
       <c r="B316" s="79" t="n"/>
       <c r="C316" s="58" t="n"/>
       <c r="D316" s="58" t="inlineStr">
@@ -12804,7 +12425,7 @@
       <c r="H316" s="58" t="n"/>
       <c r="I316" s="58" t="n"/>
     </row>
-    <row r="317">
+    <row r="317" s="60">
       <c r="B317" s="79" t="n"/>
       <c r="C317" s="58" t="n"/>
       <c r="D317" s="58" t="inlineStr">
@@ -12820,7 +12441,7 @@
       <c r="H317" s="58" t="n"/>
       <c r="I317" s="58" t="n"/>
     </row>
-    <row r="318">
+    <row r="318" s="60">
       <c r="B318" s="79" t="n"/>
       <c r="C318" s="58" t="n"/>
       <c r="D318" s="58" t="inlineStr">
@@ -12836,7 +12457,7 @@
       <c r="H318" s="58" t="n"/>
       <c r="I318" s="58" t="n"/>
     </row>
-    <row r="319">
+    <row r="319" s="60">
       <c r="B319" s="79" t="n"/>
       <c r="C319" s="58" t="n">
         <v>24031</v>
@@ -12860,7 +12481,7 @@
       <c r="H319" s="58" t="n"/>
       <c r="I319" s="58" t="n"/>
     </row>
-    <row r="320">
+    <row r="320" s="60">
       <c r="B320" s="79" t="n"/>
       <c r="C320" s="58" t="n"/>
       <c r="D320" s="58" t="inlineStr">
@@ -12876,7 +12497,7 @@
       <c r="H320" s="58" t="n"/>
       <c r="I320" s="58" t="n"/>
     </row>
-    <row r="321">
+    <row r="321" s="60">
       <c r="B321" s="79" t="n"/>
       <c r="C321" s="58" t="n">
         <v>24041</v>
@@ -12900,7 +12521,7 @@
       <c r="H321" s="58" t="n"/>
       <c r="I321" s="58" t="n"/>
     </row>
-    <row r="322">
+    <row r="322" s="60">
       <c r="B322" s="79" t="n"/>
       <c r="C322" s="58" t="n"/>
       <c r="D322" s="58" t="inlineStr">
@@ -12916,7 +12537,7 @@
       <c r="H322" s="58" t="n"/>
       <c r="I322" s="58" t="n"/>
     </row>
-    <row r="323">
+    <row r="323" s="60">
       <c r="B323" s="79" t="n"/>
       <c r="C323" s="58" t="n"/>
       <c r="D323" s="58" t="inlineStr">
@@ -12932,7 +12553,7 @@
       <c r="H323" s="58" t="n"/>
       <c r="I323" s="58" t="n"/>
     </row>
-    <row r="324">
+    <row r="324" s="60">
       <c r="B324" s="79" t="n"/>
       <c r="C324" s="58" t="n">
         <v>24019</v>
@@ -12956,7 +12577,7 @@
       <c r="H324" s="58" t="n"/>
       <c r="I324" s="58" t="n"/>
     </row>
-    <row r="325">
+    <row r="325" s="60">
       <c r="B325" s="79" t="n"/>
       <c r="C325" s="58" t="n"/>
       <c r="D325" s="58" t="inlineStr">
@@ -12972,7 +12593,7 @@
       <c r="H325" s="58" t="n"/>
       <c r="I325" s="58" t="n"/>
     </row>
-    <row r="326">
+    <row r="326" s="60">
       <c r="B326" s="79" t="n"/>
       <c r="C326" s="58" t="n"/>
       <c r="D326" s="58" t="inlineStr">
@@ -12988,7 +12609,7 @@
       <c r="H326" s="58" t="n"/>
       <c r="I326" s="58" t="n"/>
     </row>
-    <row r="327">
+    <row r="327" s="60">
       <c r="B327" s="79" t="n"/>
       <c r="C327" s="58" t="n">
         <v>24020</v>
@@ -13012,7 +12633,7 @@
       <c r="H327" s="58" t="n"/>
       <c r="I327" s="58" t="n"/>
     </row>
-    <row r="328">
+    <row r="328" s="60">
       <c r="B328" s="79" t="n"/>
       <c r="C328" s="58" t="n"/>
       <c r="D328" s="58" t="inlineStr">
@@ -13028,7 +12649,7 @@
       <c r="H328" s="58" t="n"/>
       <c r="I328" s="58" t="n"/>
     </row>
-    <row r="329">
+    <row r="329" s="60">
       <c r="B329" s="79" t="n"/>
       <c r="C329" s="58" t="n"/>
       <c r="D329" s="58" t="inlineStr">
@@ -13044,7 +12665,7 @@
       <c r="H329" s="58" t="n"/>
       <c r="I329" s="58" t="n"/>
     </row>
-    <row r="330">
+    <row r="330" s="60">
       <c r="B330" s="79" t="n"/>
       <c r="C330" s="58" t="n">
         <v>24021</v>
@@ -13068,7 +12689,7 @@
       <c r="H330" s="58" t="n"/>
       <c r="I330" s="58" t="n"/>
     </row>
-    <row r="331">
+    <row r="331" s="60">
       <c r="B331" s="79" t="n"/>
       <c r="C331" s="58" t="n"/>
       <c r="D331" s="58" t="inlineStr">
@@ -13084,7 +12705,7 @@
       <c r="H331" s="58" t="n"/>
       <c r="I331" s="58" t="n"/>
     </row>
-    <row r="332">
+    <row r="332" s="60">
       <c r="B332" s="79" t="n"/>
       <c r="C332" s="58" t="n"/>
       <c r="D332" s="58" t="inlineStr">
@@ -13100,7 +12721,7 @@
       <c r="H332" s="58" t="n"/>
       <c r="I332" s="58" t="n"/>
     </row>
-    <row r="333">
+    <row r="333" s="60">
       <c r="B333" s="79" t="n"/>
       <c r="C333" s="58" t="n"/>
       <c r="D333" s="58" t="inlineStr">
@@ -13116,7 +12737,7 @@
       <c r="H333" s="58" t="n"/>
       <c r="I333" s="58" t="n"/>
     </row>
-    <row r="334">
+    <row r="334" s="60">
       <c r="B334" s="79" t="n"/>
       <c r="C334" s="58" t="n"/>
       <c r="D334" s="58" t="inlineStr">
@@ -13132,7 +12753,7 @@
       <c r="H334" s="58" t="n"/>
       <c r="I334" s="58" t="n"/>
     </row>
-    <row r="335">
+    <row r="335" s="60">
       <c r="B335" s="79" t="n"/>
       <c r="C335" s="58" t="n">
         <v>24003</v>
@@ -13156,7 +12777,7 @@
       <c r="H335" s="58" t="n"/>
       <c r="I335" s="58" t="n"/>
     </row>
-    <row r="336">
+    <row r="336" s="60">
       <c r="B336" s="79" t="n"/>
       <c r="C336" s="58" t="n"/>
       <c r="D336" s="58" t="inlineStr">
@@ -13172,7 +12793,7 @@
       <c r="H336" s="58" t="n"/>
       <c r="I336" s="58" t="n"/>
     </row>
-    <row r="337">
+    <row r="337" s="60">
       <c r="B337" s="79" t="n"/>
       <c r="C337" s="58" t="n"/>
       <c r="D337" s="58" t="inlineStr">
@@ -13188,7 +12809,7 @@
       <c r="H337" s="58" t="n"/>
       <c r="I337" s="58" t="n"/>
     </row>
-    <row r="338">
+    <row r="338" s="60">
       <c r="B338" s="79" t="n"/>
       <c r="C338" s="58" t="n"/>
       <c r="D338" s="58" t="inlineStr">
@@ -13204,7 +12825,7 @@
       <c r="H338" s="58" t="n"/>
       <c r="I338" s="58" t="n"/>
     </row>
-    <row r="339">
+    <row r="339" s="60">
       <c r="B339" s="79" t="n"/>
       <c r="C339" s="58" t="n">
         <v>24008</v>
@@ -13228,7 +12849,7 @@
       <c r="H339" s="58" t="n"/>
       <c r="I339" s="58" t="n"/>
     </row>
-    <row r="340">
+    <row r="340" s="60">
       <c r="B340" s="79" t="n"/>
       <c r="C340" s="58" t="n"/>
       <c r="D340" s="58" t="inlineStr">
@@ -13244,7 +12865,7 @@
       <c r="H340" s="58" t="n"/>
       <c r="I340" s="58" t="n"/>
     </row>
-    <row r="341">
+    <row r="341" s="60">
       <c r="B341" s="79" t="n"/>
       <c r="C341" s="58" t="n"/>
       <c r="D341" s="58" t="inlineStr">
@@ -13260,7 +12881,7 @@
       <c r="H341" s="58" t="n"/>
       <c r="I341" s="58" t="n"/>
     </row>
-    <row r="342">
+    <row r="342" s="60">
       <c r="B342" s="79" t="n"/>
       <c r="C342" s="58" t="n"/>
       <c r="D342" s="58" t="inlineStr">
@@ -13276,7 +12897,7 @@
       <c r="H342" s="58" t="n"/>
       <c r="I342" s="58" t="n"/>
     </row>
-    <row r="343">
+    <row r="343" s="60">
       <c r="B343" s="79" t="n"/>
       <c r="C343" s="58" t="n"/>
       <c r="D343" s="58" t="inlineStr">
@@ -13292,7 +12913,7 @@
       <c r="H343" s="58" t="n"/>
       <c r="I343" s="58" t="n"/>
     </row>
-    <row r="344">
+    <row r="344" s="60">
       <c r="B344" s="79" t="n"/>
       <c r="C344" s="58" t="n"/>
       <c r="D344" s="58" t="inlineStr">
@@ -13308,7 +12929,7 @@
       <c r="H344" s="58" t="n"/>
       <c r="I344" s="58" t="n"/>
     </row>
-    <row r="345">
+    <row r="345" s="60">
       <c r="B345" s="79" t="n"/>
       <c r="C345" s="58" t="n"/>
       <c r="D345" s="58" t="inlineStr">
@@ -13324,7 +12945,7 @@
       <c r="H345" s="58" t="n"/>
       <c r="I345" s="58" t="n"/>
     </row>
-    <row r="346">
+    <row r="346" s="60">
       <c r="B346" s="79" t="n"/>
       <c r="C346" s="58" t="n">
         <v>24022</v>
@@ -13348,7 +12969,7 @@
       <c r="H346" s="58" t="n"/>
       <c r="I346" s="58" t="n"/>
     </row>
-    <row r="347">
+    <row r="347" s="60">
       <c r="B347" s="79" t="n"/>
       <c r="C347" s="58" t="n"/>
       <c r="D347" s="58" t="inlineStr">
@@ -13364,7 +12985,7 @@
       <c r="H347" s="58" t="n"/>
       <c r="I347" s="58" t="n"/>
     </row>
-    <row r="348">
+    <row r="348" s="60">
       <c r="B348" s="79" t="n"/>
       <c r="C348" s="58" t="n"/>
       <c r="D348" s="58" t="inlineStr">
@@ -13380,7 +13001,7 @@
       <c r="H348" s="58" t="n"/>
       <c r="I348" s="58" t="n"/>
     </row>
-    <row r="349">
+    <row r="349" s="60">
       <c r="B349" s="79" t="n"/>
       <c r="C349" s="58" t="n">
         <v>24005</v>
@@ -13404,7 +13025,7 @@
       <c r="H349" s="58" t="n"/>
       <c r="I349" s="58" t="n"/>
     </row>
-    <row r="350">
+    <row r="350" s="60">
       <c r="B350" s="79" t="n"/>
       <c r="C350" s="58" t="n"/>
       <c r="D350" s="58" t="inlineStr">
@@ -13420,7 +13041,7 @@
       <c r="H350" s="58" t="n"/>
       <c r="I350" s="58" t="n"/>
     </row>
-    <row r="351">
+    <row r="351" s="60">
       <c r="B351" s="79" t="n"/>
       <c r="C351" s="58" t="n">
         <v>24023</v>
@@ -13444,7 +13065,7 @@
       <c r="H351" s="58" t="n"/>
       <c r="I351" s="58" t="n"/>
     </row>
-    <row r="352">
+    <row r="352" s="60">
       <c r="B352" s="79" t="n"/>
       <c r="C352" s="58" t="n"/>
       <c r="D352" s="58" t="inlineStr">
@@ -13460,7 +13081,7 @@
       <c r="H352" s="58" t="n"/>
       <c r="I352" s="58" t="n"/>
     </row>
-    <row r="353">
+    <row r="353" s="60">
       <c r="B353" s="79" t="n"/>
       <c r="C353" s="58" t="n"/>
       <c r="D353" s="58" t="inlineStr">
@@ -13476,7 +13097,7 @@
       <c r="H353" s="58" t="n"/>
       <c r="I353" s="58" t="n"/>
     </row>
-    <row r="354">
+    <row r="354" s="60">
       <c r="B354" s="79" t="n"/>
       <c r="C354" s="58" t="n"/>
       <c r="D354" s="58" t="inlineStr">
@@ -13492,7 +13113,7 @@
       <c r="H354" s="58" t="n"/>
       <c r="I354" s="58" t="n"/>
     </row>
-    <row r="355">
+    <row r="355" s="60">
       <c r="B355" s="79" t="n"/>
       <c r="C355" s="58" t="n">
         <v>24024</v>
@@ -13516,7 +13137,7 @@
       <c r="H355" s="58" t="n"/>
       <c r="I355" s="58" t="n"/>
     </row>
-    <row r="356">
+    <row r="356" s="60">
       <c r="B356" s="79" t="n"/>
       <c r="C356" s="58" t="n"/>
       <c r="D356" s="58" t="inlineStr">
@@ -13532,7 +13153,7 @@
       <c r="H356" s="58" t="n"/>
       <c r="I356" s="58" t="n"/>
     </row>
-    <row r="357">
+    <row r="357" s="60">
       <c r="B357" s="79" t="n"/>
       <c r="C357" s="58" t="n"/>
       <c r="D357" s="58" t="inlineStr">
@@ -13548,7 +13169,7 @@
       <c r="H357" s="58" t="n"/>
       <c r="I357" s="58" t="n"/>
     </row>
-    <row r="358">
+    <row r="358" s="60">
       <c r="B358" s="79" t="n"/>
       <c r="C358" s="58" t="n">
         <v>24025</v>
@@ -13572,7 +13193,7 @@
       <c r="H358" s="58" t="n"/>
       <c r="I358" s="58" t="n"/>
     </row>
-    <row r="359">
+    <row r="359" s="60">
       <c r="B359" s="79" t="n"/>
       <c r="C359" s="58" t="n"/>
       <c r="D359" s="58" t="inlineStr">
@@ -13588,7 +13209,7 @@
       <c r="H359" s="58" t="n"/>
       <c r="I359" s="58" t="n"/>
     </row>
-    <row r="360">
+    <row r="360" s="60">
       <c r="B360" s="79" t="n"/>
       <c r="C360" s="58" t="n"/>
       <c r="D360" s="58" t="inlineStr">
@@ -13604,7 +13225,7 @@
       <c r="H360" s="58" t="n"/>
       <c r="I360" s="58" t="n"/>
     </row>
-    <row r="361">
+    <row r="361" s="60">
       <c r="B361" s="79" t="n"/>
       <c r="C361" s="58" t="n"/>
       <c r="D361" s="58" t="inlineStr">
@@ -13620,7 +13241,7 @@
       <c r="H361" s="58" t="n"/>
       <c r="I361" s="58" t="n"/>
     </row>
-    <row r="362">
+    <row r="362" s="60">
       <c r="B362" s="79" t="n"/>
       <c r="C362" s="58" t="n"/>
       <c r="D362" s="58" t="inlineStr">
@@ -13636,7 +13257,7 @@
       <c r="H362" s="58" t="n"/>
       <c r="I362" s="58" t="n"/>
     </row>
-    <row r="363">
+    <row r="363" s="60">
       <c r="B363" s="79" t="n"/>
       <c r="C363" s="58" t="n">
         <v>24026</v>
@@ -13660,7 +13281,7 @@
       <c r="H363" s="58" t="n"/>
       <c r="I363" s="58" t="n"/>
     </row>
-    <row r="364">
+    <row r="364" s="60">
       <c r="B364" s="79" t="n"/>
       <c r="C364" s="58" t="n"/>
       <c r="D364" s="58" t="inlineStr">
@@ -13676,7 +13297,7 @@
       <c r="H364" s="58" t="n"/>
       <c r="I364" s="58" t="n"/>
     </row>
-    <row r="365">
+    <row r="365" s="60">
       <c r="B365" s="79" t="n"/>
       <c r="C365" s="58" t="n"/>
       <c r="D365" s="58" t="inlineStr">
@@ -13692,7 +13313,7 @@
       <c r="H365" s="58" t="n"/>
       <c r="I365" s="58" t="n"/>
     </row>
-    <row r="366">
+    <row r="366" s="60">
       <c r="B366" s="79" t="n"/>
       <c r="C366" s="58" t="n">
         <v>24027</v>
@@ -13716,7 +13337,7 @@
       <c r="H366" s="58" t="n"/>
       <c r="I366" s="58" t="n"/>
     </row>
-    <row r="367">
+    <row r="367" s="60">
       <c r="B367" s="79" t="n"/>
       <c r="C367" s="58" t="n"/>
       <c r="D367" s="58" t="inlineStr">
@@ -13732,7 +13353,7 @@
       <c r="H367" s="58" t="n"/>
       <c r="I367" s="58" t="n"/>
     </row>
-    <row r="368">
+    <row r="368" s="60">
       <c r="B368" s="79" t="n"/>
       <c r="C368" s="58" t="n">
         <v>24028</v>
@@ -13756,7 +13377,7 @@
       <c r="H368" s="58" t="n"/>
       <c r="I368" s="58" t="n"/>
     </row>
-    <row r="369">
+    <row r="369" s="60">
       <c r="B369" s="79" t="n"/>
       <c r="C369" s="58" t="n"/>
       <c r="D369" s="58" t="inlineStr">
@@ -13772,7 +13393,7 @@
       <c r="H369" s="58" t="n"/>
       <c r="I369" s="58" t="n"/>
     </row>
-    <row r="370">
+    <row r="370" s="60">
       <c r="B370" s="79" t="n"/>
       <c r="C370" s="58" t="n"/>
       <c r="D370" s="58" t="inlineStr">
@@ -13788,7 +13409,7 @@
       <c r="H370" s="58" t="n"/>
       <c r="I370" s="58" t="n"/>
     </row>
-    <row r="371">
+    <row r="371" s="60">
       <c r="B371" s="79" t="n"/>
       <c r="C371" s="58" t="n">
         <v>24600</v>
@@ -13812,7 +13433,7 @@
       <c r="H371" s="58" t="n"/>
       <c r="I371" s="58" t="n"/>
     </row>
-    <row r="372">
+    <row r="372" s="60">
       <c r="B372" s="79" t="n"/>
       <c r="C372" s="58" t="n"/>
       <c r="D372" s="58" t="inlineStr">
@@ -13828,7 +13449,7 @@
       <c r="H372" s="58" t="n"/>
       <c r="I372" s="58" t="n"/>
     </row>
-    <row r="373">
+    <row r="373" s="60">
       <c r="B373" s="79" t="n"/>
       <c r="C373" s="58" t="n"/>
       <c r="D373" s="58" t="inlineStr">
@@ -13844,7 +13465,7 @@
       <c r="H373" s="58" t="n"/>
       <c r="I373" s="58" t="n"/>
     </row>
-    <row r="374">
+    <row r="374" s="60">
       <c r="B374" s="79" t="n"/>
       <c r="C374" s="58" t="n"/>
       <c r="D374" s="58" t="inlineStr">
@@ -13860,7 +13481,7 @@
       <c r="H374" s="58" t="n"/>
       <c r="I374" s="58" t="n"/>
     </row>
-    <row r="375">
+    <row r="375" s="60">
       <c r="B375" s="79" t="n"/>
       <c r="C375" s="58" t="n">
         <v>24300</v>
@@ -13884,7 +13505,7 @@
       <c r="H375" s="58" t="n"/>
       <c r="I375" s="58" t="n"/>
     </row>
-    <row r="376">
+    <row r="376" s="60">
       <c r="B376" s="79" t="n"/>
       <c r="C376" s="58" t="n"/>
       <c r="D376" s="58" t="inlineStr">
@@ -13900,7 +13521,7 @@
       <c r="H376" s="58" t="n"/>
       <c r="I376" s="58" t="n"/>
     </row>
-    <row r="377">
+    <row r="377" s="60">
       <c r="B377" s="79" t="n"/>
       <c r="C377" s="58" t="n">
         <v>24030</v>
@@ -13924,7 +13545,7 @@
       <c r="H377" s="58" t="n"/>
       <c r="I377" s="58" t="n"/>
     </row>
-    <row r="378">
+    <row r="378" s="60">
       <c r="B378" s="79" t="n"/>
       <c r="C378" s="58" t="n"/>
       <c r="D378" s="58" t="inlineStr">
@@ -13940,7 +13561,7 @@
       <c r="H378" s="58" t="n"/>
       <c r="I378" s="58" t="n"/>
     </row>
-    <row r="379">
+    <row r="379" s="60">
       <c r="B379" s="79" t="n"/>
       <c r="C379" s="58" t="n"/>
       <c r="D379" s="58" t="inlineStr">
@@ -13956,7 +13577,7 @@
       <c r="H379" s="58" t="n"/>
       <c r="I379" s="58" t="n"/>
     </row>
-    <row r="380">
+    <row r="380" s="60">
       <c r="B380" s="79" t="n"/>
       <c r="C380" s="58" t="n"/>
       <c r="D380" s="58" t="inlineStr">
@@ -13972,7 +13593,7 @@
       <c r="H380" s="58" t="n"/>
       <c r="I380" s="58" t="n"/>
     </row>
-    <row r="381">
+    <row r="381" s="60">
       <c r="B381" s="79" t="n"/>
       <c r="C381" s="58" t="n"/>
       <c r="D381" s="58" t="inlineStr">
@@ -13988,7 +13609,7 @@
       <c r="H381" s="58" t="n"/>
       <c r="I381" s="58" t="n"/>
     </row>
-    <row r="382">
+    <row r="382" s="60">
       <c r="B382" s="79" t="n"/>
       <c r="C382" s="58" t="n"/>
       <c r="D382" s="58" t="inlineStr">
@@ -14004,7 +13625,7 @@
       <c r="H382" s="58" t="n"/>
       <c r="I382" s="58" t="n"/>
     </row>
-    <row r="383">
+    <row r="383" s="60">
       <c r="B383" s="79" t="n"/>
       <c r="C383" s="58" t="n">
         <v>24032</v>
@@ -14028,7 +13649,7 @@
       <c r="H383" s="58" t="n"/>
       <c r="I383" s="58" t="n"/>
     </row>
-    <row r="384">
+    <row r="384" s="60">
       <c r="B384" s="79" t="n"/>
       <c r="C384" s="58" t="n"/>
       <c r="D384" s="58" t="inlineStr">
@@ -14044,7 +13665,7 @@
       <c r="H384" s="58" t="n"/>
       <c r="I384" s="58" t="n"/>
     </row>
-    <row r="385">
+    <row r="385" s="60">
       <c r="B385" s="79" t="n"/>
       <c r="C385" s="58" t="n"/>
       <c r="D385" s="58" t="inlineStr">
@@ -14060,7 +13681,7 @@
       <c r="H385" s="58" t="n"/>
       <c r="I385" s="58" t="n"/>
     </row>
-    <row r="386">
+    <row r="386" s="60">
       <c r="B386" s="79" t="n"/>
       <c r="C386" s="58" t="n"/>
       <c r="D386" s="58" t="inlineStr">
@@ -14076,7 +13697,7 @@
       <c r="H386" s="58" t="n"/>
       <c r="I386" s="58" t="n"/>
     </row>
-    <row r="387">
+    <row r="387" s="60">
       <c r="B387" s="79" t="n"/>
       <c r="C387" s="58" t="n">
         <v>24042</v>
@@ -14100,7 +13721,7 @@
       <c r="H387" s="58" t="n"/>
       <c r="I387" s="58" t="n"/>
     </row>
-    <row r="388">
+    <row r="388" s="60">
       <c r="B388" s="79" t="n"/>
       <c r="C388" s="58" t="n"/>
       <c r="D388" s="58" t="inlineStr">
@@ -14116,7 +13737,7 @@
       <c r="H388" s="58" t="n"/>
       <c r="I388" s="58" t="n"/>
     </row>
-    <row r="389">
+    <row r="389" s="60">
       <c r="B389" s="79" t="n"/>
       <c r="C389" s="58" t="n"/>
       <c r="D389" s="58" t="inlineStr">
@@ -14132,7 +13753,7 @@
       <c r="H389" s="58" t="n"/>
       <c r="I389" s="58" t="n"/>
     </row>
-    <row r="390">
+    <row r="390" s="60">
       <c r="B390" s="79" t="n"/>
       <c r="C390" s="58" t="n">
         <v>24033</v>
@@ -14156,7 +13777,7 @@
       <c r="H390" s="58" t="n"/>
       <c r="I390" s="58" t="n"/>
     </row>
-    <row r="391">
+    <row r="391" s="60">
       <c r="B391" s="79" t="n"/>
       <c r="C391" s="58" t="n"/>
       <c r="D391" s="58" t="inlineStr">
@@ -14172,7 +13793,7 @@
       <c r="H391" s="58" t="n"/>
       <c r="I391" s="58" t="n"/>
     </row>
-    <row r="392">
+    <row r="392" s="60">
       <c r="B392" s="79" t="n"/>
       <c r="C392" s="58" t="n"/>
       <c r="D392" s="58" t="inlineStr">
@@ -14188,7 +13809,7 @@
       <c r="H392" s="58" t="n"/>
       <c r="I392" s="58" t="n"/>
     </row>
-    <row r="393">
+    <row r="393" s="60">
       <c r="B393" s="79" t="n"/>
       <c r="C393" s="58" t="n"/>
       <c r="D393" s="58" t="inlineStr">
@@ -14204,7 +13825,7 @@
       <c r="H393" s="58" t="n"/>
       <c r="I393" s="58" t="n"/>
     </row>
-    <row r="394">
+    <row r="394" s="60">
       <c r="B394" s="79" t="n"/>
       <c r="C394" s="58" t="n"/>
       <c r="D394" s="58" t="inlineStr">
@@ -14220,7 +13841,7 @@
       <c r="H394" s="58" t="n"/>
       <c r="I394" s="58" t="n"/>
     </row>
-    <row r="395">
+    <row r="395" s="60">
       <c r="B395" s="79" t="n"/>
       <c r="C395" s="58" t="n">
         <v>24034</v>
@@ -14244,7 +13865,7 @@
       <c r="H395" s="58" t="n"/>
       <c r="I395" s="58" t="n"/>
     </row>
-    <row r="396">
+    <row r="396" s="60">
       <c r="B396" s="79" t="n"/>
       <c r="C396" s="58" t="n"/>
       <c r="D396" s="58" t="inlineStr">
@@ -14260,7 +13881,7 @@
       <c r="H396" s="58" t="n"/>
       <c r="I396" s="58" t="n"/>
     </row>
-    <row r="397">
+    <row r="397" s="60">
       <c r="B397" s="79" t="n"/>
       <c r="C397" s="58" t="n"/>
       <c r="D397" s="58" t="inlineStr">
@@ -14276,7 +13897,7 @@
       <c r="H397" s="58" t="n"/>
       <c r="I397" s="58" t="n"/>
     </row>
-    <row r="398">
+    <row r="398" s="60">
       <c r="B398" s="79" t="n"/>
       <c r="C398" s="58" t="n"/>
       <c r="D398" s="58" t="inlineStr">
@@ -14292,7 +13913,7 @@
       <c r="H398" s="58" t="n"/>
       <c r="I398" s="58" t="n"/>
     </row>
-    <row r="399">
+    <row r="399" s="60">
       <c r="B399" s="79" t="n"/>
       <c r="C399" s="58" t="n">
         <v>24035</v>
@@ -14316,7 +13937,7 @@
       <c r="H399" s="58" t="n"/>
       <c r="I399" s="58" t="n"/>
     </row>
-    <row r="400">
+    <row r="400" s="60">
       <c r="B400" s="79" t="n"/>
       <c r="C400" s="58" t="n"/>
       <c r="D400" s="58" t="inlineStr">
@@ -14332,7 +13953,7 @@
       <c r="H400" s="58" t="n"/>
       <c r="I400" s="58" t="n"/>
     </row>
-    <row r="401">
+    <row r="401" s="60">
       <c r="B401" s="79" t="n"/>
       <c r="C401" s="58" t="n"/>
       <c r="D401" s="58" t="inlineStr">
@@ -14348,7 +13969,7 @@
       <c r="H401" s="58" t="n"/>
       <c r="I401" s="58" t="n"/>
     </row>
-    <row r="402">
+    <row r="402" s="60">
       <c r="B402" s="79" t="n"/>
       <c r="C402" s="58" t="n">
         <v>24036</v>
@@ -14372,7 +13993,7 @@
       <c r="H402" s="58" t="n"/>
       <c r="I402" s="58" t="n"/>
     </row>
-    <row r="403">
+    <row r="403" s="60">
       <c r="B403" s="79" t="n"/>
       <c r="C403" s="58" t="n"/>
       <c r="D403" s="58" t="inlineStr">
@@ -14388,7 +14009,7 @@
       <c r="H403" s="58" t="n"/>
       <c r="I403" s="58" t="n"/>
     </row>
-    <row r="404">
+    <row r="404" s="60">
       <c r="B404" s="79" t="n"/>
       <c r="C404" s="58" t="n"/>
       <c r="D404" s="58" t="inlineStr">
@@ -14404,7 +14025,7 @@
       <c r="H404" s="58" t="n"/>
       <c r="I404" s="58" t="n"/>
     </row>
-    <row r="405">
+    <row r="405" s="60">
       <c r="B405" s="79" t="n"/>
       <c r="C405" s="58" t="n">
         <v>24601</v>
@@ -14428,7 +14049,7 @@
       <c r="H405" s="58" t="n"/>
       <c r="I405" s="58" t="n"/>
     </row>
-    <row r="406">
+    <row r="406" s="60">
       <c r="B406" s="79" t="n"/>
       <c r="C406" s="58" t="n"/>
       <c r="D406" s="58" t="inlineStr">
@@ -14444,7 +14065,7 @@
       <c r="H406" s="58" t="n"/>
       <c r="I406" s="58" t="n"/>
     </row>
-    <row r="407">
+    <row r="407" s="60">
       <c r="B407" s="79" t="n"/>
       <c r="C407" s="58" t="n"/>
       <c r="D407" s="58" t="inlineStr">
@@ -14460,7 +14081,7 @@
       <c r="H407" s="58" t="n"/>
       <c r="I407" s="58" t="n"/>
     </row>
-    <row r="408">
+    <row r="408" s="60">
       <c r="B408" s="79" t="n"/>
       <c r="C408" s="58" t="n"/>
       <c r="D408" s="58" t="inlineStr">
@@ -14476,7 +14097,7 @@
       <c r="H408" s="58" t="n"/>
       <c r="I408" s="58" t="n"/>
     </row>
-    <row r="409">
+    <row r="409" s="60">
       <c r="B409" s="79" t="n"/>
       <c r="C409" s="58" t="n">
         <v>24037</v>
@@ -14500,7 +14121,7 @@
       <c r="H409" s="58" t="n"/>
       <c r="I409" s="58" t="n"/>
     </row>
-    <row r="410">
+    <row r="410" s="60">
       <c r="B410" s="79" t="n"/>
       <c r="C410" s="58" t="n"/>
       <c r="D410" s="58" t="inlineStr">
@@ -14516,7 +14137,7 @@
       <c r="H410" s="58" t="n"/>
       <c r="I410" s="58" t="n"/>
     </row>
-    <row r="411">
+    <row r="411" s="60">
       <c r="B411" s="79" t="n"/>
       <c r="C411" s="58" t="n"/>
       <c r="D411" s="58" t="inlineStr">
@@ -14532,7 +14153,7 @@
       <c r="H411" s="58" t="n"/>
       <c r="I411" s="58" t="n"/>
     </row>
-    <row r="412">
+    <row r="412" s="60">
       <c r="B412" s="79" t="n"/>
       <c r="C412" s="58" t="n"/>
       <c r="D412" s="58" t="inlineStr">
@@ -14548,7 +14169,7 @@
       <c r="H412" s="58" t="n"/>
       <c r="I412" s="58" t="n"/>
     </row>
-    <row r="413">
+    <row r="413" s="60">
       <c r="B413" s="79" t="n"/>
       <c r="C413" s="58" t="n"/>
       <c r="D413" s="58" t="inlineStr">
@@ -14564,7 +14185,7 @@
       <c r="H413" s="58" t="n"/>
       <c r="I413" s="58" t="n"/>
     </row>
-    <row r="414">
+    <row r="414" s="60">
       <c r="B414" s="79" t="n"/>
       <c r="C414" s="58" t="n"/>
       <c r="D414" s="58" t="inlineStr">
@@ -14580,7 +14201,7 @@
       <c r="H414" s="58" t="n"/>
       <c r="I414" s="58" t="n"/>
     </row>
-    <row r="415">
+    <row r="415" s="60">
       <c r="B415" s="79" t="n"/>
       <c r="C415" s="58" t="n">
         <v>24038</v>
@@ -14604,7 +14225,7 @@
       <c r="H415" s="58" t="n"/>
       <c r="I415" s="58" t="n"/>
     </row>
-    <row r="416">
+    <row r="416" s="60">
       <c r="B416" s="79" t="n"/>
       <c r="C416" s="58" t="n"/>
       <c r="D416" s="58" t="inlineStr">
@@ -14620,7 +14241,7 @@
       <c r="H416" s="58" t="n"/>
       <c r="I416" s="58" t="n"/>
     </row>
-    <row r="417">
+    <row r="417" s="60">
       <c r="B417" s="79" t="n"/>
       <c r="C417" s="58" t="n"/>
       <c r="D417" s="58" t="inlineStr">
@@ -14636,7 +14257,7 @@
       <c r="H417" s="58" t="n"/>
       <c r="I417" s="58" t="n"/>
     </row>
-    <row r="418">
+    <row r="418" s="60">
       <c r="B418" s="79" t="n"/>
       <c r="C418" s="58" t="n">
         <v>24039</v>
@@ -14660,7 +14281,7 @@
       <c r="H418" s="58" t="n"/>
       <c r="I418" s="58" t="n"/>
     </row>
-    <row r="419">
+    <row r="419" s="60">
       <c r="B419" s="79" t="n"/>
       <c r="C419" s="58" t="n"/>
       <c r="D419" s="58" t="inlineStr">
@@ -14676,7 +14297,7 @@
       <c r="H419" s="58" t="n"/>
       <c r="I419" s="58" t="n"/>
     </row>
-    <row r="420">
+    <row r="420" s="60">
       <c r="B420" s="79" t="n"/>
       <c r="C420" s="58" t="n">
         <v>24040</v>
@@ -14700,7 +14321,7 @@
       <c r="H420" s="58" t="n"/>
       <c r="I420" s="58" t="n"/>
     </row>
-    <row r="421">
+    <row r="421" s="60">
       <c r="B421" s="79" t="n"/>
       <c r="C421" s="58" t="n"/>
       <c r="D421" s="58" t="inlineStr">
@@ -14716,7 +14337,7 @@
       <c r="H421" s="58" t="n"/>
       <c r="I421" s="58" t="n"/>
     </row>
-    <row r="422">
+    <row r="422" s="60">
       <c r="B422" s="80" t="n"/>
       <c r="C422" s="58" t="n"/>
       <c r="D422" s="58" t="inlineStr">
@@ -14732,7 +14353,7 @@
       <c r="H422" s="58" t="n"/>
       <c r="I422" s="58" t="n"/>
     </row>
-    <row r="423">
+    <row r="423" s="60">
       <c r="B423" s="58" t="inlineStr">
         <is>
           <t>Above</t>
@@ -14764,7 +14385,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="424">
+    <row r="424" s="60">
       <c r="B424" s="79" t="n"/>
       <c r="C424" s="58" t="n"/>
       <c r="D424" s="58" t="inlineStr">
@@ -14780,7 +14401,7 @@
       <c r="H424" s="58" t="n"/>
       <c r="I424" s="58" t="n"/>
     </row>
-    <row r="425">
+    <row r="425" s="60">
       <c r="B425" s="79" t="n"/>
       <c r="C425" s="58" t="n"/>
       <c r="D425" s="58" t="inlineStr">
@@ -14796,7 +14417,7 @@
       <c r="H425" s="58" t="n"/>
       <c r="I425" s="58" t="n"/>
     </row>
-    <row r="426">
+    <row r="426" s="60">
       <c r="B426" s="79" t="n"/>
       <c r="C426" s="58" t="n">
         <v>25000</v>
@@ -14820,7 +14441,7 @@
       <c r="H426" s="58" t="n"/>
       <c r="I426" s="58" t="n"/>
     </row>
-    <row r="427">
+    <row r="427" s="60">
       <c r="B427" s="79" t="n"/>
       <c r="C427" s="58" t="n"/>
       <c r="D427" s="58" t="inlineStr">
@@ -14836,7 +14457,7 @@
       <c r="H427" s="58" t="n"/>
       <c r="I427" s="58" t="n"/>
     </row>
-    <row r="428">
+    <row r="428" s="60">
       <c r="B428" s="79" t="n"/>
       <c r="C428" s="58" t="n"/>
       <c r="D428" s="58" t="inlineStr">
@@ -14852,7 +14473,7 @@
       <c r="H428" s="58" t="n"/>
       <c r="I428" s="58" t="n"/>
     </row>
-    <row r="429">
+    <row r="429" s="60">
       <c r="B429" s="79" t="n"/>
       <c r="C429" s="58" t="n">
         <v>25001</v>
@@ -14876,7 +14497,7 @@
       <c r="H429" s="58" t="n"/>
       <c r="I429" s="58" t="n"/>
     </row>
-    <row r="430">
+    <row r="430" s="60">
       <c r="B430" s="80" t="n"/>
       <c r="C430" s="58" t="n"/>
       <c r="D430" s="58" t="inlineStr">
@@ -14892,7 +14513,7 @@
       <c r="H430" s="58" t="n"/>
       <c r="I430" s="58" t="n"/>
     </row>
-    <row r="431">
+    <row r="431" s="60">
       <c r="B431" s="58" t="inlineStr">
         <is>
           <t>Silak's Mansion</t>
@@ -14924,7 +14545,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="432">
+    <row r="432" s="60">
       <c r="B432" s="79" t="n"/>
       <c r="C432" s="58" t="n"/>
       <c r="D432" s="58" t="inlineStr">
@@ -14940,7 +14561,7 @@
       <c r="H432" s="58" t="n"/>
       <c r="I432" s="58" t="n"/>
     </row>
-    <row r="433">
+    <row r="433" s="60">
       <c r="B433" s="79" t="n"/>
       <c r="C433" s="58" t="n"/>
       <c r="D433" s="58" t="inlineStr">
@@ -14956,7 +14577,7 @@
       <c r="H433" s="58" t="n"/>
       <c r="I433" s="58" t="n"/>
     </row>
-    <row r="434">
+    <row r="434" s="60">
       <c r="B434" s="79" t="n"/>
       <c r="C434" s="58" t="n"/>
       <c r="D434" s="58" t="inlineStr">
@@ -14972,7 +14593,7 @@
       <c r="H434" s="58" t="n"/>
       <c r="I434" s="58" t="n"/>
     </row>
-    <row r="435">
+    <row r="435" s="60">
       <c r="B435" s="79" t="n"/>
       <c r="C435" s="58" t="n"/>
       <c r="D435" s="58" t="inlineStr">
@@ -14988,7 +14609,7 @@
       <c r="H435" s="58" t="n"/>
       <c r="I435" s="58" t="n"/>
     </row>
-    <row r="436">
+    <row r="436" s="60">
       <c r="B436" s="79" t="n"/>
       <c r="C436" s="58" t="n"/>
       <c r="D436" s="58" t="inlineStr">
@@ -15004,7 +14625,7 @@
       <c r="H436" s="58" t="n"/>
       <c r="I436" s="58" t="n"/>
     </row>
-    <row r="437">
+    <row r="437" s="60">
       <c r="B437" s="79" t="n"/>
       <c r="C437" s="58" t="n"/>
       <c r="D437" s="58" t="inlineStr">
@@ -15020,7 +14641,7 @@
       <c r="H437" s="58" t="n"/>
       <c r="I437" s="58" t="n"/>
     </row>
-    <row r="438">
+    <row r="438" s="60">
       <c r="B438" s="79" t="n"/>
       <c r="C438" s="58" t="n">
         <v>26031</v>
@@ -15044,7 +14665,7 @@
       <c r="H438" s="58" t="n"/>
       <c r="I438" s="58" t="n"/>
     </row>
-    <row r="439">
+    <row r="439" s="60">
       <c r="B439" s="79" t="n"/>
       <c r="C439" s="58" t="n"/>
       <c r="D439" s="58" t="inlineStr">
@@ -15060,7 +14681,7 @@
       <c r="H439" s="58" t="n"/>
       <c r="I439" s="58" t="n"/>
     </row>
-    <row r="440">
+    <row r="440" s="60">
       <c r="B440" s="79" t="n"/>
       <c r="C440" s="58" t="n"/>
       <c r="D440" s="58" t="inlineStr">
@@ -15076,7 +14697,7 @@
       <c r="H440" s="58" t="n"/>
       <c r="I440" s="58" t="n"/>
     </row>
-    <row r="441">
+    <row r="441" s="60">
       <c r="B441" s="79" t="n"/>
       <c r="C441" s="58" t="n">
         <v>26032</v>
@@ -15100,7 +14721,7 @@
       <c r="H441" s="58" t="n"/>
       <c r="I441" s="58" t="n"/>
     </row>
-    <row r="442">
+    <row r="442" s="60">
       <c r="B442" s="79" t="n"/>
       <c r="C442" s="58" t="n"/>
       <c r="D442" s="58" t="inlineStr">
@@ -15116,7 +14737,7 @@
       <c r="H442" s="58" t="n"/>
       <c r="I442" s="58" t="n"/>
     </row>
-    <row r="443">
+    <row r="443" s="60">
       <c r="B443" s="79" t="n"/>
       <c r="C443" s="58" t="n">
         <v>26000</v>
@@ -15140,7 +14761,7 @@
       <c r="H443" s="58" t="n"/>
       <c r="I443" s="58" t="n"/>
     </row>
-    <row r="444">
+    <row r="444" s="60">
       <c r="B444" s="79" t="n"/>
       <c r="C444" s="58" t="n"/>
       <c r="D444" s="58" t="inlineStr">
@@ -15156,7 +14777,7 @@
       <c r="H444" s="58" t="n"/>
       <c r="I444" s="58" t="n"/>
     </row>
-    <row r="445">
+    <row r="445" s="60">
       <c r="B445" s="79" t="n"/>
       <c r="C445" s="58" t="n"/>
       <c r="D445" s="58" t="inlineStr">
@@ -15172,7 +14793,7 @@
       <c r="H445" s="58" t="n"/>
       <c r="I445" s="58" t="n"/>
     </row>
-    <row r="446">
+    <row r="446" s="60">
       <c r="B446" s="79" t="n"/>
       <c r="C446" s="58" t="n">
         <v>26001</v>
@@ -15196,7 +14817,7 @@
       <c r="H446" s="58" t="n"/>
       <c r="I446" s="58" t="n"/>
     </row>
-    <row r="447">
+    <row r="447" s="60">
       <c r="B447" s="79" t="n"/>
       <c r="C447" s="58" t="n"/>
       <c r="D447" s="58" t="inlineStr">
@@ -15212,7 +14833,7 @@
       <c r="H447" s="58" t="n"/>
       <c r="I447" s="58" t="n"/>
     </row>
-    <row r="448">
+    <row r="448" s="60">
       <c r="B448" s="79" t="n"/>
       <c r="C448" s="58" t="n"/>
       <c r="D448" s="58" t="inlineStr">
@@ -15228,7 +14849,7 @@
       <c r="H448" s="58" t="n"/>
       <c r="I448" s="58" t="n"/>
     </row>
-    <row r="449">
+    <row r="449" s="60">
       <c r="B449" s="79" t="n"/>
       <c r="C449" s="58" t="n">
         <v>26002</v>
@@ -15252,7 +14873,7 @@
       <c r="H449" s="58" t="n"/>
       <c r="I449" s="58" t="n"/>
     </row>
-    <row r="450">
+    <row r="450" s="60">
       <c r="B450" s="79" t="n"/>
       <c r="C450" s="58" t="n"/>
       <c r="D450" s="58" t="inlineStr">
@@ -15268,7 +14889,7 @@
       <c r="H450" s="58" t="n"/>
       <c r="I450" s="58" t="n"/>
     </row>
-    <row r="451">
+    <row r="451" s="60">
       <c r="B451" s="79" t="n"/>
       <c r="C451" s="58" t="n"/>
       <c r="D451" s="58" t="inlineStr">
@@ -15284,7 +14905,7 @@
       <c r="H451" s="58" t="n"/>
       <c r="I451" s="58" t="n"/>
     </row>
-    <row r="452">
+    <row r="452" s="60">
       <c r="B452" s="79" t="n"/>
       <c r="C452" s="58" t="n"/>
       <c r="D452" s="58" t="inlineStr">
@@ -15300,7 +14921,7 @@
       <c r="H452" s="58" t="n"/>
       <c r="I452" s="58" t="n"/>
     </row>
-    <row r="453">
+    <row r="453" s="60">
       <c r="B453" s="79" t="n"/>
       <c r="C453" s="58" t="n">
         <v>26003</v>
@@ -15324,7 +14945,7 @@
       <c r="H453" s="58" t="n"/>
       <c r="I453" s="58" t="n"/>
     </row>
-    <row r="454">
+    <row r="454" s="60">
       <c r="B454" s="79" t="n"/>
       <c r="C454" s="58" t="n"/>
       <c r="D454" s="58" t="inlineStr">
@@ -15340,7 +14961,7 @@
       <c r="H454" s="58" t="n"/>
       <c r="I454" s="58" t="n"/>
     </row>
-    <row r="455">
+    <row r="455" s="60">
       <c r="B455" s="79" t="n"/>
       <c r="C455" s="58" t="n">
         <v>26004</v>
@@ -15364,7 +14985,7 @@
       <c r="H455" s="58" t="n"/>
       <c r="I455" s="58" t="n"/>
     </row>
-    <row r="456">
+    <row r="456" s="60">
       <c r="B456" s="79" t="n"/>
       <c r="C456" s="58" t="n"/>
       <c r="D456" s="58" t="inlineStr">
@@ -15380,7 +15001,7 @@
       <c r="H456" s="58" t="n"/>
       <c r="I456" s="58" t="n"/>
     </row>
-    <row r="457">
+    <row r="457" s="60">
       <c r="B457" s="79" t="n"/>
       <c r="C457" s="58" t="n"/>
       <c r="D457" s="58" t="inlineStr">
@@ -15396,7 +15017,7 @@
       <c r="H457" s="58" t="n"/>
       <c r="I457" s="58" t="n"/>
     </row>
-    <row r="458">
+    <row r="458" s="60">
       <c r="B458" s="79" t="n"/>
       <c r="C458" s="58" t="n"/>
       <c r="D458" s="58" t="inlineStr">
@@ -15412,7 +15033,7 @@
       <c r="H458" s="58" t="n"/>
       <c r="I458" s="58" t="n"/>
     </row>
-    <row r="459">
+    <row r="459" s="60">
       <c r="B459" s="79" t="n"/>
       <c r="C459" s="58" t="n"/>
       <c r="D459" s="58" t="inlineStr">
@@ -15428,7 +15049,7 @@
       <c r="H459" s="58" t="n"/>
       <c r="I459" s="58" t="n"/>
     </row>
-    <row r="460">
+    <row r="460" s="60">
       <c r="B460" s="79" t="n"/>
       <c r="C460" s="58" t="n"/>
       <c r="D460" s="58" t="inlineStr">
@@ -15444,7 +15065,7 @@
       <c r="H460" s="58" t="n"/>
       <c r="I460" s="58" t="n"/>
     </row>
-    <row r="461">
+    <row r="461" s="60">
       <c r="B461" s="79" t="n"/>
       <c r="C461" s="58" t="n"/>
       <c r="D461" s="58" t="inlineStr">
@@ -15460,7 +15081,7 @@
       <c r="H461" s="58" t="n"/>
       <c r="I461" s="58" t="n"/>
     </row>
-    <row r="462">
+    <row r="462" s="60">
       <c r="B462" s="79" t="n"/>
       <c r="C462" s="58" t="n">
         <v>26005</v>
@@ -15484,7 +15105,7 @@
       <c r="H462" s="58" t="n"/>
       <c r="I462" s="58" t="n"/>
     </row>
-    <row r="463">
+    <row r="463" s="60">
       <c r="B463" s="79" t="n"/>
       <c r="C463" s="58" t="n"/>
       <c r="D463" s="58" t="inlineStr">
@@ -15500,7 +15121,7 @@
       <c r="H463" s="58" t="n"/>
       <c r="I463" s="58" t="n"/>
     </row>
-    <row r="464">
+    <row r="464" s="60">
       <c r="B464" s="79" t="n"/>
       <c r="C464" s="58" t="n">
         <v>26006</v>
@@ -15524,7 +15145,7 @@
       <c r="H464" s="58" t="n"/>
       <c r="I464" s="58" t="n"/>
     </row>
-    <row r="465">
+    <row r="465" s="60">
       <c r="B465" s="79" t="n"/>
       <c r="C465" s="58" t="n"/>
       <c r="D465" s="58" t="inlineStr">
@@ -15540,7 +15161,7 @@
       <c r="H465" s="58" t="n"/>
       <c r="I465" s="58" t="n"/>
     </row>
-    <row r="466">
+    <row r="466" s="60">
       <c r="B466" s="79" t="n"/>
       <c r="C466" s="58" t="n"/>
       <c r="D466" s="58" t="inlineStr">
@@ -15556,7 +15177,7 @@
       <c r="H466" s="58" t="n"/>
       <c r="I466" s="58" t="n"/>
     </row>
-    <row r="467">
+    <row r="467" s="60">
       <c r="B467" s="79" t="n"/>
       <c r="C467" s="58" t="n"/>
       <c r="D467" s="58" t="inlineStr">
@@ -15572,7 +15193,7 @@
       <c r="H467" s="58" t="n"/>
       <c r="I467" s="58" t="n"/>
     </row>
-    <row r="468">
+    <row r="468" s="60">
       <c r="B468" s="79" t="n"/>
       <c r="C468" s="58" t="n"/>
       <c r="D468" s="58" t="inlineStr">
@@ -15588,7 +15209,7 @@
       <c r="H468" s="58" t="n"/>
       <c r="I468" s="58" t="n"/>
     </row>
-    <row r="469">
+    <row r="469" s="60">
       <c r="B469" s="79" t="n"/>
       <c r="C469" s="58" t="n"/>
       <c r="D469" s="58" t="inlineStr">
@@ -15604,7 +15225,7 @@
       <c r="H469" s="58" t="n"/>
       <c r="I469" s="58" t="n"/>
     </row>
-    <row r="470">
+    <row r="470" s="60">
       <c r="B470" s="79" t="n"/>
       <c r="C470" s="58" t="n">
         <v>26007</v>
@@ -15628,7 +15249,7 @@
       <c r="H470" s="58" t="n"/>
       <c r="I470" s="58" t="n"/>
     </row>
-    <row r="471">
+    <row r="471" s="60">
       <c r="B471" s="79" t="n"/>
       <c r="C471" s="58" t="n"/>
       <c r="D471" s="58" t="inlineStr">
@@ -15644,7 +15265,7 @@
       <c r="H471" s="58" t="n"/>
       <c r="I471" s="58" t="n"/>
     </row>
-    <row r="472">
+    <row r="472" s="60">
       <c r="B472" s="79" t="n"/>
       <c r="C472" s="58" t="n"/>
       <c r="D472" s="58" t="inlineStr">
@@ -15660,7 +15281,7 @@
       <c r="H472" s="58" t="n"/>
       <c r="I472" s="58" t="n"/>
     </row>
-    <row r="473">
+    <row r="473" s="60">
       <c r="B473" s="79" t="n"/>
       <c r="C473" s="58" t="n"/>
       <c r="D473" s="58" t="inlineStr">
@@ -15676,7 +15297,7 @@
       <c r="H473" s="58" t="n"/>
       <c r="I473" s="58" t="n"/>
     </row>
-    <row r="474">
+    <row r="474" s="60">
       <c r="B474" s="79" t="n"/>
       <c r="C474" s="58" t="n">
         <v>26008</v>
@@ -15700,7 +15321,7 @@
       <c r="H474" s="58" t="n"/>
       <c r="I474" s="58" t="n"/>
     </row>
-    <row r="475">
+    <row r="475" s="60">
       <c r="B475" s="79" t="n"/>
       <c r="C475" s="58" t="n"/>
       <c r="D475" s="58" t="inlineStr">
@@ -15716,7 +15337,7 @@
       <c r="H475" s="58" t="n"/>
       <c r="I475" s="58" t="n"/>
     </row>
-    <row r="476">
+    <row r="476" s="60">
       <c r="B476" s="79" t="n"/>
       <c r="C476" s="58" t="n"/>
       <c r="D476" s="58" t="inlineStr">
@@ -15732,7 +15353,7 @@
       <c r="H476" s="58" t="n"/>
       <c r="I476" s="58" t="n"/>
     </row>
-    <row r="477">
+    <row r="477" s="60">
       <c r="B477" s="79" t="n"/>
       <c r="C477" s="58" t="n"/>
       <c r="D477" s="58" t="inlineStr">
@@ -15748,7 +15369,7 @@
       <c r="H477" s="58" t="n"/>
       <c r="I477" s="58" t="n"/>
     </row>
-    <row r="478">
+    <row r="478" s="60">
       <c r="B478" s="79" t="n"/>
       <c r="C478" s="58" t="n"/>
       <c r="D478" s="58" t="inlineStr">
@@ -15764,7 +15385,7 @@
       <c r="H478" s="58" t="n"/>
       <c r="I478" s="58" t="n"/>
     </row>
-    <row r="479">
+    <row r="479" s="60">
       <c r="B479" s="79" t="n"/>
       <c r="C479" s="58" t="n"/>
       <c r="D479" s="58" t="inlineStr">
@@ -15780,7 +15401,7 @@
       <c r="H479" s="58" t="n"/>
       <c r="I479" s="58" t="n"/>
     </row>
-    <row r="480">
+    <row r="480" s="60">
       <c r="B480" s="79" t="n"/>
       <c r="C480" s="58" t="n">
         <v>26009</v>
@@ -15804,7 +15425,7 @@
       <c r="H480" s="58" t="n"/>
       <c r="I480" s="58" t="n"/>
     </row>
-    <row r="481">
+    <row r="481" s="60">
       <c r="B481" s="79" t="n"/>
       <c r="C481" s="58" t="n"/>
       <c r="D481" s="58" t="inlineStr">
@@ -15820,7 +15441,7 @@
       <c r="H481" s="58" t="n"/>
       <c r="I481" s="58" t="n"/>
     </row>
-    <row r="482">
+    <row r="482" s="60">
       <c r="B482" s="79" t="n"/>
       <c r="C482" s="58" t="n"/>
       <c r="D482" s="58" t="inlineStr">
@@ -15836,7 +15457,7 @@
       <c r="H482" s="58" t="n"/>
       <c r="I482" s="58" t="n"/>
     </row>
-    <row r="483">
+    <row r="483" s="60">
       <c r="B483" s="79" t="n"/>
       <c r="C483" s="58" t="n">
         <v>26010</v>
@@ -15860,7 +15481,7 @@
       <c r="H483" s="58" t="n"/>
       <c r="I483" s="58" t="n"/>
     </row>
-    <row r="484">
+    <row r="484" s="60">
       <c r="B484" s="79" t="n"/>
       <c r="C484" s="58" t="n"/>
       <c r="D484" s="58" t="inlineStr">
@@ -15876,7 +15497,7 @@
       <c r="H484" s="58" t="n"/>
       <c r="I484" s="58" t="n"/>
     </row>
-    <row r="485">
+    <row r="485" s="60">
       <c r="B485" s="79" t="n"/>
       <c r="C485" s="58" t="n">
         <v>26011</v>
@@ -15900,7 +15521,7 @@
       <c r="H485" s="58" t="n"/>
       <c r="I485" s="58" t="n"/>
     </row>
-    <row r="486">
+    <row r="486" s="60">
       <c r="B486" s="79" t="n"/>
       <c r="C486" s="58" t="n"/>
       <c r="D486" s="58" t="inlineStr">
@@ -15916,7 +15537,7 @@
       <c r="H486" s="58" t="n"/>
       <c r="I486" s="58" t="n"/>
     </row>
-    <row r="487">
+    <row r="487" s="60">
       <c r="B487" s="79" t="n"/>
       <c r="C487" s="58" t="n"/>
       <c r="D487" s="58" t="inlineStr">
@@ -15932,7 +15553,7 @@
       <c r="H487" s="58" t="n"/>
       <c r="I487" s="58" t="n"/>
     </row>
-    <row r="488">
+    <row r="488" s="60">
       <c r="B488" s="79" t="n"/>
       <c r="C488" s="58" t="n"/>
       <c r="D488" s="58" t="inlineStr">
@@ -15948,7 +15569,7 @@
       <c r="H488" s="58" t="n"/>
       <c r="I488" s="58" t="n"/>
     </row>
-    <row r="489">
+    <row r="489" s="60">
       <c r="B489" s="79" t="n"/>
       <c r="C489" s="58" t="n"/>
       <c r="D489" s="58" t="inlineStr">
@@ -15964,7 +15585,7 @@
       <c r="H489" s="58" t="n"/>
       <c r="I489" s="58" t="n"/>
     </row>
-    <row r="490">
+    <row r="490" s="60">
       <c r="B490" s="79" t="n"/>
       <c r="C490" s="58" t="n"/>
       <c r="D490" s="58" t="inlineStr">
@@ -15980,7 +15601,7 @@
       <c r="H490" s="58" t="n"/>
       <c r="I490" s="58" t="n"/>
     </row>
-    <row r="491">
+    <row r="491" s="60">
       <c r="B491" s="79" t="n"/>
       <c r="C491" s="58" t="n">
         <v>26012</v>
@@ -16004,7 +15625,7 @@
       <c r="H491" s="58" t="n"/>
       <c r="I491" s="58" t="n"/>
     </row>
-    <row r="492">
+    <row r="492" s="60">
       <c r="B492" s="79" t="n"/>
       <c r="C492" s="58" t="n"/>
       <c r="D492" s="58" t="inlineStr">
@@ -16020,7 +15641,7 @@
       <c r="H492" s="58" t="n"/>
       <c r="I492" s="58" t="n"/>
     </row>
-    <row r="493">
+    <row r="493" s="60">
       <c r="B493" s="79" t="n"/>
       <c r="C493" s="58" t="n"/>
       <c r="D493" s="58" t="inlineStr">
@@ -16036,7 +15657,7 @@
       <c r="H493" s="58" t="n"/>
       <c r="I493" s="58" t="n"/>
     </row>
-    <row r="494">
+    <row r="494" s="60">
       <c r="B494" s="79" t="n"/>
       <c r="C494" s="58" t="n">
         <v>26013</v>
@@ -16060,7 +15681,7 @@
       <c r="H494" s="58" t="n"/>
       <c r="I494" s="58" t="n"/>
     </row>
-    <row r="495">
+    <row r="495" s="60">
       <c r="B495" s="79" t="n"/>
       <c r="C495" s="58" t="n"/>
       <c r="D495" s="58" t="inlineStr">
@@ -16076,7 +15697,7 @@
       <c r="H495" s="58" t="n"/>
       <c r="I495" s="58" t="n"/>
     </row>
-    <row r="496">
+    <row r="496" s="60">
       <c r="B496" s="79" t="n"/>
       <c r="C496" s="58" t="n"/>
       <c r="D496" s="58" t="inlineStr">
@@ -16092,7 +15713,7 @@
       <c r="H496" s="58" t="n"/>
       <c r="I496" s="58" t="n"/>
     </row>
-    <row r="497">
+    <row r="497" s="60">
       <c r="B497" s="79" t="n"/>
       <c r="C497" s="58" t="n">
         <v>26015</v>
@@ -16116,7 +15737,7 @@
       <c r="H497" s="58" t="n"/>
       <c r="I497" s="58" t="n"/>
     </row>
-    <row r="498">
+    <row r="498" s="60">
       <c r="B498" s="79" t="n"/>
       <c r="C498" s="58" t="n"/>
       <c r="D498" s="58" t="inlineStr">
@@ -16132,7 +15753,7 @@
       <c r="H498" s="58" t="n"/>
       <c r="I498" s="58" t="n"/>
     </row>
-    <row r="499">
+    <row r="499" s="60">
       <c r="B499" s="79" t="n"/>
       <c r="C499" s="58" t="n"/>
       <c r="D499" s="58" t="inlineStr">
@@ -16148,7 +15769,7 @@
       <c r="H499" s="58" t="n"/>
       <c r="I499" s="58" t="n"/>
     </row>
-    <row r="500">
+    <row r="500" s="60">
       <c r="B500" s="79" t="n"/>
       <c r="C500" s="58" t="n"/>
       <c r="D500" s="58" t="inlineStr">
@@ -16164,7 +15785,7 @@
       <c r="H500" s="58" t="n"/>
       <c r="I500" s="58" t="n"/>
     </row>
-    <row r="501">
+    <row r="501" s="60">
       <c r="B501" s="79" t="n"/>
       <c r="C501" s="58" t="n"/>
       <c r="D501" s="58" t="inlineStr">
@@ -16180,7 +15801,7 @@
       <c r="H501" s="58" t="n"/>
       <c r="I501" s="58" t="n"/>
     </row>
-    <row r="502">
+    <row r="502" s="60">
       <c r="B502" s="79" t="n"/>
       <c r="C502" s="58" t="n">
         <v>26014</v>
@@ -16204,7 +15825,7 @@
       <c r="H502" s="58" t="n"/>
       <c r="I502" s="58" t="n"/>
     </row>
-    <row r="503">
+    <row r="503" s="60">
       <c r="B503" s="79" t="n"/>
       <c r="C503" s="58" t="n"/>
       <c r="D503" s="58" t="inlineStr">
@@ -16220,7 +15841,7 @@
       <c r="H503" s="58" t="n"/>
       <c r="I503" s="58" t="n"/>
     </row>
-    <row r="504">
+    <row r="504" s="60">
       <c r="B504" s="79" t="n"/>
       <c r="C504" s="58" t="n"/>
       <c r="D504" s="58" t="inlineStr">
@@ -16236,7 +15857,7 @@
       <c r="H504" s="58" t="n"/>
       <c r="I504" s="58" t="n"/>
     </row>
-    <row r="505">
+    <row r="505" s="60">
       <c r="B505" s="79" t="n"/>
       <c r="C505" s="58" t="n">
         <v>26600</v>
@@ -16260,7 +15881,7 @@
       <c r="H505" s="58" t="n"/>
       <c r="I505" s="58" t="n"/>
     </row>
-    <row r="506">
+    <row r="506" s="60">
       <c r="B506" s="79" t="n"/>
       <c r="C506" s="58" t="n"/>
       <c r="D506" s="58" t="inlineStr">
@@ -16276,7 +15897,7 @@
       <c r="H506" s="58" t="n"/>
       <c r="I506" s="58" t="n"/>
     </row>
-    <row r="507">
+    <row r="507" s="60">
       <c r="B507" s="79" t="n"/>
       <c r="C507" s="58" t="n"/>
       <c r="D507" s="58" t="inlineStr">
@@ -16292,7 +15913,7 @@
       <c r="H507" s="58" t="n"/>
       <c r="I507" s="58" t="n"/>
     </row>
-    <row r="508">
+    <row r="508" s="60">
       <c r="B508" s="79" t="n"/>
       <c r="C508" s="58" t="n"/>
       <c r="D508" s="58" t="inlineStr">
@@ -16308,7 +15929,7 @@
       <c r="H508" s="58" t="n"/>
       <c r="I508" s="58" t="n"/>
     </row>
-    <row r="509">
+    <row r="509" s="60">
       <c r="B509" s="79" t="n"/>
       <c r="C509" s="58" t="n"/>
       <c r="D509" s="58" t="inlineStr">
@@ -16324,7 +15945,7 @@
       <c r="H509" s="58" t="n"/>
       <c r="I509" s="58" t="n"/>
     </row>
-    <row r="510">
+    <row r="510" s="60">
       <c r="B510" s="79" t="n"/>
       <c r="C510" s="58" t="n">
         <v>26017</v>
@@ -16348,7 +15969,7 @@
       <c r="H510" s="58" t="n"/>
       <c r="I510" s="58" t="n"/>
     </row>
-    <row r="511">
+    <row r="511" s="60">
       <c r="B511" s="79" t="n"/>
       <c r="C511" s="58" t="n"/>
       <c r="D511" s="58" t="inlineStr">
@@ -16364,7 +15985,7 @@
       <c r="H511" s="58" t="n"/>
       <c r="I511" s="58" t="n"/>
     </row>
-    <row r="512">
+    <row r="512" s="60">
       <c r="B512" s="79" t="n"/>
       <c r="C512" s="58" t="n"/>
       <c r="D512" s="58" t="inlineStr">
@@ -16380,7 +16001,7 @@
       <c r="H512" s="58" t="n"/>
       <c r="I512" s="58" t="n"/>
     </row>
-    <row r="513">
+    <row r="513" s="60">
       <c r="B513" s="79" t="n"/>
       <c r="C513" s="58" t="n"/>
       <c r="D513" s="58" t="inlineStr">
@@ -16396,7 +16017,7 @@
       <c r="H513" s="58" t="n"/>
       <c r="I513" s="58" t="n"/>
     </row>
-    <row r="514">
+    <row r="514" s="60">
       <c r="B514" s="79" t="n"/>
       <c r="C514" s="58" t="n"/>
       <c r="D514" s="58" t="inlineStr">
@@ -16412,7 +16033,7 @@
       <c r="H514" s="58" t="n"/>
       <c r="I514" s="58" t="n"/>
     </row>
-    <row r="515">
+    <row r="515" s="60">
       <c r="B515" s="79" t="n"/>
       <c r="C515" s="58" t="n"/>
       <c r="D515" s="58" t="inlineStr">
@@ -16428,7 +16049,7 @@
       <c r="H515" s="58" t="n"/>
       <c r="I515" s="58" t="n"/>
     </row>
-    <row r="516">
+    <row r="516" s="60">
       <c r="B516" s="79" t="n"/>
       <c r="C516" s="58" t="n">
         <v>26018</v>
@@ -16452,7 +16073,7 @@
       <c r="H516" s="58" t="n"/>
       <c r="I516" s="58" t="n"/>
     </row>
-    <row r="517">
+    <row r="517" s="60">
       <c r="B517" s="79" t="n"/>
       <c r="C517" s="58" t="n"/>
       <c r="D517" s="58" t="inlineStr">
@@ -16468,7 +16089,7 @@
       <c r="H517" s="58" t="n"/>
       <c r="I517" s="58" t="n"/>
     </row>
-    <row r="518">
+    <row r="518" s="60">
       <c r="B518" s="79" t="n"/>
       <c r="C518" s="58" t="n">
         <v>26021</v>
@@ -16492,7 +16113,7 @@
       <c r="H518" s="58" t="n"/>
       <c r="I518" s="58" t="n"/>
     </row>
-    <row r="519">
+    <row r="519" s="60">
       <c r="B519" s="79" t="n"/>
       <c r="C519" s="58" t="n"/>
       <c r="D519" s="58" t="inlineStr">
@@ -16508,7 +16129,7 @@
       <c r="H519" s="58" t="n"/>
       <c r="I519" s="58" t="n"/>
     </row>
-    <row r="520">
+    <row r="520" s="60">
       <c r="B520" s="79" t="n"/>
       <c r="C520" s="58" t="n"/>
       <c r="D520" s="58" t="inlineStr">
@@ -16524,7 +16145,7 @@
       <c r="H520" s="58" t="n"/>
       <c r="I520" s="58" t="n"/>
     </row>
-    <row r="521">
+    <row r="521" s="60">
       <c r="B521" s="79" t="n"/>
       <c r="C521" s="58" t="n"/>
       <c r="D521" s="58" t="inlineStr">
@@ -16540,7 +16161,7 @@
       <c r="H521" s="58" t="n"/>
       <c r="I521" s="58" t="n"/>
     </row>
-    <row r="522">
+    <row r="522" s="60">
       <c r="B522" s="79" t="n"/>
       <c r="C522" s="58" t="n"/>
       <c r="D522" s="58" t="inlineStr">
@@ -16556,7 +16177,7 @@
       <c r="H522" s="58" t="n"/>
       <c r="I522" s="58" t="n"/>
     </row>
-    <row r="523">
+    <row r="523" s="60">
       <c r="B523" s="79" t="n"/>
       <c r="C523" s="58" t="n"/>
       <c r="D523" s="58" t="inlineStr">
@@ -16572,7 +16193,7 @@
       <c r="H523" s="58" t="n"/>
       <c r="I523" s="58" t="n"/>
     </row>
-    <row r="524">
+    <row r="524" s="60">
       <c r="B524" s="79" t="n"/>
       <c r="C524" s="58" t="n">
         <v>26020</v>
@@ -16596,7 +16217,7 @@
       <c r="H524" s="58" t="n"/>
       <c r="I524" s="58" t="n"/>
     </row>
-    <row r="525">
+    <row r="525" s="60">
       <c r="B525" s="79" t="n"/>
       <c r="C525" s="58" t="n"/>
       <c r="D525" s="58" t="inlineStr">
@@ -16612,7 +16233,7 @@
       <c r="H525" s="58" t="n"/>
       <c r="I525" s="58" t="n"/>
     </row>
-    <row r="526">
+    <row r="526" s="60">
       <c r="B526" s="79" t="n"/>
       <c r="C526" s="58" t="n"/>
       <c r="D526" s="58" t="inlineStr">
@@ -16628,7 +16249,7 @@
       <c r="H526" s="58" t="n"/>
       <c r="I526" s="58" t="n"/>
     </row>
-    <row r="527">
+    <row r="527" s="60">
       <c r="B527" s="79" t="n"/>
       <c r="C527" s="58" t="n"/>
       <c r="D527" s="58" t="inlineStr">
@@ -16644,7 +16265,7 @@
       <c r="H527" s="58" t="n"/>
       <c r="I527" s="58" t="n"/>
     </row>
-    <row r="528">
+    <row r="528" s="60">
       <c r="B528" s="79" t="n"/>
       <c r="C528" s="58" t="n">
         <v>26022</v>
@@ -16668,7 +16289,7 @@
       <c r="H528" s="58" t="n"/>
       <c r="I528" s="58" t="n"/>
     </row>
-    <row r="529">
+    <row r="529" s="60">
       <c r="B529" s="79" t="n"/>
       <c r="C529" s="58" t="n"/>
       <c r="D529" s="58" t="inlineStr">
@@ -16684,7 +16305,7 @@
       <c r="H529" s="58" t="n"/>
       <c r="I529" s="58" t="n"/>
     </row>
-    <row r="530">
+    <row r="530" s="60">
       <c r="B530" s="79" t="n"/>
       <c r="C530" s="58" t="n"/>
       <c r="D530" s="58" t="inlineStr">
@@ -16700,7 +16321,7 @@
       <c r="H530" s="58" t="n"/>
       <c r="I530" s="58" t="n"/>
     </row>
-    <row r="531">
+    <row r="531" s="60">
       <c r="B531" s="79" t="n"/>
       <c r="C531" s="58" t="n">
         <v>26023</v>
@@ -16724,7 +16345,7 @@
       <c r="H531" s="58" t="n"/>
       <c r="I531" s="58" t="n"/>
     </row>
-    <row r="532">
+    <row r="532" s="60">
       <c r="B532" s="79" t="n"/>
       <c r="C532" s="58" t="n"/>
       <c r="D532" s="58" t="inlineStr">
@@ -16740,7 +16361,7 @@
       <c r="H532" s="58" t="n"/>
       <c r="I532" s="58" t="n"/>
     </row>
-    <row r="533">
+    <row r="533" s="60">
       <c r="B533" s="79" t="n"/>
       <c r="C533" s="58" t="n"/>
       <c r="D533" s="58" t="inlineStr">
@@ -16756,7 +16377,7 @@
       <c r="H533" s="58" t="n"/>
       <c r="I533" s="58" t="n"/>
     </row>
-    <row r="534">
+    <row r="534" s="60">
       <c r="B534" s="79" t="n"/>
       <c r="C534" s="58" t="n"/>
       <c r="D534" s="58" t="inlineStr">
@@ -16772,7 +16393,7 @@
       <c r="H534" s="58" t="n"/>
       <c r="I534" s="58" t="n"/>
     </row>
-    <row r="535">
+    <row r="535" s="60">
       <c r="B535" s="79" t="n"/>
       <c r="C535" s="58" t="n">
         <v>26024</v>
@@ -16796,7 +16417,7 @@
       <c r="H535" s="58" t="n"/>
       <c r="I535" s="58" t="n"/>
     </row>
-    <row r="536">
+    <row r="536" s="60">
       <c r="B536" s="79" t="n"/>
       <c r="C536" s="58" t="n"/>
       <c r="D536" s="58" t="inlineStr">
@@ -16812,7 +16433,7 @@
       <c r="H536" s="58" t="n"/>
       <c r="I536" s="58" t="n"/>
     </row>
-    <row r="537">
+    <row r="537" s="60">
       <c r="B537" s="79" t="n"/>
       <c r="C537" s="58" t="n"/>
       <c r="D537" s="58" t="inlineStr">
@@ -16828,7 +16449,7 @@
       <c r="H537" s="58" t="n"/>
       <c r="I537" s="58" t="n"/>
     </row>
-    <row r="538">
+    <row r="538" s="60">
       <c r="B538" s="79" t="n"/>
       <c r="C538" s="58" t="n"/>
       <c r="D538" s="58" t="inlineStr">
@@ -16844,7 +16465,7 @@
       <c r="H538" s="58" t="n"/>
       <c r="I538" s="58" t="n"/>
     </row>
-    <row r="539">
+    <row r="539" s="60">
       <c r="B539" s="79" t="n"/>
       <c r="C539" s="58" t="n">
         <v>26025</v>
@@ -16868,7 +16489,7 @@
       <c r="H539" s="58" t="n"/>
       <c r="I539" s="58" t="n"/>
     </row>
-    <row r="540">
+    <row r="540" s="60">
       <c r="B540" s="79" t="n"/>
       <c r="C540" s="58" t="n"/>
       <c r="D540" s="58" t="inlineStr">
@@ -16884,7 +16505,7 @@
       <c r="H540" s="58" t="n"/>
       <c r="I540" s="58" t="n"/>
     </row>
-    <row r="541">
+    <row r="541" s="60">
       <c r="B541" s="79" t="n"/>
       <c r="C541" s="58" t="n"/>
       <c r="D541" s="58" t="inlineStr">
@@ -16900,7 +16521,7 @@
       <c r="H541" s="58" t="n"/>
       <c r="I541" s="58" t="n"/>
     </row>
-    <row r="542">
+    <row r="542" s="60">
       <c r="B542" s="79" t="n"/>
       <c r="C542" s="58" t="n"/>
       <c r="D542" s="58" t="inlineStr">
@@ -16916,7 +16537,7 @@
       <c r="H542" s="58" t="n"/>
       <c r="I542" s="58" t="n"/>
     </row>
-    <row r="543">
+    <row r="543" s="60">
       <c r="B543" s="79" t="n"/>
       <c r="C543" s="58" t="n"/>
       <c r="D543" s="58" t="inlineStr">
@@ -16932,7 +16553,7 @@
       <c r="H543" s="58" t="n"/>
       <c r="I543" s="58" t="n"/>
     </row>
-    <row r="544">
+    <row r="544" s="60">
       <c r="B544" s="79" t="n"/>
       <c r="C544" s="58" t="n">
         <v>26019</v>
@@ -16956,7 +16577,7 @@
       <c r="H544" s="58" t="n"/>
       <c r="I544" s="58" t="n"/>
     </row>
-    <row r="545">
+    <row r="545" s="60">
       <c r="B545" s="79" t="n"/>
       <c r="C545" s="58" t="n"/>
       <c r="D545" s="58" t="inlineStr">
@@ -16972,7 +16593,7 @@
       <c r="H545" s="58" t="n"/>
       <c r="I545" s="58" t="n"/>
     </row>
-    <row r="546">
+    <row r="546" s="60">
       <c r="B546" s="79" t="n"/>
       <c r="C546" s="58" t="n"/>
       <c r="D546" s="58" t="inlineStr">
@@ -16988,7 +16609,7 @@
       <c r="H546" s="58" t="n"/>
       <c r="I546" s="58" t="n"/>
     </row>
-    <row r="547">
+    <row r="547" s="60">
       <c r="B547" s="79" t="n"/>
       <c r="C547" s="58" t="n">
         <v>26300</v>
@@ -17012,7 +16633,7 @@
       <c r="H547" s="58" t="n"/>
       <c r="I547" s="58" t="n"/>
     </row>
-    <row r="548">
+    <row r="548" s="60">
       <c r="B548" s="79" t="n"/>
       <c r="C548" s="58" t="n"/>
       <c r="D548" s="58" t="inlineStr">
@@ -17028,7 +16649,7 @@
       <c r="H548" s="58" t="n"/>
       <c r="I548" s="58" t="n"/>
     </row>
-    <row r="549">
+    <row r="549" s="60">
       <c r="B549" s="79" t="n"/>
       <c r="C549" s="58" t="n"/>
       <c r="D549" s="58" t="inlineStr">
@@ -17044,7 +16665,7 @@
       <c r="H549" s="58" t="n"/>
       <c r="I549" s="58" t="n"/>
     </row>
-    <row r="550">
+    <row r="550" s="60">
       <c r="B550" s="79" t="n"/>
       <c r="C550" s="58" t="n">
         <v>26026</v>
@@ -17068,7 +16689,7 @@
       <c r="H550" s="58" t="n"/>
       <c r="I550" s="58" t="n"/>
     </row>
-    <row r="551">
+    <row r="551" s="60">
       <c r="B551" s="79" t="n"/>
       <c r="C551" s="58" t="n"/>
       <c r="D551" s="58" t="inlineStr">
@@ -17084,7 +16705,7 @@
       <c r="H551" s="58" t="n"/>
       <c r="I551" s="58" t="n"/>
     </row>
-    <row r="552">
+    <row r="552" s="60">
       <c r="B552" s="79" t="n"/>
       <c r="C552" s="58" t="n"/>
       <c r="D552" s="58" t="inlineStr">
@@ -17100,7 +16721,7 @@
       <c r="H552" s="58" t="n"/>
       <c r="I552" s="58" t="n"/>
     </row>
-    <row r="553">
+    <row r="553" s="60">
       <c r="B553" s="79" t="n"/>
       <c r="C553" s="58" t="n"/>
       <c r="D553" s="58" t="inlineStr">
@@ -17116,7 +16737,7 @@
       <c r="H553" s="58" t="n"/>
       <c r="I553" s="58" t="n"/>
     </row>
-    <row r="554">
+    <row r="554" s="60">
       <c r="B554" s="79" t="n"/>
       <c r="C554" s="58" t="n">
         <v>26601</v>
@@ -17140,7 +16761,7 @@
       <c r="H554" s="58" t="n"/>
       <c r="I554" s="58" t="n"/>
     </row>
-    <row r="555">
+    <row r="555" s="60">
       <c r="B555" s="79" t="n"/>
       <c r="C555" s="58" t="n"/>
       <c r="D555" s="58" t="inlineStr">
@@ -17156,7 +16777,7 @@
       <c r="H555" s="58" t="n"/>
       <c r="I555" s="58" t="n"/>
     </row>
-    <row r="556">
+    <row r="556" s="60">
       <c r="B556" s="79" t="n"/>
       <c r="C556" s="58" t="n"/>
       <c r="D556" s="58" t="inlineStr">
@@ -17172,7 +16793,7 @@
       <c r="H556" s="58" t="n"/>
       <c r="I556" s="58" t="n"/>
     </row>
-    <row r="557">
+    <row r="557" s="60">
       <c r="B557" s="79" t="n"/>
       <c r="C557" s="58" t="n"/>
       <c r="D557" s="58" t="inlineStr">
@@ -17188,7 +16809,7 @@
       <c r="H557" s="58" t="n"/>
       <c r="I557" s="58" t="n"/>
     </row>
-    <row r="558">
+    <row r="558" s="60">
       <c r="B558" s="79" t="n"/>
       <c r="C558" s="58" t="n">
         <v>26027</v>
@@ -17212,7 +16833,7 @@
       <c r="H558" s="58" t="n"/>
       <c r="I558" s="58" t="n"/>
     </row>
-    <row r="559">
+    <row r="559" s="60">
       <c r="B559" s="79" t="n"/>
       <c r="C559" s="58" t="n"/>
       <c r="D559" s="58" t="inlineStr">
@@ -17228,7 +16849,7 @@
       <c r="H559" s="58" t="n"/>
       <c r="I559" s="58" t="n"/>
     </row>
-    <row r="560">
+    <row r="560" s="60">
       <c r="B560" s="79" t="n"/>
       <c r="C560" s="58" t="n"/>
       <c r="D560" s="58" t="inlineStr">
@@ -17244,7 +16865,7 @@
       <c r="H560" s="58" t="n"/>
       <c r="I560" s="58" t="n"/>
     </row>
-    <row r="561">
+    <row r="561" s="60">
       <c r="B561" s="79" t="n"/>
       <c r="C561" s="58" t="n">
         <v>26030</v>
@@ -17268,7 +16889,7 @@
       <c r="H561" s="58" t="n"/>
       <c r="I561" s="58" t="n"/>
     </row>
-    <row r="562">
+    <row r="562" s="60">
       <c r="B562" s="79" t="n"/>
       <c r="C562" s="58" t="n"/>
       <c r="D562" s="58" t="inlineStr">
@@ -17284,7 +16905,7 @@
       <c r="H562" s="58" t="n"/>
       <c r="I562" s="58" t="n"/>
     </row>
-    <row r="563">
+    <row r="563" s="60">
       <c r="B563" s="79" t="n"/>
       <c r="C563" s="58" t="n"/>
       <c r="D563" s="58" t="inlineStr">
@@ -17300,7 +16921,7 @@
       <c r="H563" s="58" t="n"/>
       <c r="I563" s="58" t="n"/>
     </row>
-    <row r="564">
+    <row r="564" s="60">
       <c r="B564" s="79" t="n"/>
       <c r="C564" s="58" t="n">
         <v>26028</v>
@@ -17324,7 +16945,7 @@
       <c r="H564" s="58" t="n"/>
       <c r="I564" s="58" t="n"/>
     </row>
-    <row r="565">
+    <row r="565" s="60">
       <c r="B565" s="79" t="n"/>
       <c r="C565" s="58" t="n"/>
       <c r="D565" s="58" t="inlineStr">
@@ -17340,7 +16961,7 @@
       <c r="H565" s="58" t="n"/>
       <c r="I565" s="58" t="n"/>
     </row>
-    <row r="566">
+    <row r="566" s="60">
       <c r="B566" s="79" t="n"/>
       <c r="C566" s="58" t="n"/>
       <c r="D566" s="58" t="inlineStr">
@@ -17356,7 +16977,7 @@
       <c r="H566" s="58" t="n"/>
       <c r="I566" s="58" t="n"/>
     </row>
-    <row r="567">
+    <row r="567" s="60">
       <c r="B567" s="79" t="n"/>
       <c r="C567" s="58" t="n"/>
       <c r="D567" s="58" t="inlineStr">
@@ -17372,7 +16993,7 @@
       <c r="H567" s="58" t="n"/>
       <c r="I567" s="58" t="n"/>
     </row>
-    <row r="568">
+    <row r="568" s="60">
       <c r="B568" s="79" t="n"/>
       <c r="C568" s="58" t="n"/>
       <c r="D568" s="58" t="inlineStr">
@@ -17388,7 +17009,7 @@
       <c r="H568" s="58" t="n"/>
       <c r="I568" s="58" t="n"/>
     </row>
-    <row r="569">
+    <row r="569" s="60">
       <c r="B569" s="79" t="n"/>
       <c r="C569" s="58" t="n">
         <v>26029</v>
@@ -17412,7 +17033,7 @@
       <c r="H569" s="58" t="n"/>
       <c r="I569" s="58" t="n"/>
     </row>
-    <row r="570">
+    <row r="570" s="60">
       <c r="B570" s="80" t="n"/>
       <c r="C570" s="58" t="n"/>
       <c r="D570" s="58" t="inlineStr">
@@ -17428,7 +17049,7 @@
       <c r="H570" s="58" t="n"/>
       <c r="I570" s="58" t="n"/>
     </row>
-    <row r="571">
+    <row r="571" s="60">
       <c r="B571" s="58" t="inlineStr">
         <is>
           <t>Wind Valley</t>
@@ -17460,7 +17081,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="572">
+    <row r="572" s="60">
       <c r="B572" s="79" t="n"/>
       <c r="C572" s="58" t="n"/>
       <c r="D572" s="58" t="inlineStr">
@@ -17476,7 +17097,7 @@
       <c r="H572" s="58" t="n"/>
       <c r="I572" s="58" t="n"/>
     </row>
-    <row r="573">
+    <row r="573" s="60">
       <c r="B573" s="79" t="n"/>
       <c r="C573" s="58" t="n"/>
       <c r="D573" s="58" t="inlineStr">
@@ -17492,7 +17113,7 @@
       <c r="H573" s="58" t="n"/>
       <c r="I573" s="58" t="n"/>
     </row>
-    <row r="574">
+    <row r="574" s="60">
       <c r="B574" s="79" t="n"/>
       <c r="C574" s="58" t="n">
         <v>30001</v>
@@ -17516,7 +17137,7 @@
       <c r="H574" s="58" t="n"/>
       <c r="I574" s="58" t="n"/>
     </row>
-    <row r="575">
+    <row r="575" s="60">
       <c r="B575" s="79" t="n"/>
       <c r="C575" s="58" t="n"/>
       <c r="D575" s="58" t="inlineStr">
@@ -17532,7 +17153,7 @@
       <c r="H575" s="58" t="n"/>
       <c r="I575" s="58" t="n"/>
     </row>
-    <row r="576">
+    <row r="576" s="60">
       <c r="B576" s="79" t="n"/>
       <c r="C576" s="58" t="n">
         <v>30002</v>
@@ -17556,7 +17177,7 @@
       <c r="H576" s="58" t="n"/>
       <c r="I576" s="58" t="n"/>
     </row>
-    <row r="577">
+    <row r="577" s="60">
       <c r="B577" s="79" t="n"/>
       <c r="C577" s="58" t="n"/>
       <c r="D577" s="58" t="inlineStr">
@@ -17572,7 +17193,7 @@
       <c r="H577" s="58" t="n"/>
       <c r="I577" s="58" t="n"/>
     </row>
-    <row r="578">
+    <row r="578" s="60">
       <c r="B578" s="80" t="n"/>
       <c r="C578" s="58" t="n"/>
       <c r="D578" s="58" t="inlineStr">
@@ -17588,7 +17209,7 @@
       <c r="H578" s="58" t="n"/>
       <c r="I578" s="58" t="n"/>
     </row>
-    <row r="579">
+    <row r="579" s="60">
       <c r="B579" s="58" t="inlineStr">
         <is>
           <t>Burning Furnace</t>
@@ -17620,7 +17241,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="580">
+    <row r="580" s="60">
       <c r="B580" s="79" t="n"/>
       <c r="C580" s="58" t="n"/>
       <c r="D580" s="58" t="inlineStr">
@@ -17636,7 +17257,7 @@
       <c r="H580" s="58" t="n"/>
       <c r="I580" s="58" t="n"/>
     </row>
-    <row r="581">
+    <row r="581" s="60">
       <c r="B581" s="79" t="n"/>
       <c r="C581" s="58" t="n"/>
       <c r="D581" s="58" t="inlineStr">
@@ -17652,7 +17273,7 @@
       <c r="H581" s="58" t="n"/>
       <c r="I581" s="58" t="n"/>
     </row>
-    <row r="582">
+    <row r="582" s="60">
       <c r="B582" s="79" t="n"/>
       <c r="C582" s="58" t="n"/>
       <c r="D582" s="58" t="inlineStr">
@@ -17668,7 +17289,7 @@
       <c r="H582" s="58" t="n"/>
       <c r="I582" s="58" t="n"/>
     </row>
-    <row r="583">
+    <row r="583" s="60">
       <c r="B583" s="79" t="n"/>
       <c r="C583" s="58" t="n"/>
       <c r="D583" s="58" t="inlineStr">
@@ -17684,7 +17305,7 @@
       <c r="H583" s="58" t="n"/>
       <c r="I583" s="58" t="n"/>
     </row>
-    <row r="584">
+    <row r="584" s="60">
       <c r="B584" s="79" t="n"/>
       <c r="C584" s="58" t="n"/>
       <c r="D584" s="58" t="inlineStr">
@@ -17700,7 +17321,7 @@
       <c r="H584" s="58" t="n"/>
       <c r="I584" s="58" t="n"/>
     </row>
-    <row r="585">
+    <row r="585" s="60">
       <c r="B585" s="79" t="n"/>
       <c r="C585" s="58" t="n"/>
       <c r="D585" s="58" t="inlineStr">
@@ -17716,7 +17337,7 @@
       <c r="H585" s="58" t="n"/>
       <c r="I585" s="58" t="n"/>
     </row>
-    <row r="586">
+    <row r="586" s="60">
       <c r="B586" s="79" t="n"/>
       <c r="C586" s="58" t="n">
         <v>27000</v>
@@ -17740,7 +17361,7 @@
       <c r="H586" s="58" t="n"/>
       <c r="I586" s="58" t="n"/>
     </row>
-    <row r="587">
+    <row r="587" s="60">
       <c r="B587" s="79" t="n"/>
       <c r="C587" s="58" t="n"/>
       <c r="D587" s="58" t="inlineStr">
@@ -17756,7 +17377,7 @@
       <c r="H587" s="58" t="n"/>
       <c r="I587" s="58" t="n"/>
     </row>
-    <row r="588">
+    <row r="588" s="60">
       <c r="B588" s="79" t="n"/>
       <c r="C588" s="58" t="n">
         <v>27001</v>
@@ -17780,7 +17401,7 @@
       <c r="H588" s="58" t="n"/>
       <c r="I588" s="58" t="n"/>
     </row>
-    <row r="589">
+    <row r="589" s="60">
       <c r="B589" s="79" t="n"/>
       <c r="C589" s="58" t="n"/>
       <c r="D589" s="58" t="inlineStr">
@@ -17796,7 +17417,7 @@
       <c r="H589" s="58" t="n"/>
       <c r="I589" s="58" t="n"/>
     </row>
-    <row r="590">
+    <row r="590" s="60">
       <c r="B590" s="79" t="n"/>
       <c r="C590" s="58" t="n"/>
       <c r="D590" s="58" t="inlineStr">
@@ -17812,7 +17433,7 @@
       <c r="H590" s="58" t="n"/>
       <c r="I590" s="58" t="n"/>
     </row>
-    <row r="591">
+    <row r="591" s="60">
       <c r="B591" s="79" t="n"/>
       <c r="C591" s="58" t="n">
         <v>27002</v>
@@ -17836,7 +17457,7 @@
       <c r="H591" s="58" t="n"/>
       <c r="I591" s="58" t="n"/>
     </row>
-    <row r="592">
+    <row r="592" s="60">
       <c r="B592" s="79" t="n"/>
       <c r="C592" s="58" t="n"/>
       <c r="D592" s="58" t="inlineStr">
@@ -17852,7 +17473,7 @@
       <c r="H592" s="58" t="n"/>
       <c r="I592" s="58" t="n"/>
     </row>
-    <row r="593">
+    <row r="593" s="60">
       <c r="B593" s="79" t="n"/>
       <c r="C593" s="58" t="n"/>
       <c r="D593" s="58" t="inlineStr">
@@ -17868,7 +17489,7 @@
       <c r="H593" s="58" t="n"/>
       <c r="I593" s="58" t="n"/>
     </row>
-    <row r="594">
+    <row r="594" s="60">
       <c r="B594" s="79" t="n"/>
       <c r="C594" s="58" t="n"/>
       <c r="D594" s="58" t="inlineStr">
@@ -17884,7 +17505,7 @@
       <c r="H594" s="58" t="n"/>
       <c r="I594" s="58" t="n"/>
     </row>
-    <row r="595">
+    <row r="595" s="60">
       <c r="B595" s="79" t="n"/>
       <c r="C595" s="58" t="n">
         <v>27003</v>
@@ -17908,7 +17529,7 @@
       <c r="H595" s="58" t="n"/>
       <c r="I595" s="58" t="n"/>
     </row>
-    <row r="596">
+    <row r="596" s="60">
       <c r="B596" s="79" t="n"/>
       <c r="C596" s="58" t="n"/>
       <c r="D596" s="58" t="inlineStr">
@@ -17924,7 +17545,7 @@
       <c r="H596" s="58" t="n"/>
       <c r="I596" s="58" t="n"/>
     </row>
-    <row r="597">
+    <row r="597" s="60">
       <c r="B597" s="79" t="n"/>
       <c r="C597" s="58" t="n"/>
       <c r="D597" s="58" t="inlineStr">
@@ -17940,7 +17561,7 @@
       <c r="H597" s="58" t="n"/>
       <c r="I597" s="58" t="n"/>
     </row>
-    <row r="598">
+    <row r="598" s="60">
       <c r="B598" s="79" t="n"/>
       <c r="C598" s="58" t="n"/>
       <c r="D598" s="58" t="inlineStr">
@@ -17956,7 +17577,7 @@
       <c r="H598" s="58" t="n"/>
       <c r="I598" s="58" t="n"/>
     </row>
-    <row r="599">
+    <row r="599" s="60">
       <c r="B599" s="79" t="n"/>
       <c r="C599" s="58" t="n"/>
       <c r="D599" s="58" t="inlineStr">
@@ -17972,7 +17593,7 @@
       <c r="H599" s="58" t="n"/>
       <c r="I599" s="58" t="n"/>
     </row>
-    <row r="600">
+    <row r="600" s="60">
       <c r="B600" s="79" t="n"/>
       <c r="C600" s="58" t="n"/>
       <c r="D600" s="58" t="inlineStr">
@@ -17988,7 +17609,7 @@
       <c r="H600" s="58" t="n"/>
       <c r="I600" s="58" t="n"/>
     </row>
-    <row r="601">
+    <row r="601" s="60">
       <c r="B601" s="79" t="n"/>
       <c r="C601" s="58" t="n">
         <v>27004</v>
@@ -18012,7 +17633,7 @@
       <c r="H601" s="58" t="n"/>
       <c r="I601" s="58" t="n"/>
     </row>
-    <row r="602">
+    <row r="602" s="60">
       <c r="B602" s="79" t="n"/>
       <c r="C602" s="58" t="n"/>
       <c r="D602" s="58" t="inlineStr">
@@ -18028,7 +17649,7 @@
       <c r="H602" s="58" t="n"/>
       <c r="I602" s="58" t="n"/>
     </row>
-    <row r="603">
+    <row r="603" s="60">
       <c r="B603" s="79" t="n"/>
       <c r="C603" s="58" t="n"/>
       <c r="D603" s="58" t="inlineStr">
@@ -18044,7 +17665,7 @@
       <c r="H603" s="58" t="n"/>
       <c r="I603" s="58" t="n"/>
     </row>
-    <row r="604">
+    <row r="604" s="60">
       <c r="B604" s="79" t="n"/>
       <c r="C604" s="58" t="n"/>
       <c r="D604" s="58" t="inlineStr">
@@ -18060,7 +17681,7 @@
       <c r="H604" s="58" t="n"/>
       <c r="I604" s="58" t="n"/>
     </row>
-    <row r="605">
+    <row r="605" s="60">
       <c r="B605" s="79" t="n"/>
       <c r="C605" s="58" t="n"/>
       <c r="D605" s="58" t="inlineStr">
@@ -18076,7 +17697,7 @@
       <c r="H605" s="58" t="n"/>
       <c r="I605" s="58" t="n"/>
     </row>
-    <row r="606">
+    <row r="606" s="60">
       <c r="B606" s="79" t="n"/>
       <c r="C606" s="58" t="n"/>
       <c r="D606" s="58" t="inlineStr">
@@ -18092,7 +17713,7 @@
       <c r="H606" s="58" t="n"/>
       <c r="I606" s="58" t="n"/>
     </row>
-    <row r="607">
+    <row r="607" s="60">
       <c r="B607" s="79" t="n"/>
       <c r="C607" s="58" t="n"/>
       <c r="D607" s="58" t="inlineStr">
@@ -18108,7 +17729,7 @@
       <c r="H607" s="58" t="n"/>
       <c r="I607" s="58" t="n"/>
     </row>
-    <row r="608">
+    <row r="608" s="60">
       <c r="B608" s="79" t="n"/>
       <c r="C608" s="58" t="n">
         <v>27005</v>
@@ -18132,7 +17753,7 @@
       <c r="H608" s="58" t="n"/>
       <c r="I608" s="58" t="n"/>
     </row>
-    <row r="609">
+    <row r="609" s="60">
       <c r="B609" s="79" t="n"/>
       <c r="C609" s="58" t="n"/>
       <c r="D609" s="58" t="inlineStr">
@@ -18148,7 +17769,7 @@
       <c r="H609" s="58" t="n"/>
       <c r="I609" s="58" t="n"/>
     </row>
-    <row r="610">
+    <row r="610" s="60">
       <c r="B610" s="79" t="n"/>
       <c r="C610" s="58" t="n"/>
       <c r="D610" s="58" t="inlineStr">
@@ -18164,7 +17785,7 @@
       <c r="H610" s="58" t="n"/>
       <c r="I610" s="58" t="n"/>
     </row>
-    <row r="611">
+    <row r="611" s="60">
       <c r="B611" s="79" t="n"/>
       <c r="C611" s="58" t="n"/>
       <c r="D611" s="58" t="inlineStr">
@@ -18180,7 +17801,7 @@
       <c r="H611" s="58" t="n"/>
       <c r="I611" s="58" t="n"/>
     </row>
-    <row r="612">
+    <row r="612" s="60">
       <c r="B612" s="79" t="n"/>
       <c r="C612" s="58" t="n"/>
       <c r="D612" s="58" t="inlineStr">
@@ -18196,7 +17817,7 @@
       <c r="H612" s="58" t="n"/>
       <c r="I612" s="58" t="n"/>
     </row>
-    <row r="613">
+    <row r="613" s="60">
       <c r="B613" s="79" t="n"/>
       <c r="C613" s="58" t="n">
         <v>27006</v>
@@ -18220,7 +17841,7 @@
       <c r="H613" s="58" t="n"/>
       <c r="I613" s="58" t="n"/>
     </row>
-    <row r="614">
+    <row r="614" s="60">
       <c r="B614" s="79" t="n"/>
       <c r="C614" s="58" t="n"/>
       <c r="D614" s="58" t="inlineStr">
@@ -18236,7 +17857,7 @@
       <c r="H614" s="58" t="n"/>
       <c r="I614" s="58" t="n"/>
     </row>
-    <row r="615">
+    <row r="615" s="60">
       <c r="B615" s="79" t="n"/>
       <c r="C615" s="58" t="n"/>
       <c r="D615" s="58" t="inlineStr">
@@ -18252,7 +17873,7 @@
       <c r="H615" s="58" t="n"/>
       <c r="I615" s="58" t="n"/>
     </row>
-    <row r="616">
+    <row r="616" s="60">
       <c r="B616" s="79" t="n"/>
       <c r="C616" s="58" t="n">
         <v>27007</v>
@@ -18276,7 +17897,7 @@
       <c r="H616" s="58" t="n"/>
       <c r="I616" s="58" t="n"/>
     </row>
-    <row r="617">
+    <row r="617" s="60">
       <c r="B617" s="79" t="n"/>
       <c r="C617" s="58" t="n"/>
       <c r="D617" s="58" t="inlineStr">
@@ -18292,7 +17913,7 @@
       <c r="H617" s="58" t="n"/>
       <c r="I617" s="58" t="n"/>
     </row>
-    <row r="618">
+    <row r="618" s="60">
       <c r="B618" s="79" t="n"/>
       <c r="C618" s="58" t="n">
         <v>27008</v>
@@ -18316,7 +17937,7 @@
       <c r="H618" s="58" t="n"/>
       <c r="I618" s="58" t="n"/>
     </row>
-    <row r="619">
+    <row r="619" s="60">
       <c r="B619" s="79" t="n"/>
       <c r="C619" s="58" t="n"/>
       <c r="D619" s="58" t="inlineStr">
@@ -18332,7 +17953,7 @@
       <c r="H619" s="58" t="n"/>
       <c r="I619" s="58" t="n"/>
     </row>
-    <row r="620">
+    <row r="620" s="60">
       <c r="B620" s="79" t="n"/>
       <c r="C620" s="58" t="n"/>
       <c r="D620" s="58" t="inlineStr">
@@ -18348,7 +17969,7 @@
       <c r="H620" s="58" t="n"/>
       <c r="I620" s="58" t="n"/>
     </row>
-    <row r="621">
+    <row r="621" s="60">
       <c r="B621" s="79" t="n"/>
       <c r="C621" s="58" t="n"/>
       <c r="D621" s="58" t="inlineStr">
@@ -18364,7 +17985,7 @@
       <c r="H621" s="58" t="n"/>
       <c r="I621" s="58" t="n"/>
     </row>
-    <row r="622">
+    <row r="622" s="60">
       <c r="B622" s="79" t="n"/>
       <c r="C622" s="58" t="n"/>
       <c r="D622" s="58" t="inlineStr">
@@ -18380,7 +18001,7 @@
       <c r="H622" s="58" t="n"/>
       <c r="I622" s="58" t="n"/>
     </row>
-    <row r="623">
+    <row r="623" s="60">
       <c r="B623" s="79" t="n"/>
       <c r="C623" s="58" t="n"/>
       <c r="D623" s="58" t="inlineStr">
@@ -18396,7 +18017,7 @@
       <c r="H623" s="58" t="n"/>
       <c r="I623" s="58" t="n"/>
     </row>
-    <row r="624">
+    <row r="624" s="60">
       <c r="B624" s="79" t="n"/>
       <c r="C624" s="58" t="n"/>
       <c r="D624" s="58" t="inlineStr">
@@ -18412,7 +18033,7 @@
       <c r="H624" s="58" t="n"/>
       <c r="I624" s="58" t="n"/>
     </row>
-    <row r="625">
+    <row r="625" s="60">
       <c r="B625" s="79" t="n"/>
       <c r="C625" s="58" t="n">
         <v>27009</v>
@@ -18436,7 +18057,7 @@
       <c r="H625" s="58" t="n"/>
       <c r="I625" s="58" t="n"/>
     </row>
-    <row r="626">
+    <row r="626" s="60">
       <c r="B626" s="79" t="n"/>
       <c r="C626" s="58" t="n"/>
       <c r="D626" s="58" t="inlineStr">
@@ -18452,7 +18073,7 @@
       <c r="H626" s="58" t="n"/>
       <c r="I626" s="58" t="n"/>
     </row>
-    <row r="627">
+    <row r="627" s="60">
       <c r="B627" s="79" t="n"/>
       <c r="C627" s="58" t="n"/>
       <c r="D627" s="58" t="inlineStr">
@@ -18468,7 +18089,7 @@
       <c r="H627" s="58" t="n"/>
       <c r="I627" s="58" t="n"/>
     </row>
-    <row r="628">
+    <row r="628" s="60">
       <c r="B628" s="79" t="n"/>
       <c r="C628" s="58" t="n">
         <v>27600</v>
@@ -18492,7 +18113,7 @@
       <c r="H628" s="58" t="n"/>
       <c r="I628" s="58" t="n"/>
     </row>
-    <row r="629">
+    <row r="629" s="60">
       <c r="B629" s="79" t="n"/>
       <c r="C629" s="58" t="n"/>
       <c r="D629" s="58" t="inlineStr">
@@ -18508,7 +18129,7 @@
       <c r="H629" s="58" t="n"/>
       <c r="I629" s="58" t="n"/>
     </row>
-    <row r="630">
+    <row r="630" s="60">
       <c r="B630" s="79" t="n"/>
       <c r="C630" s="58" t="n"/>
       <c r="D630" s="58" t="inlineStr">
@@ -18524,7 +18145,7 @@
       <c r="H630" s="58" t="n"/>
       <c r="I630" s="58" t="n"/>
     </row>
-    <row r="631">
+    <row r="631" s="60">
       <c r="B631" s="79" t="n"/>
       <c r="C631" s="58" t="n"/>
       <c r="D631" s="58" t="inlineStr">
@@ -18540,7 +18161,7 @@
       <c r="H631" s="58" t="n"/>
       <c r="I631" s="58" t="n"/>
     </row>
-    <row r="632">
+    <row r="632" s="60">
       <c r="B632" s="79" t="n"/>
       <c r="C632" s="58" t="n"/>
       <c r="D632" s="58" t="inlineStr">
@@ -18556,7 +18177,7 @@
       <c r="H632" s="58" t="n"/>
       <c r="I632" s="58" t="n"/>
     </row>
-    <row r="633">
+    <row r="633" s="60">
       <c r="B633" s="79" t="n"/>
       <c r="C633" s="58" t="n">
         <v>27010</v>
@@ -18580,7 +18201,7 @@
       <c r="H633" s="58" t="n"/>
       <c r="I633" s="58" t="n"/>
     </row>
-    <row r="634">
+    <row r="634" s="60">
       <c r="B634" s="79" t="n"/>
       <c r="C634" s="58" t="n"/>
       <c r="D634" s="58" t="inlineStr">
@@ -18596,7 +18217,7 @@
       <c r="H634" s="58" t="n"/>
       <c r="I634" s="58" t="n"/>
     </row>
-    <row r="635">
+    <row r="635" s="60">
       <c r="B635" s="79" t="n"/>
       <c r="C635" s="58" t="n"/>
       <c r="D635" s="58" t="inlineStr">
@@ -18612,7 +18233,7 @@
       <c r="H635" s="58" t="n"/>
       <c r="I635" s="58" t="n"/>
     </row>
-    <row r="636">
+    <row r="636" s="60">
       <c r="B636" s="79" t="n"/>
       <c r="C636" s="58" t="n"/>
       <c r="D636" s="58" t="inlineStr">
@@ -18628,7 +18249,7 @@
       <c r="H636" s="58" t="n"/>
       <c r="I636" s="58" t="n"/>
     </row>
-    <row r="637">
+    <row r="637" s="60">
       <c r="B637" s="79" t="n"/>
       <c r="C637" s="58" t="n"/>
       <c r="D637" s="58" t="inlineStr">
@@ -18644,7 +18265,7 @@
       <c r="H637" s="58" t="n"/>
       <c r="I637" s="58" t="n"/>
     </row>
-    <row r="638">
+    <row r="638" s="60">
       <c r="B638" s="79" t="n"/>
       <c r="C638" s="58" t="n"/>
       <c r="D638" s="58" t="inlineStr">
@@ -18660,7 +18281,7 @@
       <c r="H638" s="58" t="n"/>
       <c r="I638" s="58" t="n"/>
     </row>
-    <row r="639">
+    <row r="639" s="60">
       <c r="B639" s="79" t="n"/>
       <c r="C639" s="58" t="n"/>
       <c r="D639" s="58" t="inlineStr">
@@ -18676,7 +18297,7 @@
       <c r="H639" s="58" t="n"/>
       <c r="I639" s="58" t="n"/>
     </row>
-    <row r="640">
+    <row r="640" s="60">
       <c r="B640" s="79" t="n"/>
       <c r="C640" s="58" t="n">
         <v>27011</v>
@@ -18700,7 +18321,7 @@
       <c r="H640" s="58" t="n"/>
       <c r="I640" s="58" t="n"/>
     </row>
-    <row r="641">
+    <row r="641" s="60">
       <c r="B641" s="79" t="n"/>
       <c r="C641" s="58" t="n"/>
       <c r="D641" s="58" t="inlineStr">
@@ -18716,7 +18337,7 @@
       <c r="H641" s="58" t="n"/>
       <c r="I641" s="58" t="n"/>
     </row>
-    <row r="642">
+    <row r="642" s="60">
       <c r="B642" s="79" t="n"/>
       <c r="C642" s="58" t="n"/>
       <c r="D642" s="58" t="inlineStr">
@@ -18732,7 +18353,7 @@
       <c r="H642" s="58" t="n"/>
       <c r="I642" s="58" t="n"/>
     </row>
-    <row r="643">
+    <row r="643" s="60">
       <c r="B643" s="79" t="n"/>
       <c r="C643" s="58" t="n"/>
       <c r="D643" s="58" t="inlineStr">
@@ -18748,7 +18369,7 @@
       <c r="H643" s="58" t="n"/>
       <c r="I643" s="58" t="n"/>
     </row>
-    <row r="644">
+    <row r="644" s="60">
       <c r="B644" s="79" t="n"/>
       <c r="C644" s="58" t="n">
         <v>27012</v>
@@ -18772,7 +18393,7 @@
       <c r="H644" s="58" t="n"/>
       <c r="I644" s="58" t="n"/>
     </row>
-    <row r="645">
+    <row r="645" s="60">
       <c r="B645" s="79" t="n"/>
       <c r="C645" s="58" t="n"/>
       <c r="D645" s="58" t="inlineStr">
@@ -18788,7 +18409,7 @@
       <c r="H645" s="58" t="n"/>
       <c r="I645" s="58" t="n"/>
     </row>
-    <row r="646">
+    <row r="646" s="60">
       <c r="B646" s="79" t="n"/>
       <c r="C646" s="58" t="n">
         <v>27013</v>
@@ -18812,7 +18433,7 @@
       <c r="H646" s="58" t="n"/>
       <c r="I646" s="58" t="n"/>
     </row>
-    <row r="647">
+    <row r="647" s="60">
       <c r="B647" s="79" t="n"/>
       <c r="C647" s="58" t="n"/>
       <c r="D647" s="58" t="inlineStr">
@@ -18828,7 +18449,7 @@
       <c r="H647" s="58" t="n"/>
       <c r="I647" s="58" t="n"/>
     </row>
-    <row r="648">
+    <row r="648" s="60">
       <c r="B648" s="79" t="n"/>
       <c r="C648" s="58" t="n"/>
       <c r="D648" s="58" t="inlineStr">
@@ -18844,7 +18465,7 @@
       <c r="H648" s="58" t="n"/>
       <c r="I648" s="58" t="n"/>
     </row>
-    <row r="649">
+    <row r="649" s="60">
       <c r="B649" s="79" t="n"/>
       <c r="C649" s="58" t="n"/>
       <c r="D649" s="58" t="inlineStr">
@@ -18860,7 +18481,7 @@
       <c r="H649" s="58" t="n"/>
       <c r="I649" s="58" t="n"/>
     </row>
-    <row r="650">
+    <row r="650" s="60">
       <c r="B650" s="79" t="n"/>
       <c r="C650" s="58" t="n"/>
       <c r="D650" s="58" t="inlineStr">
@@ -18876,7 +18497,7 @@
       <c r="H650" s="58" t="n"/>
       <c r="I650" s="58" t="n"/>
     </row>
-    <row r="651">
+    <row r="651" s="60">
       <c r="B651" s="79" t="n"/>
       <c r="C651" s="58" t="n">
         <v>27014</v>
@@ -18900,7 +18521,7 @@
       <c r="H651" s="58" t="n"/>
       <c r="I651" s="58" t="n"/>
     </row>
-    <row r="652">
+    <row r="652" s="60">
       <c r="B652" s="79" t="n"/>
       <c r="C652" s="58" t="n"/>
       <c r="D652" s="58" t="inlineStr">
@@ -18916,7 +18537,7 @@
       <c r="H652" s="58" t="n"/>
       <c r="I652" s="58" t="n"/>
     </row>
-    <row r="653">
+    <row r="653" s="60">
       <c r="B653" s="79" t="n"/>
       <c r="C653" s="58" t="n"/>
       <c r="D653" s="58" t="inlineStr">
@@ -18932,7 +18553,7 @@
       <c r="H653" s="58" t="n"/>
       <c r="I653" s="58" t="n"/>
     </row>
-    <row r="654">
+    <row r="654" s="60">
       <c r="B654" s="79" t="n"/>
       <c r="C654" s="58" t="n"/>
       <c r="D654" s="58" t="inlineStr">
@@ -18948,7 +18569,7 @@
       <c r="H654" s="58" t="n"/>
       <c r="I654" s="58" t="n"/>
     </row>
-    <row r="655">
+    <row r="655" s="60">
       <c r="B655" s="79" t="n"/>
       <c r="C655" s="58" t="n"/>
       <c r="D655" s="58" t="inlineStr">
@@ -18964,7 +18585,7 @@
       <c r="H655" s="58" t="n"/>
       <c r="I655" s="58" t="n"/>
     </row>
-    <row r="656">
+    <row r="656" s="60">
       <c r="B656" s="79" t="n"/>
       <c r="C656" s="58" t="n"/>
       <c r="D656" s="58" t="inlineStr">
@@ -18980,7 +18601,7 @@
       <c r="H656" s="58" t="n"/>
       <c r="I656" s="58" t="n"/>
     </row>
-    <row r="657">
+    <row r="657" s="60">
       <c r="B657" s="79" t="n"/>
       <c r="C657" s="58" t="n"/>
       <c r="D657" s="58" t="inlineStr">
@@ -18996,7 +18617,7 @@
       <c r="H657" s="58" t="n"/>
       <c r="I657" s="58" t="n"/>
     </row>
-    <row r="658">
+    <row r="658" s="60">
       <c r="B658" s="79" t="n"/>
       <c r="C658" s="58" t="n">
         <v>27015</v>
@@ -19020,7 +18641,7 @@
       <c r="H658" s="58" t="n"/>
       <c r="I658" s="58" t="n"/>
     </row>
-    <row r="659">
+    <row r="659" s="60">
       <c r="B659" s="79" t="n"/>
       <c r="C659" s="58" t="n"/>
       <c r="D659" s="58" t="inlineStr">
@@ -19036,7 +18657,7 @@
       <c r="H659" s="58" t="n"/>
       <c r="I659" s="58" t="n"/>
     </row>
-    <row r="660">
+    <row r="660" s="60">
       <c r="B660" s="79" t="n"/>
       <c r="C660" s="58" t="n"/>
       <c r="D660" s="58" t="inlineStr">
@@ -19052,7 +18673,7 @@
       <c r="H660" s="58" t="n"/>
       <c r="I660" s="58" t="n"/>
     </row>
-    <row r="661">
+    <row r="661" s="60">
       <c r="B661" s="79" t="n"/>
       <c r="C661" s="58" t="n">
         <v>27016</v>
@@ -19076,7 +18697,7 @@
       <c r="H661" s="58" t="n"/>
       <c r="I661" s="58" t="n"/>
     </row>
-    <row r="662">
+    <row r="662" s="60">
       <c r="B662" s="79" t="n"/>
       <c r="C662" s="58" t="n"/>
       <c r="D662" s="58" t="inlineStr">
@@ -19092,7 +18713,7 @@
       <c r="H662" s="58" t="n"/>
       <c r="I662" s="58" t="n"/>
     </row>
-    <row r="663">
+    <row r="663" s="60">
       <c r="B663" s="79" t="n"/>
       <c r="C663" s="58" t="n"/>
       <c r="D663" s="58" t="inlineStr">
@@ -19108,7 +18729,7 @@
       <c r="H663" s="58" t="n"/>
       <c r="I663" s="58" t="n"/>
     </row>
-    <row r="664">
+    <row r="664" s="60">
       <c r="B664" s="79" t="n"/>
       <c r="C664" s="58" t="n"/>
       <c r="D664" s="58" t="inlineStr">
@@ -19124,7 +18745,7 @@
       <c r="H664" s="58" t="n"/>
       <c r="I664" s="58" t="n"/>
     </row>
-    <row r="665">
+    <row r="665" s="60">
       <c r="B665" s="79" t="n"/>
       <c r="C665" s="58" t="n"/>
       <c r="D665" s="58" t="inlineStr">
@@ -19140,7 +18761,7 @@
       <c r="H665" s="58" t="n"/>
       <c r="I665" s="58" t="n"/>
     </row>
-    <row r="666">
+    <row r="666" s="60">
       <c r="B666" s="79" t="n"/>
       <c r="C666" s="58" t="n"/>
       <c r="D666" s="58" t="inlineStr">
@@ -19156,7 +18777,7 @@
       <c r="H666" s="58" t="n"/>
       <c r="I666" s="58" t="n"/>
     </row>
-    <row r="667">
+    <row r="667" s="60">
       <c r="B667" s="79" t="n"/>
       <c r="C667" s="58" t="n">
         <v>27017</v>
@@ -19180,7 +18801,7 @@
       <c r="H667" s="58" t="n"/>
       <c r="I667" s="58" t="n"/>
     </row>
-    <row r="668">
+    <row r="668" s="60">
       <c r="B668" s="79" t="n"/>
       <c r="C668" s="58" t="n"/>
       <c r="D668" s="58" t="inlineStr">
@@ -19196,7 +18817,7 @@
       <c r="H668" s="58" t="n"/>
       <c r="I668" s="58" t="n"/>
     </row>
-    <row r="669">
+    <row r="669" s="60">
       <c r="B669" s="79" t="n"/>
       <c r="C669" s="58" t="n"/>
       <c r="D669" s="58" t="inlineStr">
@@ -19212,7 +18833,7 @@
       <c r="H669" s="58" t="n"/>
       <c r="I669" s="58" t="n"/>
     </row>
-    <row r="670">
+    <row r="670" s="60">
       <c r="B670" s="79" t="n"/>
       <c r="C670" s="58" t="n"/>
       <c r="D670" s="58" t="inlineStr">
@@ -19228,7 +18849,7 @@
       <c r="H670" s="58" t="n"/>
       <c r="I670" s="58" t="n"/>
     </row>
-    <row r="671">
+    <row r="671" s="60">
       <c r="B671" s="79" t="n"/>
       <c r="C671" s="58" t="n">
         <v>27018</v>
@@ -19252,7 +18873,7 @@
       <c r="H671" s="58" t="n"/>
       <c r="I671" s="58" t="n"/>
     </row>
-    <row r="672">
+    <row r="672" s="60">
       <c r="B672" s="79" t="n"/>
       <c r="C672" s="58" t="n"/>
       <c r="D672" s="58" t="inlineStr">
@@ -19268,7 +18889,7 @@
       <c r="H672" s="58" t="n"/>
       <c r="I672" s="58" t="n"/>
     </row>
-    <row r="673">
+    <row r="673" s="60">
       <c r="B673" s="79" t="n"/>
       <c r="C673" s="58" t="n"/>
       <c r="D673" s="58" t="inlineStr">
@@ -19284,7 +18905,7 @@
       <c r="H673" s="58" t="n"/>
       <c r="I673" s="58" t="n"/>
     </row>
-    <row r="674">
+    <row r="674" s="60">
       <c r="B674" s="79" t="n"/>
       <c r="C674" s="58" t="n"/>
       <c r="D674" s="58" t="inlineStr">
@@ -19300,7 +18921,7 @@
       <c r="H674" s="58" t="n"/>
       <c r="I674" s="58" t="n"/>
     </row>
-    <row r="675">
+    <row r="675" s="60">
       <c r="B675" s="79" t="n"/>
       <c r="C675" s="58" t="n"/>
       <c r="D675" s="58" t="inlineStr">
@@ -19316,7 +18937,7 @@
       <c r="H675" s="58" t="n"/>
       <c r="I675" s="58" t="n"/>
     </row>
-    <row r="676">
+    <row r="676" s="60">
       <c r="B676" s="79" t="n"/>
       <c r="C676" s="58" t="n">
         <v>27019</v>
@@ -19340,7 +18961,7 @@
       <c r="H676" s="58" t="n"/>
       <c r="I676" s="58" t="n"/>
     </row>
-    <row r="677">
+    <row r="677" s="60">
       <c r="B677" s="79" t="n"/>
       <c r="C677" s="58" t="n"/>
       <c r="D677" s="58" t="inlineStr">
@@ -19356,7 +18977,7 @@
       <c r="H677" s="58" t="n"/>
       <c r="I677" s="58" t="n"/>
     </row>
-    <row r="678">
+    <row r="678" s="60">
       <c r="B678" s="79" t="n"/>
       <c r="C678" s="58" t="n"/>
       <c r="D678" s="58" t="inlineStr">
@@ -19372,7 +18993,7 @@
       <c r="H678" s="58" t="n"/>
       <c r="I678" s="58" t="n"/>
     </row>
-    <row r="679">
+    <row r="679" s="60">
       <c r="B679" s="79" t="n"/>
       <c r="C679" s="58" t="n"/>
       <c r="D679" s="58" t="inlineStr">
@@ -19388,7 +19009,7 @@
       <c r="H679" s="58" t="n"/>
       <c r="I679" s="58" t="n"/>
     </row>
-    <row r="680">
+    <row r="680" s="60">
       <c r="B680" s="79" t="n"/>
       <c r="C680" s="58" t="n">
         <v>27601</v>
@@ -19412,7 +19033,7 @@
       <c r="H680" s="58" t="n"/>
       <c r="I680" s="58" t="n"/>
     </row>
-    <row r="681">
+    <row r="681" s="60">
       <c r="B681" s="79" t="n"/>
       <c r="C681" s="58" t="n"/>
       <c r="D681" s="58" t="inlineStr">
@@ -19428,7 +19049,7 @@
       <c r="H681" s="58" t="n"/>
       <c r="I681" s="58" t="n"/>
     </row>
-    <row r="682">
+    <row r="682" s="60">
       <c r="B682" s="79" t="n"/>
       <c r="C682" s="58" t="n"/>
       <c r="D682" s="58" t="inlineStr">
@@ -19444,7 +19065,7 @@
       <c r="H682" s="58" t="n"/>
       <c r="I682" s="58" t="n"/>
     </row>
-    <row r="683">
+    <row r="683" s="60">
       <c r="B683" s="79" t="n"/>
       <c r="C683" s="58" t="n"/>
       <c r="D683" s="58" t="inlineStr">
@@ -19460,7 +19081,7 @@
       <c r="H683" s="58" t="n"/>
       <c r="I683" s="58" t="n"/>
     </row>
-    <row r="684">
+    <row r="684" s="60">
       <c r="B684" s="79" t="n"/>
       <c r="C684" s="58" t="n"/>
       <c r="D684" s="58" t="inlineStr">
@@ -19476,7 +19097,7 @@
       <c r="H684" s="58" t="n"/>
       <c r="I684" s="58" t="n"/>
     </row>
-    <row r="685">
+    <row r="685" s="60">
       <c r="B685" s="79" t="n"/>
       <c r="C685" s="58" t="n">
         <v>27030</v>
@@ -19500,7 +19121,7 @@
       <c r="H685" s="58" t="n"/>
       <c r="I685" s="58" t="n"/>
     </row>
-    <row r="686">
+    <row r="686" s="60">
       <c r="B686" s="79" t="n"/>
       <c r="C686" s="58" t="n"/>
       <c r="D686" s="58" t="inlineStr">
@@ -19516,7 +19137,7 @@
       <c r="H686" s="58" t="n"/>
       <c r="I686" s="58" t="n"/>
     </row>
-    <row r="687">
+    <row r="687" s="60">
       <c r="B687" s="79" t="n"/>
       <c r="C687" s="58" t="n"/>
       <c r="D687" s="58" t="inlineStr">
@@ -19532,7 +19153,7 @@
       <c r="H687" s="58" t="n"/>
       <c r="I687" s="58" t="n"/>
     </row>
-    <row r="688">
+    <row r="688" s="60">
       <c r="B688" s="79" t="n"/>
       <c r="C688" s="58" t="n">
         <v>27300</v>
@@ -19556,7 +19177,7 @@
       <c r="H688" s="58" t="n"/>
       <c r="I688" s="58" t="n"/>
     </row>
-    <row r="689">
+    <row r="689" s="60">
       <c r="B689" s="79" t="n"/>
       <c r="C689" s="58" t="n"/>
       <c r="D689" s="58" t="inlineStr">
@@ -19572,7 +19193,7 @@
       <c r="H689" s="58" t="n"/>
       <c r="I689" s="58" t="n"/>
     </row>
-    <row r="690">
+    <row r="690" s="60">
       <c r="B690" s="79" t="n"/>
       <c r="C690" s="58" t="n"/>
       <c r="D690" s="58" t="inlineStr">
@@ -19588,7 +19209,7 @@
       <c r="H690" s="58" t="n"/>
       <c r="I690" s="58" t="n"/>
     </row>
-    <row r="691">
+    <row r="691" s="60">
       <c r="B691" s="79" t="n"/>
       <c r="C691" s="58" t="n">
         <v>27020</v>
@@ -19612,7 +19233,7 @@
       <c r="H691" s="58" t="n"/>
       <c r="I691" s="58" t="n"/>
     </row>
-    <row r="692">
+    <row r="692" s="60">
       <c r="B692" s="79" t="n"/>
       <c r="C692" s="58" t="n"/>
       <c r="D692" s="58" t="inlineStr">
@@ -19628,7 +19249,7 @@
       <c r="H692" s="58" t="n"/>
       <c r="I692" s="58" t="n"/>
     </row>
-    <row r="693">
+    <row r="693" s="60">
       <c r="B693" s="79" t="n"/>
       <c r="C693" s="58" t="n">
         <v>27021</v>
@@ -19652,7 +19273,7 @@
       <c r="H693" s="58" t="n"/>
       <c r="I693" s="58" t="n"/>
     </row>
-    <row r="694">
+    <row r="694" s="60">
       <c r="B694" s="79" t="n"/>
       <c r="C694" s="58" t="n"/>
       <c r="D694" s="58" t="inlineStr">
@@ -19668,7 +19289,7 @@
       <c r="H694" s="58" t="n"/>
       <c r="I694" s="58" t="n"/>
     </row>
-    <row r="695">
+    <row r="695" s="60">
       <c r="B695" s="79" t="n"/>
       <c r="C695" s="58" t="n"/>
       <c r="D695" s="58" t="inlineStr">
@@ -19684,7 +19305,7 @@
       <c r="H695" s="58" t="n"/>
       <c r="I695" s="58" t="n"/>
     </row>
-    <row r="696">
+    <row r="696" s="60">
       <c r="B696" s="79" t="n"/>
       <c r="C696" s="58" t="n"/>
       <c r="D696" s="58" t="inlineStr">
@@ -19700,7 +19321,7 @@
       <c r="H696" s="58" t="n"/>
       <c r="I696" s="58" t="n"/>
     </row>
-    <row r="697">
+    <row r="697" s="60">
       <c r="B697" s="79" t="n"/>
       <c r="C697" s="58" t="n"/>
       <c r="D697" s="58" t="inlineStr">
@@ -19716,7 +19337,7 @@
       <c r="H697" s="58" t="n"/>
       <c r="I697" s="58" t="n"/>
     </row>
-    <row r="698">
+    <row r="698" s="60">
       <c r="B698" s="79" t="n"/>
       <c r="C698" s="58" t="n">
         <v>27022</v>
@@ -19740,7 +19361,7 @@
       <c r="H698" s="58" t="n"/>
       <c r="I698" s="58" t="n"/>
     </row>
-    <row r="699">
+    <row r="699" s="60">
       <c r="B699" s="79" t="n"/>
       <c r="C699" s="58" t="n"/>
       <c r="D699" s="58" t="inlineStr">
@@ -19756,7 +19377,7 @@
       <c r="H699" s="58" t="n"/>
       <c r="I699" s="58" t="n"/>
     </row>
-    <row r="700">
+    <row r="700" s="60">
       <c r="B700" s="79" t="n"/>
       <c r="C700" s="58" t="n"/>
       <c r="D700" s="58" t="inlineStr">
@@ -19772,7 +19393,7 @@
       <c r="H700" s="58" t="n"/>
       <c r="I700" s="58" t="n"/>
     </row>
-    <row r="701">
+    <row r="701" s="60">
       <c r="B701" s="79" t="n"/>
       <c r="C701" s="58" t="n"/>
       <c r="D701" s="58" t="inlineStr">
@@ -19788,7 +19409,7 @@
       <c r="H701" s="58" t="n"/>
       <c r="I701" s="58" t="n"/>
     </row>
-    <row r="702">
+    <row r="702" s="60">
       <c r="B702" s="79" t="n"/>
       <c r="C702" s="58" t="n"/>
       <c r="D702" s="58" t="inlineStr">
@@ -19804,7 +19425,7 @@
       <c r="H702" s="58" t="n"/>
       <c r="I702" s="58" t="n"/>
     </row>
-    <row r="703">
+    <row r="703" s="60">
       <c r="B703" s="79" t="n"/>
       <c r="C703" s="58" t="n"/>
       <c r="D703" s="58" t="inlineStr">
@@ -19820,7 +19441,7 @@
       <c r="H703" s="58" t="n"/>
       <c r="I703" s="58" t="n"/>
     </row>
-    <row r="704">
+    <row r="704" s="60">
       <c r="B704" s="79" t="n"/>
       <c r="C704" s="58" t="n">
         <v>27023</v>
@@ -19844,7 +19465,7 @@
       <c r="H704" s="58" t="n"/>
       <c r="I704" s="58" t="n"/>
     </row>
-    <row r="705">
+    <row r="705" s="60">
       <c r="B705" s="79" t="n"/>
       <c r="C705" s="58" t="n"/>
       <c r="D705" s="58" t="inlineStr">
@@ -19860,7 +19481,7 @@
       <c r="H705" s="58" t="n"/>
       <c r="I705" s="58" t="n"/>
     </row>
-    <row r="706">
+    <row r="706" s="60">
       <c r="B706" s="79" t="n"/>
       <c r="C706" s="58" t="n"/>
       <c r="D706" s="58" t="inlineStr">
@@ -19876,7 +19497,7 @@
       <c r="H706" s="58" t="n"/>
       <c r="I706" s="58" t="n"/>
     </row>
-    <row r="707">
+    <row r="707" s="60">
       <c r="B707" s="79" t="n"/>
       <c r="C707" s="58" t="n">
         <v>27024</v>
@@ -19900,7 +19521,7 @@
       <c r="H707" s="58" t="n"/>
       <c r="I707" s="58" t="n"/>
     </row>
-    <row r="708">
+    <row r="708" s="60">
       <c r="B708" s="79" t="n"/>
       <c r="C708" s="58" t="n"/>
       <c r="D708" s="58" t="inlineStr">
@@ -19916,7 +19537,7 @@
       <c r="H708" s="58" t="n"/>
       <c r="I708" s="58" t="n"/>
     </row>
-    <row r="709">
+    <row r="709" s="60">
       <c r="B709" s="79" t="n"/>
       <c r="C709" s="58" t="n"/>
       <c r="D709" s="58" t="inlineStr">
@@ -19932,7 +19553,7 @@
       <c r="H709" s="58" t="n"/>
       <c r="I709" s="58" t="n"/>
     </row>
-    <row r="710">
+    <row r="710" s="60">
       <c r="B710" s="79" t="n"/>
       <c r="C710" s="58" t="n">
         <v>27027</v>
@@ -19956,7 +19577,7 @@
       <c r="H710" s="58" t="n"/>
       <c r="I710" s="58" t="n"/>
     </row>
-    <row r="711">
+    <row r="711" s="60">
       <c r="B711" s="79" t="n"/>
       <c r="C711" s="58" t="n"/>
       <c r="D711" s="58" t="inlineStr">
@@ -19972,7 +19593,7 @@
       <c r="H711" s="58" t="n"/>
       <c r="I711" s="58" t="n"/>
     </row>
-    <row r="712">
+    <row r="712" s="60">
       <c r="B712" s="79" t="n"/>
       <c r="C712" s="58" t="n"/>
       <c r="D712" s="58" t="inlineStr">
@@ -19988,7 +19609,7 @@
       <c r="H712" s="58" t="n"/>
       <c r="I712" s="58" t="n"/>
     </row>
-    <row r="713">
+    <row r="713" s="60">
       <c r="B713" s="79" t="n"/>
       <c r="C713" s="58" t="n"/>
       <c r="D713" s="58" t="inlineStr">
@@ -20004,7 +19625,7 @@
       <c r="H713" s="58" t="n"/>
       <c r="I713" s="58" t="n"/>
     </row>
-    <row r="714">
+    <row r="714" s="60">
       <c r="B714" s="79" t="n"/>
       <c r="C714" s="58" t="n"/>
       <c r="D714" s="58" t="inlineStr">
@@ -20020,7 +19641,7 @@
       <c r="H714" s="58" t="n"/>
       <c r="I714" s="58" t="n"/>
     </row>
-    <row r="715">
+    <row r="715" s="60">
       <c r="B715" s="79" t="n"/>
       <c r="C715" s="58" t="n"/>
       <c r="D715" s="58" t="inlineStr">
@@ -20036,7 +19657,7 @@
       <c r="H715" s="58" t="n"/>
       <c r="I715" s="58" t="n"/>
     </row>
-    <row r="716">
+    <row r="716" s="60">
       <c r="B716" s="79" t="n"/>
       <c r="C716" s="58" t="n">
         <v>27026</v>
@@ -20060,7 +19681,7 @@
       <c r="H716" s="58" t="n"/>
       <c r="I716" s="58" t="n"/>
     </row>
-    <row r="717">
+    <row r="717" s="60">
       <c r="B717" s="79" t="n"/>
       <c r="C717" s="58" t="n"/>
       <c r="D717" s="58" t="inlineStr">
@@ -20076,7 +19697,7 @@
       <c r="H717" s="58" t="n"/>
       <c r="I717" s="58" t="n"/>
     </row>
-    <row r="718">
+    <row r="718" s="60">
       <c r="B718" s="79" t="n"/>
       <c r="C718" s="58" t="n"/>
       <c r="D718" s="58" t="inlineStr">
@@ -20092,7 +19713,7 @@
       <c r="H718" s="58" t="n"/>
       <c r="I718" s="58" t="n"/>
     </row>
-    <row r="719">
+    <row r="719" s="60">
       <c r="B719" s="79" t="n"/>
       <c r="C719" s="58" t="n"/>
       <c r="D719" s="58" t="inlineStr">
@@ -20108,7 +19729,7 @@
       <c r="H719" s="58" t="n"/>
       <c r="I719" s="58" t="n"/>
     </row>
-    <row r="720">
+    <row r="720" s="60">
       <c r="B720" s="79" t="n"/>
       <c r="C720" s="58" t="n">
         <v>27025</v>
@@ -20132,7 +19753,7 @@
       <c r="H720" s="58" t="n"/>
       <c r="I720" s="58" t="n"/>
     </row>
-    <row r="721">
+    <row r="721" s="60">
       <c r="B721" s="79" t="n"/>
       <c r="C721" s="58" t="n"/>
       <c r="D721" s="58" t="inlineStr">
@@ -20148,7 +19769,7 @@
       <c r="H721" s="58" t="n"/>
       <c r="I721" s="58" t="n"/>
     </row>
-    <row r="722">
+    <row r="722" s="60">
       <c r="B722" s="79" t="n"/>
       <c r="C722" s="58" t="n">
         <v>27028</v>
@@ -20172,7 +19793,7 @@
       <c r="H722" s="58" t="n"/>
       <c r="I722" s="58" t="n"/>
     </row>
-    <row r="723">
+    <row r="723" s="60">
       <c r="B723" s="79" t="n"/>
       <c r="C723" s="58" t="n"/>
       <c r="D723" s="58" t="inlineStr">
@@ -20188,7 +19809,7 @@
       <c r="H723" s="58" t="n"/>
       <c r="I723" s="58" t="n"/>
     </row>
-    <row r="724">
+    <row r="724" s="60">
       <c r="B724" s="79" t="n"/>
       <c r="C724" s="58" t="n"/>
       <c r="D724" s="58" t="inlineStr">
@@ -20204,7 +19825,7 @@
       <c r="H724" s="58" t="n"/>
       <c r="I724" s="58" t="n"/>
     </row>
-    <row r="725">
+    <row r="725" s="60">
       <c r="B725" s="79" t="n"/>
       <c r="C725" s="58" t="n">
         <v>27029</v>
@@ -20228,7 +19849,7 @@
       <c r="H725" s="58" t="n"/>
       <c r="I725" s="58" t="n"/>
     </row>
-    <row r="726">
+    <row r="726" s="60">
       <c r="B726" s="80" t="n"/>
       <c r="C726" s="58" t="n"/>
       <c r="D726" s="58" t="inlineStr">
@@ -20244,7 +19865,7 @@
       <c r="H726" s="58" t="n"/>
       <c r="I726" s="58" t="n"/>
     </row>
-    <row r="727">
+    <row r="727" s="60">
       <c r="B727" s="58" t="inlineStr">
         <is>
           <t>Sage's Library</t>
@@ -20276,7 +19897,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="728">
+    <row r="728" s="60">
       <c r="B728" s="79" t="n"/>
       <c r="C728" s="58" t="n"/>
       <c r="D728" s="58" t="inlineStr">
@@ -20292,7 +19913,7 @@
       <c r="H728" s="58" t="n"/>
       <c r="I728" s="58" t="n"/>
     </row>
-    <row r="729">
+    <row r="729" s="60">
       <c r="B729" s="79" t="n"/>
       <c r="C729" s="58" t="n"/>
       <c r="D729" s="58" t="inlineStr">
@@ -20308,7 +19929,7 @@
       <c r="H729" s="58" t="n"/>
       <c r="I729" s="58" t="n"/>
     </row>
-    <row r="730">
+    <row r="730" s="60">
       <c r="B730" s="79" t="n"/>
       <c r="C730" s="58" t="n"/>
       <c r="D730" s="58" t="inlineStr">
@@ -20324,7 +19945,7 @@
       <c r="H730" s="58" t="n"/>
       <c r="I730" s="58" t="n"/>
     </row>
-    <row r="731">
+    <row r="731" s="60">
       <c r="B731" s="79" t="n"/>
       <c r="C731" s="58" t="n"/>
       <c r="D731" s="58" t="inlineStr">
@@ -20340,7 +19961,7 @@
       <c r="H731" s="58" t="n"/>
       <c r="I731" s="58" t="n"/>
     </row>
-    <row r="732">
+    <row r="732" s="60">
       <c r="B732" s="79" t="n"/>
       <c r="C732" s="58" t="n"/>
       <c r="D732" s="58" t="inlineStr">
@@ -20356,7 +19977,7 @@
       <c r="H732" s="58" t="n"/>
       <c r="I732" s="58" t="n"/>
     </row>
-    <row r="733">
+    <row r="733" s="60">
       <c r="B733" s="79" t="n"/>
       <c r="C733" s="58" t="n">
         <v>28000</v>
@@ -20380,7 +20001,7 @@
       <c r="H733" s="58" t="n"/>
       <c r="I733" s="58" t="n"/>
     </row>
-    <row r="734">
+    <row r="734" s="60">
       <c r="B734" s="79" t="n"/>
       <c r="C734" s="58" t="n"/>
       <c r="D734" s="58" t="inlineStr">
@@ -20396,7 +20017,7 @@
       <c r="H734" s="58" t="n"/>
       <c r="I734" s="58" t="n"/>
     </row>
-    <row r="735">
+    <row r="735" s="60">
       <c r="B735" s="79" t="n"/>
       <c r="C735" s="58" t="n">
         <v>28001</v>
@@ -20420,7 +20041,7 @@
       <c r="H735" s="58" t="n"/>
       <c r="I735" s="58" t="n"/>
     </row>
-    <row r="736">
+    <row r="736" s="60">
       <c r="B736" s="79" t="n"/>
       <c r="C736" s="58" t="n"/>
       <c r="D736" s="58" t="inlineStr">
@@ -20436,7 +20057,7 @@
       <c r="H736" s="58" t="n"/>
       <c r="I736" s="58" t="n"/>
     </row>
-    <row r="737">
+    <row r="737" s="60">
       <c r="B737" s="79" t="n"/>
       <c r="C737" s="58" t="n"/>
       <c r="D737" s="58" t="inlineStr">
@@ -20452,7 +20073,7 @@
       <c r="H737" s="58" t="n"/>
       <c r="I737" s="58" t="n"/>
     </row>
-    <row r="738">
+    <row r="738" s="60">
       <c r="B738" s="79" t="n"/>
       <c r="C738" s="58" t="n">
         <v>28003</v>
@@ -20476,7 +20097,7 @@
       <c r="H738" s="58" t="n"/>
       <c r="I738" s="58" t="n"/>
     </row>
-    <row r="739">
+    <row r="739" s="60">
       <c r="B739" s="79" t="n"/>
       <c r="C739" s="58" t="n"/>
       <c r="D739" s="58" t="inlineStr">
@@ -20492,7 +20113,7 @@
       <c r="H739" s="58" t="n"/>
       <c r="I739" s="58" t="n"/>
     </row>
-    <row r="740">
+    <row r="740" s="60">
       <c r="B740" s="79" t="n"/>
       <c r="C740" s="58" t="n"/>
       <c r="D740" s="58" t="inlineStr">
@@ -20508,7 +20129,7 @@
       <c r="H740" s="58" t="n"/>
       <c r="I740" s="58" t="n"/>
     </row>
-    <row r="741">
+    <row r="741" s="60">
       <c r="B741" s="79" t="n"/>
       <c r="C741" s="58" t="n"/>
       <c r="D741" s="58" t="inlineStr">
@@ -20524,7 +20145,7 @@
       <c r="H741" s="58" t="n"/>
       <c r="I741" s="58" t="n"/>
     </row>
-    <row r="742">
+    <row r="742" s="60">
       <c r="B742" s="79" t="n"/>
       <c r="C742" s="58" t="n">
         <v>28004</v>
@@ -20548,7 +20169,7 @@
       <c r="H742" s="58" t="n"/>
       <c r="I742" s="58" t="n"/>
     </row>
-    <row r="743">
+    <row r="743" s="60">
       <c r="B743" s="79" t="n"/>
       <c r="C743" s="58" t="n"/>
       <c r="D743" s="58" t="inlineStr">
@@ -20564,7 +20185,7 @@
       <c r="H743" s="58" t="n"/>
       <c r="I743" s="58" t="n"/>
     </row>
-    <row r="744">
+    <row r="744" s="60">
       <c r="B744" s="79" t="n"/>
       <c r="C744" s="58" t="n"/>
       <c r="D744" s="58" t="inlineStr">
@@ -20580,7 +20201,7 @@
       <c r="H744" s="58" t="n"/>
       <c r="I744" s="58" t="n"/>
     </row>
-    <row r="745">
+    <row r="745" s="60">
       <c r="B745" s="79" t="n"/>
       <c r="C745" s="58" t="n"/>
       <c r="D745" s="58" t="inlineStr">
@@ -20596,7 +20217,7 @@
       <c r="H745" s="58" t="n"/>
       <c r="I745" s="58" t="n"/>
     </row>
-    <row r="746">
+    <row r="746" s="60">
       <c r="B746" s="79" t="n"/>
       <c r="C746" s="58" t="n"/>
       <c r="D746" s="58" t="inlineStr">
@@ -20612,7 +20233,7 @@
       <c r="H746" s="58" t="n"/>
       <c r="I746" s="58" t="n"/>
     </row>
-    <row r="747">
+    <row r="747" s="60">
       <c r="B747" s="79" t="n"/>
       <c r="C747" s="58" t="n"/>
       <c r="D747" s="58" t="inlineStr">
@@ -20628,7 +20249,7 @@
       <c r="H747" s="58" t="n"/>
       <c r="I747" s="58" t="n"/>
     </row>
-    <row r="748">
+    <row r="748" s="60">
       <c r="B748" s="79" t="n"/>
       <c r="C748" s="58" t="n"/>
       <c r="D748" s="58" t="inlineStr">
@@ -20644,7 +20265,7 @@
       <c r="H748" s="58" t="n"/>
       <c r="I748" s="58" t="n"/>
     </row>
-    <row r="749">
+    <row r="749" s="60">
       <c r="B749" s="79" t="n"/>
       <c r="C749" s="58" t="n">
         <v>28005</v>
@@ -20668,7 +20289,7 @@
       <c r="H749" s="58" t="n"/>
       <c r="I749" s="58" t="n"/>
     </row>
-    <row r="750">
+    <row r="750" s="60">
       <c r="B750" s="79" t="n"/>
       <c r="C750" s="58" t="n"/>
       <c r="D750" s="58" t="inlineStr">
@@ -20684,7 +20305,7 @@
       <c r="H750" s="58" t="n"/>
       <c r="I750" s="58" t="n"/>
     </row>
-    <row r="751">
+    <row r="751" s="60">
       <c r="B751" s="79" t="n"/>
       <c r="C751" s="58" t="n"/>
       <c r="D751" s="58" t="inlineStr">
@@ -20700,7 +20321,7 @@
       <c r="H751" s="58" t="n"/>
       <c r="I751" s="58" t="n"/>
     </row>
-    <row r="752">
+    <row r="752" s="60">
       <c r="B752" s="79" t="n"/>
       <c r="C752" s="58" t="n"/>
       <c r="D752" s="58" t="inlineStr">
@@ -20716,7 +20337,7 @@
       <c r="H752" s="58" t="n"/>
       <c r="I752" s="58" t="n"/>
     </row>
-    <row r="753">
+    <row r="753" s="60">
       <c r="B753" s="79" t="n"/>
       <c r="C753" s="58" t="n">
         <v>28006</v>
@@ -20740,7 +20361,7 @@
       <c r="H753" s="58" t="n"/>
       <c r="I753" s="58" t="n"/>
     </row>
-    <row r="754">
+    <row r="754" s="60">
       <c r="B754" s="79" t="n"/>
       <c r="C754" s="58" t="n"/>
       <c r="D754" s="58" t="inlineStr">
@@ -20756,7 +20377,7 @@
       <c r="H754" s="58" t="n"/>
       <c r="I754" s="58" t="n"/>
     </row>
-    <row r="755">
+    <row r="755" s="60">
       <c r="B755" s="79" t="n"/>
       <c r="C755" s="58" t="n"/>
       <c r="D755" s="58" t="inlineStr">
@@ -20772,7 +20393,7 @@
       <c r="H755" s="58" t="n"/>
       <c r="I755" s="58" t="n"/>
     </row>
-    <row r="756">
+    <row r="756" s="60">
       <c r="B756" s="79" t="n"/>
       <c r="C756" s="58" t="n"/>
       <c r="D756" s="58" t="inlineStr">
@@ -20788,7 +20409,7 @@
       <c r="H756" s="58" t="n"/>
       <c r="I756" s="58" t="n"/>
     </row>
-    <row r="757">
+    <row r="757" s="60">
       <c r="B757" s="79" t="n"/>
       <c r="C757" s="58" t="n"/>
       <c r="D757" s="58" t="inlineStr">
@@ -20804,7 +20425,7 @@
       <c r="H757" s="58" t="n"/>
       <c r="I757" s="58" t="n"/>
     </row>
-    <row r="758">
+    <row r="758" s="60">
       <c r="B758" s="79" t="n"/>
       <c r="C758" s="58" t="n"/>
       <c r="D758" s="58" t="inlineStr">
@@ -20820,7 +20441,7 @@
       <c r="H758" s="58" t="n"/>
       <c r="I758" s="58" t="n"/>
     </row>
-    <row r="759">
+    <row r="759" s="60">
       <c r="B759" s="79" t="n"/>
       <c r="C759" s="58" t="n">
         <v>28007</v>
@@ -20844,7 +20465,7 @@
       <c r="H759" s="58" t="n"/>
       <c r="I759" s="58" t="n"/>
     </row>
-    <row r="760">
+    <row r="760" s="60">
       <c r="B760" s="79" t="n"/>
       <c r="C760" s="58" t="n"/>
       <c r="D760" s="58" t="inlineStr">
@@ -20860,7 +20481,7 @@
       <c r="H760" s="58" t="n"/>
       <c r="I760" s="58" t="n"/>
     </row>
-    <row r="761">
+    <row r="761" s="60">
       <c r="B761" s="79" t="n"/>
       <c r="C761" s="58" t="n"/>
       <c r="D761" s="58" t="inlineStr">
@@ -20876,7 +20497,7 @@
       <c r="H761" s="58" t="n"/>
       <c r="I761" s="58" t="n"/>
     </row>
-    <row r="762">
+    <row r="762" s="60">
       <c r="B762" s="79" t="n"/>
       <c r="C762" s="58" t="n"/>
       <c r="D762" s="58" t="inlineStr">
@@ -20892,7 +20513,7 @@
       <c r="H762" s="58" t="n"/>
       <c r="I762" s="58" t="n"/>
     </row>
-    <row r="763">
+    <row r="763" s="60">
       <c r="B763" s="79" t="n"/>
       <c r="C763" s="58" t="n">
         <v>28008</v>
@@ -20916,7 +20537,7 @@
       <c r="H763" s="58" t="n"/>
       <c r="I763" s="58" t="n"/>
     </row>
-    <row r="764">
+    <row r="764" s="60">
       <c r="B764" s="79" t="n"/>
       <c r="C764" s="58" t="n"/>
       <c r="D764" s="58" t="inlineStr">
@@ -20932,7 +20553,7 @@
       <c r="H764" s="58" t="n"/>
       <c r="I764" s="58" t="n"/>
     </row>
-    <row r="765">
+    <row r="765" s="60">
       <c r="B765" s="79" t="n"/>
       <c r="C765" s="58" t="n"/>
       <c r="D765" s="58" t="inlineStr">
@@ -20948,7 +20569,7 @@
       <c r="H765" s="58" t="n"/>
       <c r="I765" s="58" t="n"/>
     </row>
-    <row r="766">
+    <row r="766" s="60">
       <c r="B766" s="79" t="n"/>
       <c r="C766" s="58" t="n">
         <v>28009</v>
@@ -20972,7 +20593,7 @@
       <c r="H766" s="58" t="n"/>
       <c r="I766" s="58" t="n"/>
     </row>
-    <row r="767">
+    <row r="767" s="60">
       <c r="B767" s="79" t="n"/>
       <c r="C767" s="58" t="n"/>
       <c r="D767" s="58" t="inlineStr">
@@ -20988,7 +20609,7 @@
       <c r="H767" s="58" t="n"/>
       <c r="I767" s="58" t="n"/>
     </row>
-    <row r="768">
+    <row r="768" s="60">
       <c r="B768" s="79" t="n"/>
       <c r="C768" s="58" t="n">
         <v>28010</v>
@@ -21012,7 +20633,7 @@
       <c r="H768" s="58" t="n"/>
       <c r="I768" s="58" t="n"/>
     </row>
-    <row r="769">
+    <row r="769" s="60">
       <c r="B769" s="79" t="n"/>
       <c r="C769" s="58" t="n"/>
       <c r="D769" s="58" t="inlineStr">
@@ -21028,7 +20649,7 @@
       <c r="H769" s="58" t="n"/>
       <c r="I769" s="58" t="n"/>
     </row>
-    <row r="770">
+    <row r="770" s="60">
       <c r="B770" s="79" t="n"/>
       <c r="C770" s="58" t="n"/>
       <c r="D770" s="58" t="inlineStr">
@@ -21044,7 +20665,7 @@
       <c r="H770" s="58" t="n"/>
       <c r="I770" s="58" t="n"/>
     </row>
-    <row r="771">
+    <row r="771" s="60">
       <c r="B771" s="79" t="n"/>
       <c r="C771" s="58" t="n"/>
       <c r="D771" s="58" t="inlineStr">
@@ -21060,7 +20681,7 @@
       <c r="H771" s="58" t="n"/>
       <c r="I771" s="58" t="n"/>
     </row>
-    <row r="772">
+    <row r="772" s="60">
       <c r="B772" s="79" t="n"/>
       <c r="C772" s="58" t="n">
         <v>28011</v>
@@ -21084,7 +20705,7 @@
       <c r="H772" s="58" t="n"/>
       <c r="I772" s="58" t="n"/>
     </row>
-    <row r="773">
+    <row r="773" s="60">
       <c r="B773" s="79" t="n"/>
       <c r="C773" s="58" t="n"/>
       <c r="D773" s="58" t="inlineStr">
@@ -21100,7 +20721,7 @@
       <c r="H773" s="58" t="n"/>
       <c r="I773" s="58" t="n"/>
     </row>
-    <row r="774">
+    <row r="774" s="60">
       <c r="B774" s="79" t="n"/>
       <c r="C774" s="58" t="n"/>
       <c r="D774" s="58" t="inlineStr">
@@ -21116,7 +20737,7 @@
       <c r="H774" s="58" t="n"/>
       <c r="I774" s="58" t="n"/>
     </row>
-    <row r="775">
+    <row r="775" s="60">
       <c r="B775" s="79" t="n"/>
       <c r="C775" s="58" t="n">
         <v>28012</v>
@@ -21140,7 +20761,7 @@
       <c r="H775" s="58" t="n"/>
       <c r="I775" s="58" t="n"/>
     </row>
-    <row r="776">
+    <row r="776" s="60">
       <c r="B776" s="79" t="n"/>
       <c r="C776" s="58" t="n"/>
       <c r="D776" s="58" t="inlineStr">
@@ -21156,7 +20777,7 @@
       <c r="H776" s="58" t="n"/>
       <c r="I776" s="58" t="n"/>
     </row>
-    <row r="777">
+    <row r="777" s="60">
       <c r="B777" s="79" t="n"/>
       <c r="C777" s="58" t="n"/>
       <c r="D777" s="58" t="inlineStr">
@@ -21172,7 +20793,7 @@
       <c r="H777" s="58" t="n"/>
       <c r="I777" s="58" t="n"/>
     </row>
-    <row r="778">
+    <row r="778" s="60">
       <c r="B778" s="79" t="n"/>
       <c r="C778" s="58" t="n"/>
       <c r="D778" s="58" t="inlineStr">
@@ -21188,7 +20809,7 @@
       <c r="H778" s="58" t="n"/>
       <c r="I778" s="58" t="n"/>
     </row>
-    <row r="779">
+    <row r="779" s="60">
       <c r="B779" s="79" t="n"/>
       <c r="C779" s="58" t="n"/>
       <c r="D779" s="58" t="inlineStr">
@@ -21204,7 +20825,7 @@
       <c r="H779" s="58" t="n"/>
       <c r="I779" s="58" t="n"/>
     </row>
-    <row r="780">
+    <row r="780" s="60">
       <c r="B780" s="79" t="n"/>
       <c r="C780" s="58" t="n"/>
       <c r="D780" s="58" t="inlineStr">
@@ -21220,7 +20841,7 @@
       <c r="H780" s="58" t="n"/>
       <c r="I780" s="58" t="n"/>
     </row>
-    <row r="781">
+    <row r="781" s="60">
       <c r="B781" s="79" t="n"/>
       <c r="C781" s="58" t="n"/>
       <c r="D781" s="58" t="inlineStr">
@@ -21236,7 +20857,7 @@
       <c r="H781" s="58" t="n"/>
       <c r="I781" s="58" t="n"/>
     </row>
-    <row r="782">
+    <row r="782" s="60">
       <c r="B782" s="79" t="n"/>
       <c r="C782" s="58" t="n">
         <v>28013</v>
@@ -21260,7 +20881,7 @@
       <c r="H782" s="58" t="n"/>
       <c r="I782" s="58" t="n"/>
     </row>
-    <row r="783">
+    <row r="783" s="60">
       <c r="B783" s="79" t="n"/>
       <c r="C783" s="58" t="n"/>
       <c r="D783" s="58" t="inlineStr">
@@ -21276,7 +20897,7 @@
       <c r="H783" s="58" t="n"/>
       <c r="I783" s="58" t="n"/>
     </row>
-    <row r="784">
+    <row r="784" s="60">
       <c r="B784" s="79" t="n"/>
       <c r="C784" s="58" t="n"/>
       <c r="D784" s="58" t="inlineStr">
@@ -21292,7 +20913,7 @@
       <c r="H784" s="58" t="n"/>
       <c r="I784" s="58" t="n"/>
     </row>
-    <row r="785">
+    <row r="785" s="60">
       <c r="B785" s="79" t="n"/>
       <c r="C785" s="58" t="n">
         <v>28014</v>
@@ -21316,7 +20937,7 @@
       <c r="H785" s="58" t="n"/>
       <c r="I785" s="58" t="n"/>
     </row>
-    <row r="786">
+    <row r="786" s="60">
       <c r="B786" s="79" t="n"/>
       <c r="C786" s="58" t="n"/>
       <c r="D786" s="58" t="inlineStr">
@@ -21332,7 +20953,7 @@
       <c r="H786" s="58" t="n"/>
       <c r="I786" s="58" t="n"/>
     </row>
-    <row r="787">
+    <row r="787" s="60">
       <c r="B787" s="79" t="n"/>
       <c r="C787" s="58" t="n"/>
       <c r="D787" s="58" t="inlineStr">
@@ -21348,7 +20969,7 @@
       <c r="H787" s="58" t="n"/>
       <c r="I787" s="58" t="n"/>
     </row>
-    <row r="788">
+    <row r="788" s="60">
       <c r="B788" s="79" t="n"/>
       <c r="C788" s="58" t="n"/>
       <c r="D788" s="58" t="inlineStr">
@@ -21364,7 +20985,7 @@
       <c r="H788" s="58" t="n"/>
       <c r="I788" s="58" t="n"/>
     </row>
-    <row r="789">
+    <row r="789" s="60">
       <c r="B789" s="79" t="n"/>
       <c r="C789" s="58" t="n"/>
       <c r="D789" s="58" t="inlineStr">
@@ -21380,7 +21001,7 @@
       <c r="H789" s="58" t="n"/>
       <c r="I789" s="58" t="n"/>
     </row>
-    <row r="790">
+    <row r="790" s="60">
       <c r="B790" s="79" t="n"/>
       <c r="C790" s="58" t="n"/>
       <c r="D790" s="58" t="inlineStr">
@@ -21396,7 +21017,7 @@
       <c r="H790" s="58" t="n"/>
       <c r="I790" s="58" t="n"/>
     </row>
-    <row r="791">
+    <row r="791" s="60">
       <c r="B791" s="79" t="n"/>
       <c r="C791" s="58" t="n">
         <v>28015</v>
@@ -21420,7 +21041,7 @@
       <c r="H791" s="58" t="n"/>
       <c r="I791" s="58" t="n"/>
     </row>
-    <row r="792">
+    <row r="792" s="60">
       <c r="B792" s="79" t="n"/>
       <c r="C792" s="58" t="n"/>
       <c r="D792" s="58" t="inlineStr">
@@ -21436,7 +21057,7 @@
       <c r="H792" s="58" t="n"/>
       <c r="I792" s="58" t="n"/>
     </row>
-    <row r="793">
+    <row r="793" s="60">
       <c r="B793" s="79" t="n"/>
       <c r="C793" s="58" t="n"/>
       <c r="D793" s="58" t="inlineStr">
@@ -21452,7 +21073,7 @@
       <c r="H793" s="58" t="n"/>
       <c r="I793" s="58" t="n"/>
     </row>
-    <row r="794">
+    <row r="794" s="60">
       <c r="B794" s="79" t="n"/>
       <c r="C794" s="58" t="n">
         <v>28600</v>
@@ -21476,7 +21097,7 @@
       <c r="H794" s="58" t="n"/>
       <c r="I794" s="58" t="n"/>
     </row>
-    <row r="795">
+    <row r="795" s="60">
       <c r="B795" s="79" t="n"/>
       <c r="C795" s="58" t="n"/>
       <c r="D795" s="58" t="inlineStr">
@@ -21492,7 +21113,7 @@
       <c r="H795" s="58" t="n"/>
       <c r="I795" s="58" t="n"/>
     </row>
-    <row r="796">
+    <row r="796" s="60">
       <c r="B796" s="79" t="n"/>
       <c r="C796" s="58" t="n"/>
       <c r="D796" s="58" t="inlineStr">
@@ -21508,7 +21129,7 @@
       <c r="H796" s="58" t="n"/>
       <c r="I796" s="58" t="n"/>
     </row>
-    <row r="797">
+    <row r="797" s="60">
       <c r="B797" s="79" t="n"/>
       <c r="C797" s="58" t="n"/>
       <c r="D797" s="58" t="inlineStr">
@@ -21524,7 +21145,7 @@
       <c r="H797" s="58" t="n"/>
       <c r="I797" s="58" t="n"/>
     </row>
-    <row r="798">
+    <row r="798" s="60">
       <c r="B798" s="79" t="n"/>
       <c r="C798" s="58" t="n">
         <v>28016</v>
@@ -21548,7 +21169,7 @@
       <c r="H798" s="58" t="n"/>
       <c r="I798" s="58" t="n"/>
     </row>
-    <row r="799">
+    <row r="799" s="60">
       <c r="B799" s="79" t="n"/>
       <c r="C799" s="58" t="n"/>
       <c r="D799" s="58" t="inlineStr">
@@ -21564,7 +21185,7 @@
       <c r="H799" s="58" t="n"/>
       <c r="I799" s="58" t="n"/>
     </row>
-    <row r="800">
+    <row r="800" s="60">
       <c r="B800" s="79" t="n"/>
       <c r="C800" s="58" t="n"/>
       <c r="D800" s="58" t="inlineStr">
@@ -21580,7 +21201,7 @@
       <c r="H800" s="58" t="n"/>
       <c r="I800" s="58" t="n"/>
     </row>
-    <row r="801">
+    <row r="801" s="60">
       <c r="B801" s="79" t="n"/>
       <c r="C801" s="58" t="n"/>
       <c r="D801" s="58" t="inlineStr">
@@ -21596,7 +21217,7 @@
       <c r="H801" s="58" t="n"/>
       <c r="I801" s="58" t="n"/>
     </row>
-    <row r="802">
+    <row r="802" s="60">
       <c r="B802" s="79" t="n"/>
       <c r="C802" s="58" t="n"/>
       <c r="D802" s="58" t="inlineStr">
@@ -21612,7 +21233,7 @@
       <c r="H802" s="58" t="n"/>
       <c r="I802" s="58" t="n"/>
     </row>
-    <row r="803">
+    <row r="803" s="60">
       <c r="B803" s="79" t="n"/>
       <c r="C803" s="58" t="n"/>
       <c r="D803" s="58" t="inlineStr">
@@ -21628,7 +21249,7 @@
       <c r="H803" s="58" t="n"/>
       <c r="I803" s="58" t="n"/>
     </row>
-    <row r="804">
+    <row r="804" s="60">
       <c r="B804" s="79" t="n"/>
       <c r="C804" s="58" t="n"/>
       <c r="D804" s="58" t="inlineStr">
@@ -21644,7 +21265,7 @@
       <c r="H804" s="58" t="n"/>
       <c r="I804" s="58" t="n"/>
     </row>
-    <row r="805">
+    <row r="805" s="60">
       <c r="B805" s="79" t="n"/>
       <c r="C805" s="58" t="n">
         <v>28017</v>
@@ -21668,7 +21289,7 @@
       <c r="H805" s="58" t="n"/>
       <c r="I805" s="58" t="n"/>
     </row>
-    <row r="806">
+    <row r="806" s="60">
       <c r="B806" s="79" t="n"/>
       <c r="C806" s="58" t="n"/>
       <c r="D806" s="58" t="inlineStr">
@@ -21684,7 +21305,7 @@
       <c r="H806" s="58" t="n"/>
       <c r="I806" s="58" t="n"/>
     </row>
-    <row r="807">
+    <row r="807" s="60">
       <c r="B807" s="79" t="n"/>
       <c r="C807" s="58" t="n"/>
       <c r="D807" s="58" t="inlineStr">
@@ -21700,7 +21321,7 @@
       <c r="H807" s="58" t="n"/>
       <c r="I807" s="58" t="n"/>
     </row>
-    <row r="808">
+    <row r="808" s="60">
       <c r="B808" s="79" t="n"/>
       <c r="C808" s="58" t="n"/>
       <c r="D808" s="58" t="inlineStr">
@@ -21716,7 +21337,7 @@
       <c r="H808" s="58" t="n"/>
       <c r="I808" s="58" t="n"/>
     </row>
-    <row r="809">
+    <row r="809" s="60">
       <c r="B809" s="79" t="n"/>
       <c r="C809" s="58" t="n">
         <v>28018</v>
@@ -21740,7 +21361,7 @@
       <c r="H809" s="58" t="n"/>
       <c r="I809" s="58" t="n"/>
     </row>
-    <row r="810">
+    <row r="810" s="60">
       <c r="B810" s="79" t="n"/>
       <c r="C810" s="58" t="n"/>
       <c r="D810" s="58" t="inlineStr">
@@ -21756,7 +21377,7 @@
       <c r="H810" s="58" t="n"/>
       <c r="I810" s="58" t="n"/>
     </row>
-    <row r="811">
+    <row r="811" s="60">
       <c r="B811" s="79" t="n"/>
       <c r="C811" s="58" t="n"/>
       <c r="D811" s="58" t="inlineStr">
@@ -21772,7 +21393,7 @@
       <c r="H811" s="58" t="n"/>
       <c r="I811" s="58" t="n"/>
     </row>
-    <row r="812">
+    <row r="812" s="60">
       <c r="B812" s="79" t="n"/>
       <c r="C812" s="58" t="n"/>
       <c r="D812" s="58" t="inlineStr">
@@ -21788,7 +21409,7 @@
       <c r="H812" s="58" t="n"/>
       <c r="I812" s="58" t="n"/>
     </row>
-    <row r="813">
+    <row r="813" s="60">
       <c r="B813" s="79" t="n"/>
       <c r="C813" s="58" t="n"/>
       <c r="D813" s="58" t="inlineStr">
@@ -21804,7 +21425,7 @@
       <c r="H813" s="58" t="n"/>
       <c r="I813" s="58" t="n"/>
     </row>
-    <row r="814">
+    <row r="814" s="60">
       <c r="B814" s="79" t="n"/>
       <c r="C814" s="58" t="n"/>
       <c r="D814" s="58" t="inlineStr">
@@ -21820,7 +21441,7 @@
       <c r="H814" s="58" t="n"/>
       <c r="I814" s="58" t="n"/>
     </row>
-    <row r="815">
+    <row r="815" s="60">
       <c r="B815" s="79" t="n"/>
       <c r="C815" s="58" t="n"/>
       <c r="D815" s="58" t="inlineStr">
@@ -21836,7 +21457,7 @@
       <c r="H815" s="58" t="n"/>
       <c r="I815" s="58" t="n"/>
     </row>
-    <row r="816">
+    <row r="816" s="60">
       <c r="B816" s="79" t="n"/>
       <c r="C816" s="58" t="n">
         <v>28019</v>
@@ -21860,7 +21481,7 @@
       <c r="H816" s="58" t="n"/>
       <c r="I816" s="58" t="n"/>
     </row>
-    <row r="817">
+    <row r="817" s="60">
       <c r="B817" s="79" t="n"/>
       <c r="C817" s="58" t="n"/>
       <c r="D817" s="58" t="inlineStr">
@@ -21876,7 +21497,7 @@
       <c r="H817" s="58" t="n"/>
       <c r="I817" s="58" t="n"/>
     </row>
-    <row r="818">
+    <row r="818" s="60">
       <c r="B818" s="79" t="n"/>
       <c r="C818" s="58" t="n"/>
       <c r="D818" s="58" t="inlineStr">
@@ -21892,7 +21513,7 @@
       <c r="H818" s="58" t="n"/>
       <c r="I818" s="58" t="n"/>
     </row>
-    <row r="819">
+    <row r="819" s="60">
       <c r="B819" s="79" t="n"/>
       <c r="C819" s="58" t="n"/>
       <c r="D819" s="58" t="inlineStr">
@@ -21908,7 +21529,7 @@
       <c r="H819" s="58" t="n"/>
       <c r="I819" s="58" t="n"/>
     </row>
-    <row r="820">
+    <row r="820" s="60">
       <c r="B820" s="79" t="n"/>
       <c r="C820" s="58" t="n"/>
       <c r="D820" s="58" t="inlineStr">
@@ -21924,7 +21545,7 @@
       <c r="H820" s="58" t="n"/>
       <c r="I820" s="58" t="n"/>
     </row>
-    <row r="821">
+    <row r="821" s="60">
       <c r="B821" s="79" t="n"/>
       <c r="C821" s="58" t="n">
         <v>28020</v>
@@ -21948,7 +21569,7 @@
       <c r="H821" s="58" t="n"/>
       <c r="I821" s="58" t="n"/>
     </row>
-    <row r="822">
+    <row r="822" s="60">
       <c r="B822" s="79" t="n"/>
       <c r="C822" s="58" t="n"/>
       <c r="D822" s="58" t="inlineStr">
@@ -21964,7 +21585,7 @@
       <c r="H822" s="58" t="n"/>
       <c r="I822" s="58" t="n"/>
     </row>
-    <row r="823">
+    <row r="823" s="60">
       <c r="B823" s="79" t="n"/>
       <c r="C823" s="58" t="n"/>
       <c r="D823" s="58" t="inlineStr">
@@ -21980,7 +21601,7 @@
       <c r="H823" s="58" t="n"/>
       <c r="I823" s="58" t="n"/>
     </row>
-    <row r="824">
+    <row r="824" s="60">
       <c r="B824" s="79" t="n"/>
       <c r="C824" s="58" t="n"/>
       <c r="D824" s="58" t="inlineStr">
@@ -21996,7 +21617,7 @@
       <c r="H824" s="58" t="n"/>
       <c r="I824" s="58" t="n"/>
     </row>
-    <row r="825">
+    <row r="825" s="60">
       <c r="B825" s="79" t="n"/>
       <c r="C825" s="58" t="n"/>
       <c r="D825" s="58" t="inlineStr">
@@ -22012,7 +21633,7 @@
       <c r="H825" s="58" t="n"/>
       <c r="I825" s="58" t="n"/>
     </row>
-    <row r="826">
+    <row r="826" s="60">
       <c r="B826" s="79" t="n"/>
       <c r="C826" s="58" t="n">
         <v>28021</v>
@@ -22036,7 +21657,7 @@
       <c r="H826" s="58" t="n"/>
       <c r="I826" s="58" t="n"/>
     </row>
-    <row r="827">
+    <row r="827" s="60">
       <c r="B827" s="79" t="n"/>
       <c r="C827" s="58" t="n"/>
       <c r="D827" s="58" t="inlineStr">
@@ -22052,7 +21673,7 @@
       <c r="H827" s="58" t="n"/>
       <c r="I827" s="58" t="n"/>
     </row>
-    <row r="828">
+    <row r="828" s="60">
       <c r="B828" s="79" t="n"/>
       <c r="C828" s="58" t="n"/>
       <c r="D828" s="58" t="inlineStr">
@@ -22068,7 +21689,7 @@
       <c r="H828" s="58" t="n"/>
       <c r="I828" s="58" t="n"/>
     </row>
-    <row r="829">
+    <row r="829" s="60">
       <c r="B829" s="79" t="n"/>
       <c r="C829" s="58" t="n"/>
       <c r="D829" s="58" t="inlineStr">
@@ -22084,7 +21705,7 @@
       <c r="H829" s="58" t="n"/>
       <c r="I829" s="58" t="n"/>
     </row>
-    <row r="830">
+    <row r="830" s="60">
       <c r="B830" s="79" t="n"/>
       <c r="C830" s="58" t="n"/>
       <c r="D830" s="58" t="inlineStr">
@@ -22100,7 +21721,7 @@
       <c r="H830" s="58" t="n"/>
       <c r="I830" s="58" t="n"/>
     </row>
-    <row r="831">
+    <row r="831" s="60">
       <c r="B831" s="79" t="n"/>
       <c r="C831" s="58" t="n"/>
       <c r="D831" s="58" t="inlineStr">
@@ -22116,7 +21737,7 @@
       <c r="H831" s="58" t="n"/>
       <c r="I831" s="58" t="n"/>
     </row>
-    <row r="832">
+    <row r="832" s="60">
       <c r="B832" s="79" t="n"/>
       <c r="C832" s="58" t="n"/>
       <c r="D832" s="58" t="inlineStr">
@@ -22132,7 +21753,7 @@
       <c r="H832" s="58" t="n"/>
       <c r="I832" s="58" t="n"/>
     </row>
-    <row r="833">
+    <row r="833" s="60">
       <c r="B833" s="79" t="n"/>
       <c r="C833" s="58" t="n">
         <v>28022</v>
@@ -22156,7 +21777,7 @@
       <c r="H833" s="58" t="n"/>
       <c r="I833" s="58" t="n"/>
     </row>
-    <row r="834">
+    <row r="834" s="60">
       <c r="B834" s="79" t="n"/>
       <c r="C834" s="58" t="n"/>
       <c r="D834" s="58" t="inlineStr">
@@ -22172,7 +21793,7 @@
       <c r="H834" s="58" t="n"/>
       <c r="I834" s="58" t="n"/>
     </row>
-    <row r="835">
+    <row r="835" s="60">
       <c r="B835" s="79" t="n"/>
       <c r="C835" s="58" t="n"/>
       <c r="D835" s="58" t="inlineStr">
@@ -22188,7 +21809,7 @@
       <c r="H835" s="58" t="n"/>
       <c r="I835" s="58" t="n"/>
     </row>
-    <row r="836">
+    <row r="836" s="60">
       <c r="B836" s="79" t="n"/>
       <c r="C836" s="58" t="n"/>
       <c r="D836" s="58" t="inlineStr">
@@ -22204,7 +21825,7 @@
       <c r="H836" s="58" t="n"/>
       <c r="I836" s="58" t="n"/>
     </row>
-    <row r="837">
+    <row r="837" s="60">
       <c r="B837" s="79" t="n"/>
       <c r="C837" s="58" t="n"/>
       <c r="D837" s="58" t="inlineStr">
@@ -22220,7 +21841,7 @@
       <c r="H837" s="58" t="n"/>
       <c r="I837" s="58" t="n"/>
     </row>
-    <row r="838">
+    <row r="838" s="60">
       <c r="B838" s="79" t="n"/>
       <c r="C838" s="58" t="n"/>
       <c r="D838" s="58" t="inlineStr">
@@ -22236,7 +21857,7 @@
       <c r="H838" s="58" t="n"/>
       <c r="I838" s="58" t="n"/>
     </row>
-    <row r="839">
+    <row r="839" s="60">
       <c r="B839" s="79" t="n"/>
       <c r="C839" s="58" t="n"/>
       <c r="D839" s="58" t="inlineStr">
@@ -22252,7 +21873,7 @@
       <c r="H839" s="58" t="n"/>
       <c r="I839" s="58" t="n"/>
     </row>
-    <row r="840">
+    <row r="840" s="60">
       <c r="B840" s="79" t="n"/>
       <c r="C840" s="58" t="n">
         <v>28023</v>
@@ -22276,7 +21897,7 @@
       <c r="H840" s="58" t="n"/>
       <c r="I840" s="58" t="n"/>
     </row>
-    <row r="841">
+    <row r="841" s="60">
       <c r="B841" s="79" t="n"/>
       <c r="C841" s="58" t="n"/>
       <c r="D841" s="58" t="inlineStr">
@@ -22292,7 +21913,7 @@
       <c r="H841" s="58" t="n"/>
       <c r="I841" s="58" t="n"/>
     </row>
-    <row r="842">
+    <row r="842" s="60">
       <c r="B842" s="79" t="n"/>
       <c r="C842" s="58" t="n"/>
       <c r="D842" s="58" t="inlineStr">
@@ -22308,7 +21929,7 @@
       <c r="H842" s="58" t="n"/>
       <c r="I842" s="58" t="n"/>
     </row>
-    <row r="843">
+    <row r="843" s="60">
       <c r="B843" s="79" t="n"/>
       <c r="C843" s="58" t="n"/>
       <c r="D843" s="58" t="inlineStr">
@@ -22324,7 +21945,7 @@
       <c r="H843" s="58" t="n"/>
       <c r="I843" s="58" t="n"/>
     </row>
-    <row r="844">
+    <row r="844" s="60">
       <c r="B844" s="79" t="n"/>
       <c r="C844" s="58" t="n"/>
       <c r="D844" s="58" t="inlineStr">
@@ -22340,7 +21961,7 @@
       <c r="H844" s="58" t="n"/>
       <c r="I844" s="58" t="n"/>
     </row>
-    <row r="845">
+    <row r="845" s="60">
       <c r="B845" s="79" t="n"/>
       <c r="C845" s="58" t="n"/>
       <c r="D845" s="58" t="inlineStr">
@@ -22356,7 +21977,7 @@
       <c r="H845" s="58" t="n"/>
       <c r="I845" s="58" t="n"/>
     </row>
-    <row r="846">
+    <row r="846" s="60">
       <c r="B846" s="79" t="n"/>
       <c r="C846" s="58" t="n"/>
       <c r="D846" s="58" t="inlineStr">
@@ -22372,7 +21993,7 @@
       <c r="H846" s="58" t="n"/>
       <c r="I846" s="58" t="n"/>
     </row>
-    <row r="847">
+    <row r="847" s="60">
       <c r="B847" s="79" t="n"/>
       <c r="C847" s="58" t="n">
         <v>28601</v>
@@ -22396,7 +22017,7 @@
       <c r="H847" s="58" t="n"/>
       <c r="I847" s="58" t="n"/>
     </row>
-    <row r="848">
+    <row r="848" s="60">
       <c r="B848" s="79" t="n"/>
       <c r="C848" s="58" t="n"/>
       <c r="D848" s="58" t="inlineStr">
@@ -22412,7 +22033,7 @@
       <c r="H848" s="58" t="n"/>
       <c r="I848" s="58" t="n"/>
     </row>
-    <row r="849">
+    <row r="849" s="60">
       <c r="B849" s="79" t="n"/>
       <c r="C849" s="58" t="n"/>
       <c r="D849" s="58" t="inlineStr">
@@ -22428,7 +22049,7 @@
       <c r="H849" s="58" t="n"/>
       <c r="I849" s="58" t="n"/>
     </row>
-    <row r="850">
+    <row r="850" s="60">
       <c r="B850" s="79" t="n"/>
       <c r="C850" s="58" t="n"/>
       <c r="D850" s="58" t="inlineStr">
@@ -22444,7 +22065,7 @@
       <c r="H850" s="58" t="n"/>
       <c r="I850" s="58" t="n"/>
     </row>
-    <row r="851">
+    <row r="851" s="60">
       <c r="B851" s="79" t="n"/>
       <c r="C851" s="58" t="n">
         <v>28024</v>
@@ -22468,7 +22089,7 @@
       <c r="H851" s="58" t="n"/>
       <c r="I851" s="58" t="n"/>
     </row>
-    <row r="852">
+    <row r="852" s="60">
       <c r="B852" s="79" t="n"/>
       <c r="C852" s="58" t="n"/>
       <c r="D852" s="58" t="inlineStr">
@@ -22484,7 +22105,7 @@
       <c r="H852" s="58" t="n"/>
       <c r="I852" s="58" t="n"/>
     </row>
-    <row r="853">
+    <row r="853" s="60">
       <c r="B853" s="79" t="n"/>
       <c r="C853" s="58" t="n"/>
       <c r="D853" s="58" t="inlineStr">
@@ -22500,7 +22121,7 @@
       <c r="H853" s="58" t="n"/>
       <c r="I853" s="58" t="n"/>
     </row>
-    <row r="854">
+    <row r="854" s="60">
       <c r="B854" s="79" t="n"/>
       <c r="C854" s="58" t="n">
         <v>28300</v>
@@ -22524,7 +22145,7 @@
       <c r="H854" s="58" t="n"/>
       <c r="I854" s="58" t="n"/>
     </row>
-    <row r="855">
+    <row r="855" s="60">
       <c r="B855" s="79" t="n"/>
       <c r="C855" s="58" t="n"/>
       <c r="D855" s="58" t="inlineStr">
@@ -22540,7 +22161,7 @@
       <c r="H855" s="58" t="n"/>
       <c r="I855" s="58" t="n"/>
     </row>
-    <row r="856">
+    <row r="856" s="60">
       <c r="B856" s="79" t="n"/>
       <c r="C856" s="58" t="n"/>
       <c r="D856" s="58" t="inlineStr">
@@ -22556,7 +22177,7 @@
       <c r="H856" s="58" t="n"/>
       <c r="I856" s="58" t="n"/>
     </row>
-    <row r="857">
+    <row r="857" s="60">
       <c r="B857" s="79" t="n"/>
       <c r="C857" s="58" t="n">
         <v>28025</v>
@@ -22580,7 +22201,7 @@
       <c r="H857" s="58" t="n"/>
       <c r="I857" s="58" t="n"/>
     </row>
-    <row r="858">
+    <row r="858" s="60">
       <c r="B858" s="79" t="n"/>
       <c r="C858" s="58" t="n"/>
       <c r="D858" s="58" t="inlineStr">
@@ -22596,7 +22217,7 @@
       <c r="H858" s="58" t="n"/>
       <c r="I858" s="58" t="n"/>
     </row>
-    <row r="859">
+    <row r="859" s="60">
       <c r="B859" s="79" t="n"/>
       <c r="C859" s="58" t="n"/>
       <c r="D859" s="58" t="inlineStr">
@@ -22612,7 +22233,7 @@
       <c r="H859" s="58" t="n"/>
       <c r="I859" s="58" t="n"/>
     </row>
-    <row r="860">
+    <row r="860" s="60">
       <c r="B860" s="79" t="n"/>
       <c r="C860" s="58" t="n"/>
       <c r="D860" s="58" t="inlineStr">
@@ -22628,7 +22249,7 @@
       <c r="H860" s="58" t="n"/>
       <c r="I860" s="58" t="n"/>
     </row>
-    <row r="861">
+    <row r="861" s="60">
       <c r="B861" s="79" t="n"/>
       <c r="C861" s="58" t="n">
         <v>28026</v>
@@ -22652,7 +22273,7 @@
       <c r="H861" s="58" t="n"/>
       <c r="I861" s="58" t="n"/>
     </row>
-    <row r="862">
+    <row r="862" s="60">
       <c r="B862" s="79" t="n"/>
       <c r="C862" s="58" t="n"/>
       <c r="D862" s="58" t="inlineStr">
@@ -22668,7 +22289,7 @@
       <c r="H862" s="58" t="n"/>
       <c r="I862" s="58" t="n"/>
     </row>
-    <row r="863">
+    <row r="863" s="60">
       <c r="B863" s="79" t="n"/>
       <c r="C863" s="58" t="n"/>
       <c r="D863" s="58" t="inlineStr">
@@ -22684,7 +22305,7 @@
       <c r="H863" s="58" t="n"/>
       <c r="I863" s="58" t="n"/>
     </row>
-    <row r="864">
+    <row r="864" s="60">
       <c r="B864" s="79" t="n"/>
       <c r="C864" s="58" t="n"/>
       <c r="D864" s="58" t="inlineStr">
@@ -22700,7 +22321,7 @@
       <c r="H864" s="58" t="n"/>
       <c r="I864" s="58" t="n"/>
     </row>
-    <row r="865">
+    <row r="865" s="60">
       <c r="B865" s="79" t="n"/>
       <c r="C865" s="58" t="n"/>
       <c r="D865" s="58" t="inlineStr">
@@ -22716,7 +22337,7 @@
       <c r="H865" s="58" t="n"/>
       <c r="I865" s="58" t="n"/>
     </row>
-    <row r="866">
+    <row r="866" s="60">
       <c r="B866" s="79" t="n"/>
       <c r="C866" s="58" t="n"/>
       <c r="D866" s="58" t="inlineStr">
@@ -22732,7 +22353,7 @@
       <c r="H866" s="58" t="n"/>
       <c r="I866" s="58" t="n"/>
     </row>
-    <row r="867">
+    <row r="867" s="60">
       <c r="B867" s="79" t="n"/>
       <c r="C867" s="58" t="n"/>
       <c r="D867" s="58" t="inlineStr">
@@ -22748,7 +22369,7 @@
       <c r="H867" s="58" t="n"/>
       <c r="I867" s="58" t="n"/>
     </row>
-    <row r="868">
+    <row r="868" s="60">
       <c r="B868" s="79" t="n"/>
       <c r="C868" s="58" t="n">
         <v>28002</v>
@@ -22772,7 +22393,7 @@
       <c r="H868" s="58" t="n"/>
       <c r="I868" s="58" t="n"/>
     </row>
-    <row r="869">
+    <row r="869" s="60">
       <c r="B869" s="79" t="n"/>
       <c r="C869" s="58" t="n"/>
       <c r="D869" s="58" t="inlineStr">
@@ -22788,7 +22409,7 @@
       <c r="H869" s="58" t="n"/>
       <c r="I869" s="58" t="n"/>
     </row>
-    <row r="870">
+    <row r="870" s="60">
       <c r="B870" s="79" t="n"/>
       <c r="C870" s="58" t="n"/>
       <c r="D870" s="58" t="inlineStr">
@@ -22804,7 +22425,7 @@
       <c r="H870" s="58" t="n"/>
       <c r="I870" s="58" t="n"/>
     </row>
-    <row r="871">
+    <row r="871" s="60">
       <c r="B871" s="79" t="n"/>
       <c r="C871" s="58" t="n">
         <v>28027</v>
@@ -22828,7 +22449,7 @@
       <c r="H871" s="58" t="n"/>
       <c r="I871" s="58" t="n"/>
     </row>
-    <row r="872">
+    <row r="872" s="60">
       <c r="B872" s="80" t="n"/>
       <c r="C872" s="58" t="n"/>
       <c r="D872" s="58" t="inlineStr">

--- a/docs/ExplorationMissions_DesignDocument.xlsx
+++ b/docs/ExplorationMissions_DesignDocument.xlsx
@@ -1870,18 +1870,18 @@
           <t>Content</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="82" t="inlineStr">
-        <is>
-          <t>Author</t>
-        </is>
-      </c>
+      <c r="L3" s="82" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1" s="60">
       <c r="A4" s="5" t="n"/>
@@ -1898,11 +1898,12 @@
           <t>Exploration mission list — initial draft</t>
         </is>
       </c>
-      <c r="L4" s="85" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L4" s="85" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1" s="60">
       <c r="A5" s="5" t="n"/>
@@ -1919,11 +1920,12 @@
           <t>Exploration mission system — initial draft</t>
         </is>
       </c>
-      <c r="L5" s="89" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L5" s="89" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1" s="60">
       <c r="A6" s="5" t="n"/>
@@ -1940,11 +1942,12 @@
           <t>Small Lake in the Garden, Aerial Cart Station, Garden's End — mission list updated</t>
         </is>
       </c>
-      <c r="L6" s="91" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L6" s="91" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1" s="60">
       <c r="A7" s="5" t="n"/>
@@ -1961,11 +1964,12 @@
           <t>Where the Curtain Flutters — exploration mission list modified</t>
         </is>
       </c>
-      <c r="L7" s="91" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L7" s="91" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1" s="60">
       <c r="A8" s="5" t="n"/>
@@ -1979,14 +1983,15 @@
       </c>
       <c r="D8" s="88" t="inlineStr">
         <is>
-          <t>Burning Furnace 001 (Burning Bridge) — Carlotta's Soul removed</t>
-        </is>
-      </c>
-      <c r="L8" s="91" t="inlineStr">
+          <t>Burning Forge 001 (Burning Bridge) — Carlotta's Soul removed</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L8" s="91" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1" s="60">
       <c r="A9" s="5" t="n"/>
@@ -2003,11 +2008,12 @@
           <t>Exploration mission list updated; format changed</t>
         </is>
       </c>
-      <c r="L9" s="91" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L9" s="91" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1" s="60">
       <c r="A10" s="5" t="n"/>
@@ -2024,11 +2030,12 @@
           <t>Exploration mission list updated — Resurrection Stone ×1 added</t>
         </is>
       </c>
-      <c r="L10" s="91" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L10" s="91" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="60">
       <c r="A11" s="5" t="n"/>
@@ -2045,11 +2052,12 @@
           <t>Exploration mission list — reward typo fixed</t>
         </is>
       </c>
-      <c r="L11" s="91" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L11" s="91" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="60">
       <c r="A12" s="5" t="n"/>
@@ -2066,11 +2074,12 @@
           <t>Stamina Potion reward removed</t>
         </is>
       </c>
-      <c r="L12" s="91" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L12" s="91" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1" s="60">
       <c r="A13" s="5" t="n"/>
@@ -2084,14 +2093,15 @@
       </c>
       <c r="D13" s="88" t="inlineStr">
         <is>
-          <t>Sage's Library exploration missions added</t>
-        </is>
-      </c>
-      <c r="L13" s="91" t="inlineStr">
+          <t>Library of Sage exploration missions added</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L13" s="91" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="60">
       <c r="A14" s="5" t="n"/>
@@ -2105,14 +2115,15 @@
       </c>
       <c r="D14" s="88" t="inlineStr">
         <is>
-          <t>Sage's Library exploration mission rewards specified</t>
-        </is>
-      </c>
-      <c r="L14" s="91" t="inlineStr">
+          <t>Library of Sage exploration mission rewards specified</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L14" s="91" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="60">
       <c r="A15" s="5" t="n"/>
@@ -2129,11 +2140,12 @@
           <t>Will-o'-Wisp defeat mission removed</t>
         </is>
       </c>
-      <c r="L15" s="91" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L15" s="91" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="60">
       <c r="A16" s="5" t="n"/>
@@ -2150,11 +2162,12 @@
           <t>Difficult monster defeat exploration missions removed</t>
         </is>
       </c>
-      <c r="L16" s="91" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L16" s="91" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1" s="60">
       <c r="A17" s="5" t="n"/>
@@ -2171,11 +2184,12 @@
           <t>Completed reward areas greyed out in list</t>
         </is>
       </c>
-      <c r="L17" s="91" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L17" s="91" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="60">
       <c r="A18" s="5" t="n"/>
@@ -2192,11 +2206,12 @@
           <t>Reward list updated</t>
         </is>
       </c>
-      <c r="L18" s="91" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L18" s="91" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="60">
       <c r="A19" s="5" t="n"/>
@@ -2213,11 +2228,12 @@
           <t>Spring Waterway rewards modified</t>
         </is>
       </c>
-      <c r="L19" s="91" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>Juwon Lee</t>
         </is>
       </c>
+      <c r="L19" s="91" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="60">
       <c r="A20" s="5" t="n"/>
@@ -5686,7 +5702,7 @@
       <c r="B98" s="25" t="n"/>
       <c r="C98" s="29" t="inlineStr">
         <is>
-          <t>→ Wind Valley, Submerged Passage Etc.</t>
+          <t>→ Windy Valley, Submerged Passage Etc.</t>
         </is>
       </c>
       <c r="D98" s="25" t="n"/>
@@ -14516,13 +14532,13 @@
     <row r="431" s="60">
       <c r="B431" s="58" t="inlineStr">
         <is>
-          <t>Silak's Mansion</t>
+          <t>Mansion of Syllek</t>
         </is>
       </c>
       <c r="C431" s="58" t="n"/>
       <c r="D431" s="58" t="inlineStr">
         <is>
-          <t>Silak's Mansion World</t>
+          <t>Mansion of Syllek World</t>
         </is>
       </c>
       <c r="E431" s="58" t="n">
@@ -14744,7 +14760,7 @@
       </c>
       <c r="D443" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silak's Mansion </t>
+          <t xml:space="preserve">Mansion of Syllek </t>
         </is>
       </c>
       <c r="E443" s="58" t="n">
@@ -14800,7 +14816,7 @@
       </c>
       <c r="D446" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silak's Mansion </t>
+          <t xml:space="preserve">Mansion of Syllek </t>
         </is>
       </c>
       <c r="E446" s="58" t="n">
@@ -15864,7 +15880,7 @@
       </c>
       <c r="D505" s="58" t="inlineStr">
         <is>
-          <t>Silak's Mansion Hunting Ground</t>
+          <t>Mansion of Syllek Hunting Ground</t>
         </is>
       </c>
       <c r="E505" s="58" t="n">
@@ -16744,7 +16760,7 @@
       </c>
       <c r="D554" s="58" t="inlineStr">
         <is>
-          <t>Silak's Mansion th Hunting Ground</t>
+          <t>Mansion of Syllek th Hunting Ground</t>
         </is>
       </c>
       <c r="E554" s="58" t="n">
@@ -17052,13 +17068,13 @@
     <row r="571" s="60">
       <c r="B571" s="58" t="inlineStr">
         <is>
-          <t>Wind Valley</t>
+          <t>Windy Valley</t>
         </is>
       </c>
       <c r="C571" s="58" t="n"/>
       <c r="D571" s="58" t="inlineStr">
         <is>
-          <t>Wind Valley World</t>
+          <t>Windy Valley World</t>
         </is>
       </c>
       <c r="E571" s="58" t="n">
@@ -17120,7 +17136,7 @@
       </c>
       <c r="D574" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wind Valley </t>
+          <t xml:space="preserve">Windy Valley </t>
         </is>
       </c>
       <c r="E574" s="58" t="n">
@@ -17160,7 +17176,7 @@
       </c>
       <c r="D576" s="58" t="inlineStr">
         <is>
-          <t>Wind Valley Deep Place</t>
+          <t>Windy Valley Deep Place</t>
         </is>
       </c>
       <c r="E576" s="58" t="n">
@@ -17212,13 +17228,13 @@
     <row r="579" s="60">
       <c r="B579" s="58" t="inlineStr">
         <is>
-          <t>Burning Furnace</t>
+          <t>Burning Forge</t>
         </is>
       </c>
       <c r="C579" s="58" t="n"/>
       <c r="D579" s="58" t="inlineStr">
         <is>
-          <t>Burning Furnace World</t>
+          <t>Burning Forge World</t>
         </is>
       </c>
       <c r="E579" s="58" t="n">
@@ -17344,7 +17360,7 @@
       </c>
       <c r="D586" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Burning Furnace </t>
+          <t xml:space="preserve">Burning Forge </t>
         </is>
       </c>
       <c r="E586" s="58" t="n">
@@ -18096,7 +18112,7 @@
       </c>
       <c r="D628" s="58" t="inlineStr">
         <is>
-          <t>Burning Furnace Hunting Ground</t>
+          <t>Burning Forge Hunting Ground</t>
         </is>
       </c>
       <c r="E628" s="58" t="n">
@@ -19016,7 +19032,7 @@
       </c>
       <c r="D680" s="58" t="inlineStr">
         <is>
-          <t>Burning Furnace th Hunting Ground</t>
+          <t>Burning Forge th Hunting Ground</t>
         </is>
       </c>
       <c r="E680" s="58" t="n">
@@ -19868,13 +19884,13 @@
     <row r="727" s="60">
       <c r="B727" s="58" t="inlineStr">
         <is>
-          <t>Sage's Library</t>
+          <t>Library of Sage</t>
         </is>
       </c>
       <c r="C727" s="58" t="n"/>
       <c r="D727" s="58" t="inlineStr">
         <is>
-          <t>Sage's Library World</t>
+          <t>Library of Sage World</t>
         </is>
       </c>
       <c r="E727" s="58" t="n">
@@ -20616,7 +20632,7 @@
       </c>
       <c r="D768" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sage's Library </t>
+          <t xml:space="preserve">Library of Sage </t>
         </is>
       </c>
       <c r="E768" s="58" t="n">
@@ -20688,7 +20704,7 @@
       </c>
       <c r="D772" s="58" t="inlineStr">
         <is>
-          <t>Sage's Library Entrance</t>
+          <t>Library of Sage Entrance</t>
         </is>
       </c>
       <c r="E772" s="58" t="n">
@@ -21080,7 +21096,7 @@
       </c>
       <c r="D794" s="58" t="inlineStr">
         <is>
-          <t>Sage's Library Hunting Ground</t>
+          <t>Library of Sage Hunting Ground</t>
         </is>
       </c>
       <c r="E794" s="58" t="n">
@@ -22000,7 +22016,7 @@
       </c>
       <c r="D847" s="58" t="inlineStr">
         <is>
-          <t>Sage's Library th Hunting Ground</t>
+          <t>Library of Sage th Hunting Ground</t>
         </is>
       </c>
       <c r="E847" s="58" t="n">

--- a/docs/ExplorationMissions_DesignDocument.xlsx
+++ b/docs/ExplorationMissions_DesignDocument.xlsx
@@ -1831,7 +1831,8 @@
     <col width="8" customWidth="1" style="43" min="2" max="2"/>
     <col width="12" customWidth="1" style="43" min="3" max="3"/>
     <col width="75" customWidth="1" style="43" min="4" max="15"/>
-    <col width="18" customWidth="1" style="60" min="12" max="12"/>
+    <col width="18" customWidth="1" style="60" min="5" max="5"/>
+    <col width="8.43" customWidth="1" style="60" min="12" max="12"/>
     <col width="11.375" bestFit="1" customWidth="1" style="43" min="16" max="16"/>
     <col width="9" customWidth="1" style="43" min="17" max="16384"/>
   </cols>
@@ -2528,7 +2529,7 @@
       <c r="C7" s="15" t="n"/>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>- Provides direction and goals for exploring every corner of the field</t>
         </is>
       </c>
       <c r="E7" s="15" t="n"/>
@@ -2565,7 +2566,7 @@
       <c r="C8" s="15" t="n"/>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>- PLC</t>
+          <t>- Grants PLC (player-lifecycle currency) and gameplay-essential resources</t>
         </is>
       </c>
       <c r="E8" s="15" t="n"/>
@@ -2704,7 +2705,7 @@
       <c r="B12" s="15" t="n"/>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>- Exploration Mission Exploration Mission zone Exploration Mission 2</t>
+          <t>- Exploration Missions are categorized into World-level and Area-level missions</t>
         </is>
       </c>
       <c r="D12" s="22" t="n"/>
@@ -2741,7 +2742,7 @@
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>- Exploration Mission Complete when, Reward Grant</t>
+          <t>- Rewards are granted upon mission completion</t>
         </is>
       </c>
       <c r="D13" s="22" t="n"/>
@@ -2778,7 +2779,7 @@
       <c r="B14" s="15" t="n"/>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>- Separate's Accept Always Progressduring state</t>
+          <t>- Missions are always in progress without requiring manual acceptance</t>
         </is>
       </c>
       <c r="D14" s="18" t="n"/>
@@ -2815,7 +2816,7 @@
       <c r="B15" s="15" t="n"/>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>- World and Area Provide</t>
+          <t>- Objectives reflect the unique characteristics of each world and area</t>
         </is>
       </c>
       <c r="D15" s="18" t="n"/>
@@ -6035,7 +6036,7 @@
       <c r="B107" s="25" t="n"/>
       <c r="C107" s="31" t="inlineStr">
         <is>
-          <t>- World Exploration Mission : List during Achieve when, All Achieve when 2times Reward</t>
+          <t>- World Exploration Mission : List during Achieve when, All Achieve when 2× Reward</t>
         </is>
       </c>
       <c r="D107" s="25" t="n"/>
@@ -6072,7 +6073,7 @@
       <c r="B108" s="25" t="n"/>
       <c r="C108" s="31" t="inlineStr">
         <is>
-          <t>- Area Exploration Mission : List before Achieve when, 1times Reward</t>
+          <t>- Area Exploration Mission : List before Achieve when, 1× Reward</t>
         </is>
       </c>
       <c r="D108" s="25" t="n"/>

--- a/docs/ExplorationMissions_DesignDocument.xlsx
+++ b/docs/ExplorationMissions_DesignDocument.xlsx
@@ -1047,460 +1047,460 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>1</colOff>
-      <row>32</row>
-      <rowOff>28575</rowOff>
-    </from>
-    <to>
-      <col>36</col>
-      <colOff>9526</colOff>
-      <row>52</row>
-      <rowOff>92910</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="72" name="그림 71"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<ns0:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:ns0="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:ns2="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>2</ns0:col>
+      <ns0:colOff>1</ns0:colOff>
+      <ns0:row>32</ns0:row>
+      <ns0:rowOff>28575</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>36</ns0:col>
+      <ns0:colOff>9526</ns0:colOff>
+      <ns0:row>52</ns0:row>
+      <ns0:rowOff>92910</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="72" name="그림 71"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="400051" y="6734175"/>
           <a:ext cx="7600950" cy="4255335"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>188965</colOff>
-      <row>55</row>
-      <rowOff>114354</rowOff>
-    </from>
-    <to>
-      <col>40</col>
-      <colOff>30418</colOff>
-      <row>77</row>
-      <rowOff>142820</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="73" name="그룹 72"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>0</ns0:col>
+      <ns0:colOff>188965</ns0:colOff>
+      <ns0:row>55</ns0:row>
+      <ns0:rowOff>114354</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>40</ns0:col>
+      <ns0:colOff>30418</ns0:colOff>
+      <ns0:row>77</ns0:row>
+      <ns0:rowOff>142820</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="73" name="그룹 72"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="188965" y="11639604"/>
           <a:ext cx="8633028" cy="4638566"/>
           <a:chOff x="-271771" y="33337"/>
           <a:chExt cx="12430433" cy="6791325"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="76" name="그림 75"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="76" name="그림 75"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId2"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="3743880" y="101122"/>
             <a:ext cx="3905250" cy="1400175"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>12</col>
-      <colOff>9526</colOff>
-      <row>85</row>
-      <rowOff>2990850</rowOff>
-    </from>
-    <to>
-      <col>14</col>
-      <colOff>24164</colOff>
-      <row>85</row>
-      <rowOff>3438525</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="96" name="그림 95"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>12</ns0:col>
+      <ns0:colOff>9526</ns0:colOff>
+      <ns0:row>85</ns0:row>
+      <ns0:rowOff>2990850</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>14</ns0:col>
+      <ns0:colOff>24164</ns0:colOff>
+      <ns0:row>85</ns0:row>
+      <ns0:rowOff>3438525</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="96" name="그림 95"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId3"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="3057526" y="27470100"/>
           <a:ext cx="414688" cy="447675"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>12</col>
-      <colOff>28575</colOff>
-      <row>85</row>
-      <rowOff>3838575</rowOff>
-    </from>
-    <to>
-      <col>14</col>
-      <colOff>68929</colOff>
-      <row>85</row>
-      <rowOff>4314825</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="97" name="그림 96"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>12</ns0:col>
+      <ns0:colOff>28575</ns0:colOff>
+      <ns0:row>85</ns0:row>
+      <ns0:rowOff>3838575</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>14</ns0:col>
+      <ns0:colOff>68929</ns0:colOff>
+      <ns0:row>85</ns0:row>
+      <ns0:rowOff>4314825</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="97" name="그림 96"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId4"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="3076575" y="28317825"/>
           <a:ext cx="440404" cy="476250"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>12</col>
-      <colOff>28575</colOff>
-      <row>85</row>
-      <rowOff>4695825</rowOff>
-    </from>
-    <to>
-      <col>14</col>
-      <colOff>68904</colOff>
-      <row>86</row>
-      <rowOff>0</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="98" name="그림 97"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>12</ns0:col>
+      <ns0:colOff>28575</ns0:colOff>
+      <ns0:row>85</ns0:row>
+      <ns0:rowOff>4695825</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>14</ns0:col>
+      <ns0:colOff>68904</ns0:colOff>
+      <ns0:row>86</ns0:row>
+      <ns0:rowOff>0</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="98" name="그림 97"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId5"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="3076575" y="29832300"/>
           <a:ext cx="440379" cy="504825"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>10</col>
-      <colOff>95250</colOff>
-      <row>80</row>
-      <rowOff>1971675</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>133295</colOff>
-      <row>80</row>
-      <rowOff>2400246</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="99" name="그림 98"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>10</ns0:col>
+      <ns0:colOff>95250</ns0:colOff>
+      <ns0:row>80</ns0:row>
+      <ns0:rowOff>1971675</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>12</ns0:col>
+      <ns0:colOff>133295</ns0:colOff>
+      <ns0:row>80</ns0:row>
+      <ns0:rowOff>2400246</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="99" name="그림 98"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId6"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="2743200" y="19554825"/>
           <a:ext cx="438095" cy="428571"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>10</col>
-      <colOff>85725</colOff>
-      <row>80</row>
-      <rowOff>1114192</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>133350</colOff>
-      <row>80</row>
-      <rowOff>1485847</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="100" name="그림 99"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>10</ns0:col>
+      <ns0:colOff>85725</ns0:colOff>
+      <ns0:row>80</ns0:row>
+      <ns0:rowOff>1114192</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>12</ns0:col>
+      <ns0:colOff>133350</ns0:colOff>
+      <ns0:row>80</ns0:row>
+      <ns0:rowOff>1485847</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="100" name="그림 99"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId7"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="2733675" y="18697342"/>
           <a:ext cx="447675" cy="371655"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>65699</colOff>
-      <row>113</row>
-      <rowOff>75339</rowOff>
-    </from>
-    <to>
-      <col>40</col>
-      <colOff>27134</colOff>
-      <row>129</row>
-      <rowOff>34844</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="101" name="그룹 100"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>1</ns0:col>
+      <ns0:colOff>65699</ns0:colOff>
+      <ns0:row>113</ns0:row>
+      <ns0:rowOff>75339</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>40</ns0:col>
+      <ns0:colOff>27134</ns0:colOff>
+      <ns0:row>129</ns0:row>
+      <ns0:rowOff>34844</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="101" name="그룹 100"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="265724" y="40004139"/>
           <a:ext cx="8552985" cy="2702705"/>
           <a:chOff x="-18662" y="1043233"/>
           <a:chExt cx="24402662" cy="7711132"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="105" name="그림 104"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="105" name="그림 104"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId8"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="12192000" y="5637484"/>
             <a:ext cx="12192000" cy="3116880"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>23</col>
-      <colOff>9525</colOff>
-      <row>81</row>
-      <rowOff>3143250</rowOff>
-    </from>
-    <to>
-      <col>29</col>
-      <colOff>152232</colOff>
-      <row>81</row>
-      <rowOff>3467060</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="그림 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor editAs="oneCell">
+    <ns0:from>
+      <ns0:col>23</ns0:col>
+      <ns0:colOff>9525</ns0:colOff>
+      <ns0:row>81</ns0:row>
+      <ns0:rowOff>3143250</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>29</ns0:col>
+      <ns0:colOff>152232</ns0:colOff>
+      <ns0:row>81</ns0:row>
+      <ns0:rowOff>3467060</ns0:rowOff>
+    </ns0:to>
+    <ns0:pic>
+      <ns0:nvPicPr>
+        <ns0:cNvPr id="2" name="그림 1"/>
+        <ns0:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </ns0:cNvPicPr>
+      </ns0:nvPicPr>
+      <ns0:blipFill>
+        <a:blip ns2:embed="rId9"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:blipFill>
+      <ns0:spPr>
+        <a:xfrm>
           <a:off x="5400675" y="23860125"/>
           <a:ext cx="1342857" cy="323810"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
+        <a:prstGeom prst="rect">
+          <ns0:avLst/>
         </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>20</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>43</col>
-      <colOff>2293</colOff>
-      <row>30</row>
-      <rowOff>74718</rowOff>
-    </to>
-    <grpSp>
-      <nvGrpSpPr>
-        <cNvPr id="3" name="그룹 2"/>
-        <cNvGrpSpPr/>
-      </nvGrpSpPr>
-      <grpSpPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0">
+      </ns0:spPr>
+    </ns0:pic>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+  <ns0:twoCellAnchor>
+    <ns0:from>
+      <ns0:col>2</ns0:col>
+      <ns0:colOff>0</ns0:colOff>
+      <ns0:row>20</ns0:row>
+      <ns0:rowOff>0</ns0:rowOff>
+    </ns0:from>
+    <ns0:to>
+      <ns0:col>43</ns0:col>
+      <ns0:colOff>2293</ns0:colOff>
+      <ns0:row>30</ns0:row>
+      <ns0:rowOff>74718</ns0:rowOff>
+    </ns0:to>
+    <ns0:grpSp>
+      <ns0:nvGrpSpPr>
+        <ns0:cNvPr id="3" name="그룹 2"/>
+        <ns0:cNvGrpSpPr/>
+      </ns0:nvGrpSpPr>
+      <ns0:grpSpPr>
+        <a:xfrm rot="0">
           <a:off x="400050" y="4191000"/>
           <a:ext cx="8993893" cy="2170218"/>
           <a:chOff x="-1605579" y="3199191"/>
           <a:chExt cx="13167958" cy="3177416"/>
         </a:xfrm>
-      </grpSpPr>
-      <pic>
-        <nvPicPr>
-          <cNvPr id="5" name="그림 4"/>
-          <cNvPicPr>
-            <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-          </cNvPicPr>
-        </nvPicPr>
-        <blipFill>
-          <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-          <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      </ns0:grpSpPr>
+      <ns0:pic>
+        <ns0:nvPicPr>
+          <ns0:cNvPr id="5" name="그림 4"/>
+          <ns0:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </ns0:cNvPicPr>
+        </ns0:nvPicPr>
+        <ns0:blipFill>
+          <a:blip ns2:embed="rId10"/>
+          <a:stretch>
             <a:fillRect/>
           </a:stretch>
-        </blipFill>
-        <spPr>
-          <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </ns0:blipFill>
+        <ns0:spPr>
+          <a:xfrm>
             <a:off x="5874721" y="3199191"/>
             <a:ext cx="5687658" cy="3174987"/>
           </a:xfrm>
-          <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-            <avLst/>
+          <a:prstGeom prst="rect">
+            <ns0:avLst/>
           </a:prstGeom>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:ln>
             <a:prstDash val="solid"/>
           </a:ln>
-        </spPr>
-      </pic>
-    </grpSp>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+        </ns0:spPr>
+      </ns0:pic>
+    </ns0:grpSp>
+    <ns0:clientData/>
+  </ns0:twoCellAnchor>
+</ns0:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
